--- a/Database/DAFTAR SP2D SATKER.xlsx
+++ b/Database/DAFTAR SP2D SATKER.xlsx
@@ -725,28 +725,37 @@
     <t>00363T/403829/2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530041993</t>
+  </si>
+  <si>
+    <t>19-08-2025</t>
+  </si>
+  <si>
+    <t>00335T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-08-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 50 Pegawai/125 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530041992</t>
   </si>
   <si>
-    <t>19-08-2025</t>
-  </si>
-  <si>
     <t>00340T/403829/2025</t>
   </si>
   <si>
-    <t>11-08-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 131 Pegawai/384 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530041993</t>
-  </si>
-  <si>
-    <t>00335T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 50 Pegawai/125 Jiwa</t>
+    <t xml:space="preserve"> 259991530041994</t>
+  </si>
+  <si>
+    <t>00337T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 35 Pegawai/101 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991530041991</t>
@@ -761,15 +770,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 37 Pegawai/103 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530041994</t>
-  </si>
-  <si>
-    <t>00337T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 35 Pegawai/101 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991525018157</t>
   </si>
   <si>
@@ -779,6 +779,24 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk bulan September 2025 untuk 4 Pegawai/16 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991531008984</t>
+  </si>
+  <si>
+    <t>00339T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 170 Pegawai /532 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531008986</t>
+  </si>
+  <si>
+    <t>00338T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 23 Pegawai/52 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991531008985</t>
   </si>
   <si>
@@ -788,22 +806,13 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025  untuk 63 Pegawai/181 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991531008984</t>
-  </si>
-  <si>
-    <t>00339T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 170 Pegawai /532 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531008986</t>
-  </si>
-  <si>
-    <t>00338T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 23 Pegawai/52 jiwa</t>
+    <t xml:space="preserve"> 259991310471405</t>
+  </si>
+  <si>
+    <t>00359T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991310471406</t>
@@ -824,15 +833,6 @@
     <t>Pembayaran tunjangan kinerja bulan JULI tahun 2025 untuk 134 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310471405</t>
-  </si>
-  <si>
-    <t>00359T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330150985</t>
   </si>
   <si>
@@ -1121,48 +1121,48 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juli Tahun 2025 untuk 91 Pegawai.Sesuai Sk No 9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530020754</t>
+  </si>
+  <si>
+    <t>17-07-2025</t>
+  </si>
+  <si>
+    <t>00309T/403829/2025</t>
+  </si>
+  <si>
+    <t>09-07-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Agustus 2025 untuk 132 Pegawai/388 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991530020753</t>
+  </si>
+  <si>
+    <t>00308T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji induk Bulan Agustus 2025 untuk 38 Pegawai/107 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991530020756</t>
+  </si>
+  <si>
+    <t>00301T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Agustus 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530020755</t>
   </si>
   <si>
-    <t>17-07-2025</t>
-  </si>
-  <si>
     <t>00299T/403829/2025</t>
   </si>
   <si>
-    <t>09-07-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Agustus 2025 untuk 50 Pegawai/124 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530020754</t>
-  </si>
-  <si>
-    <t>00309T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Agustus 2025 untuk 132 Pegawai/388 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530020756</t>
-  </si>
-  <si>
-    <t>00301T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Agustus 2025 untuk 35 Pegawai/101 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530020753</t>
-  </si>
-  <si>
-    <t>00308T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji induk Bulan Agustus 2025 untuk 38 Pegawai/107 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991531004439</t>
   </si>
   <si>
@@ -1205,25 +1205,43 @@
     <t>Pembayaran Belanja Barang sesuai SPD No. 0023-0037/BRPBATPP/KP.440/VII/2025 Tanggal 19 April 2025 sd 07 Juli 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310239039</t>
+  </si>
+  <si>
+    <t>11-07-2025</t>
+  </si>
+  <si>
+    <t>00318T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310239038</t>
   </si>
   <si>
-    <t>11-07-2025</t>
-  </si>
-  <si>
     <t>00315T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 134 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310239039</t>
-  </si>
-  <si>
-    <t>00318T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 35 Pegawai</t>
+    <t xml:space="preserve"> 259991330071755</t>
+  </si>
+  <si>
+    <t>00319T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991330071754</t>
+  </si>
+  <si>
+    <t>00317T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330071753</t>
@@ -1235,24 +1253,6 @@
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 174 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330071754</t>
-  </si>
-  <si>
-    <t>00317T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991330071755</t>
-  </si>
-  <si>
-    <t>00319T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 23 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310238647</t>
   </si>
   <si>
@@ -1262,18 +1262,36 @@
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310222993</t>
+  </si>
+  <si>
+    <t>10-07-2025</t>
+  </si>
+  <si>
+    <t>00305T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310222991</t>
   </si>
   <si>
-    <t>10-07-2025</t>
-  </si>
-  <si>
     <t>00314T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 37 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310222992</t>
+  </si>
+  <si>
+    <t>00304T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310222990</t>
   </si>
   <si>
@@ -1283,24 +1301,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 132 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310222992</t>
-  </si>
-  <si>
-    <t>00304T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310222993</t>
-  </si>
-  <si>
-    <t>00305T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 34 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991305050216</t>
   </si>
   <si>
@@ -1310,6 +1310,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991330066248</t>
+  </si>
+  <si>
+    <t>00307T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 22 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991330066246</t>
   </si>
   <si>
@@ -1328,15 +1337,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 62 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330066248</t>
-  </si>
-  <si>
-    <t>00307T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 22 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310213072</t>
   </si>
   <si>
@@ -1403,27 +1403,27 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 1 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991330045564</t>
+  </si>
+  <si>
+    <t>00291T/403829/2025</t>
+  </si>
+  <si>
+    <t>01-07-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991330045565</t>
   </si>
   <si>
     <t>00292T/403829/2025</t>
   </si>
   <si>
-    <t>01-07-2025</t>
-  </si>
-  <si>
     <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330045564</t>
-  </si>
-  <si>
-    <t>00291T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310150031</t>
   </si>
   <si>
@@ -1454,21 +1454,39 @@
     <t>00288T/403829/2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530018166</t>
+  </si>
+  <si>
+    <t>25-06-2025</t>
+  </si>
+  <si>
+    <t>00270T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530018167</t>
   </si>
   <si>
-    <t>25-06-2025</t>
-  </si>
-  <si>
     <t>00271T/403829/2025</t>
   </si>
   <si>
-    <t>11-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 135 Pegawai/396 jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530018169</t>
+  </si>
+  <si>
+    <t>00267T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530018168</t>
   </si>
   <si>
@@ -1478,24 +1496,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 50 Pegawai/124 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530018169</t>
-  </si>
-  <si>
-    <t>00267T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 35 Pegawai/101 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530018166</t>
-  </si>
-  <si>
-    <t>00270T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310116799</t>
   </si>
   <si>
@@ -1520,6 +1520,15 @@
     <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530011368</t>
+  </si>
+  <si>
+    <t>00286T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 103 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530011369</t>
   </si>
   <si>
@@ -1529,13 +1538,34 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 16 Pegawai.Sesuai Sk No. B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530011368</t>
-  </si>
-  <si>
-    <t>00286T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 103 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
+    <t xml:space="preserve"> 259991531001948</t>
+  </si>
+  <si>
+    <t>00266T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 63 Pegawai/181 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001947</t>
+  </si>
+  <si>
+    <t>00282T/403829/2025</t>
+  </si>
+  <si>
+    <t>19-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001949</t>
+  </si>
+  <si>
+    <t>00268T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991531001971</t>
@@ -1547,36 +1577,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991531001949</t>
-  </si>
-  <si>
-    <t>00268T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001947</t>
-  </si>
-  <si>
-    <t>00282T/403829/2025</t>
-  </si>
-  <si>
-    <t>19-06-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001948</t>
-  </si>
-  <si>
-    <t>00266T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 63 Pegawai/181 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991525004591</t>
   </si>
   <si>
@@ -1598,15 +1598,24 @@
     <t>Penjualan Belanja Pegawai berupa Kekurangan Gaji Bulan Januari 2025 untuk 1 Pegawai/3 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310059124</t>
+  </si>
+  <si>
+    <t>13-06-2025</t>
+  </si>
+  <si>
+    <t>16-06-2025</t>
+  </si>
+  <si>
+    <t>00275T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 137 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310059125</t>
   </si>
   <si>
-    <t>13-06-2025</t>
-  </si>
-  <si>
-    <t>16-06-2025</t>
-  </si>
-  <si>
     <t>00277T/403829/2025</t>
   </si>
   <si>
@@ -1622,13 +1631,22 @@
     <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 35 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310059124</t>
-  </si>
-  <si>
-    <t>00275T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 137 Pegawai</t>
+    <t xml:space="preserve"> 259991330013160</t>
+  </si>
+  <si>
+    <t>00276T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 173 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991330013162</t>
+  </si>
+  <si>
+    <t>00279T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330013161</t>
@@ -1640,24 +1658,6 @@
     <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330013162</t>
-  </si>
-  <si>
-    <t>00279T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 23 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991330013160</t>
-  </si>
-  <si>
-    <t>00276T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 173 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991320016562</t>
   </si>
   <si>
@@ -1670,18 +1670,18 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Mei 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310050294</t>
+  </si>
+  <si>
+    <t>00273T/403829/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310050295</t>
   </si>
   <si>
     <t>00274T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310050294</t>
-  </si>
-  <si>
-    <t>00273T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310039873</t>
   </si>
   <si>
@@ -1721,43 +1721,52 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 11 Pegawai/41 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310036822</t>
+  </si>
+  <si>
+    <t>00256T/403829/2025</t>
+  </si>
+  <si>
+    <t>05-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 38 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310036825</t>
+  </si>
+  <si>
+    <t>00257T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 136 jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310036824</t>
+  </si>
+  <si>
+    <t>00254T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji bulan Mei 2025 untuk 2 pegawai/ 4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310036823</t>
   </si>
   <si>
     <t>00252T/403829/2025</t>
   </si>
   <si>
-    <t>05-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 2 Pegawai/5 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310036822</t>
-  </si>
-  <si>
-    <t>00256T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 38 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310036825</t>
-  </si>
-  <si>
-    <t>00257T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 136 jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310036824</t>
-  </si>
-  <si>
-    <t>00254T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji bulan Mei 2025 untuk 2 pegawai/ 4 Jiwa</t>
+    <t xml:space="preserve"> 259991330008176</t>
+  </si>
+  <si>
+    <t>00259T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 171 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330008175</t>
@@ -1769,15 +1778,6 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Juni 2025 untuk 1 Pegawai/1 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330008176</t>
-  </si>
-  <si>
-    <t>00259T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 171 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330008177</t>
   </si>
   <si>
@@ -1796,6 +1796,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310033061</t>
+  </si>
+  <si>
+    <t>00250T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310033060</t>
   </si>
   <si>
@@ -1805,15 +1814,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310033061</t>
-  </si>
-  <si>
-    <t>00250T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 34 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330007277</t>
   </si>
   <si>
@@ -1913,6 +1913,24 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 35 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303002007</t>
+  </si>
+  <si>
+    <t>00240T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303002006</t>
+  </si>
+  <si>
+    <t>00238T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 173 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303002008</t>
   </si>
   <si>
@@ -1922,24 +1940,6 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303002007</t>
-  </si>
-  <si>
-    <t>00240T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303002006</t>
-  </si>
-  <si>
-    <t>00238T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 173 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000975</t>
   </si>
   <si>
@@ -1952,12 +1952,24 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001413</t>
+  </si>
+  <si>
+    <t>26-05-2025</t>
+  </si>
+  <si>
+    <t>00232T/403829/2025</t>
+  </si>
+  <si>
+    <t>SPM Gaji 13 PPPK</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 50 PPPK.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001439</t>
   </si>
   <si>
-    <t>26-05-2025</t>
-  </si>
-  <si>
     <t>00228T/403829/2025</t>
   </si>
   <si>
@@ -1970,21 +1982,9 @@
     <t>00234T/403829/2025</t>
   </si>
   <si>
-    <t>SPM Gaji 13 PPPK</t>
-  </si>
-  <si>
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 35 PPPK.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001413</t>
-  </si>
-  <si>
-    <t>00232T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 50 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000406</t>
   </si>
   <si>
@@ -1994,6 +1994,24 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000383</t>
+  </si>
+  <si>
+    <t>00233T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 63 PPPK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231503000382</t>
+  </si>
+  <si>
+    <t>00229T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 173 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000384</t>
   </si>
   <si>
@@ -2003,24 +2021,6 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 23 PPPK.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000382</t>
-  </si>
-  <si>
-    <t>00229T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 173 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231503000383</t>
-  </si>
-  <si>
-    <t>00233T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 63 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000959</t>
   </si>
   <si>
@@ -2072,30 +2072,30 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000351</t>
+  </si>
+  <si>
+    <t>21-05-2025</t>
+  </si>
+  <si>
+    <t>00202T/403829/2025</t>
+  </si>
+  <si>
+    <t>08-05-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji induk PPPK Bulan Juni 2025 untuk 63 Pegawai/181 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000352</t>
   </si>
   <si>
-    <t>21-05-2025</t>
-  </si>
-  <si>
     <t>00204T/403829/2025</t>
   </si>
   <si>
-    <t>08-05-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 23 Pegawai/52 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000351</t>
-  </si>
-  <si>
-    <t>00202T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji induk PPPK Bulan Juni 2025 untuk 63 Pegawai/181 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000350</t>
   </si>
   <si>
@@ -2117,6 +2117,33 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 2 Pegawai/8 jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001202</t>
+  </si>
+  <si>
+    <t>00206T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 135 Pegawai/ 396 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001208</t>
+  </si>
+  <si>
+    <t>00201T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001201</t>
+  </si>
+  <si>
+    <t>00205T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001209</t>
   </si>
   <si>
@@ -2126,54 +2153,27 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 35 Pegawai/101 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001201</t>
-  </si>
-  <si>
-    <t>00205T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001208</t>
-  </si>
-  <si>
-    <t>00201T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001202</t>
-  </si>
-  <si>
-    <t>00206T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 135 Pegawai/ 396 Jiwa</t>
+    <t xml:space="preserve"> 250231303001771</t>
+  </si>
+  <si>
+    <t>20-05-2025</t>
+  </si>
+  <si>
+    <t>00222T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303001770</t>
   </si>
   <si>
-    <t>20-05-2025</t>
-  </si>
-  <si>
     <t>00219T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai Berupa Uang Makan PPPK Bulan April 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001771</t>
-  </si>
-  <si>
-    <t>00222T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303001766</t>
   </si>
   <si>
@@ -2246,6 +2246,24 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 173 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301005718</t>
+  </si>
+  <si>
+    <t>00213T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301005716</t>
+  </si>
+  <si>
+    <t>00211T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025  untuk 135 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301005717</t>
   </si>
   <si>
@@ -2255,39 +2273,21 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005718</t>
-  </si>
-  <si>
-    <t>00213T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301005716</t>
-  </si>
-  <si>
-    <t>00211T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025  untuk 135 Pegawai</t>
+    <t xml:space="preserve"> 250231301005582</t>
+  </si>
+  <si>
+    <t>14-05-2025</t>
+  </si>
+  <si>
+    <t>00210T/403829/2025</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301005583</t>
   </si>
   <si>
-    <t>14-05-2025</t>
-  </si>
-  <si>
     <t>00209T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005582</t>
-  </si>
-  <si>
-    <t>00210T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302005378</t>
   </si>
   <si>
@@ -2345,27 +2345,27 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025 untuk 38 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231302005132</t>
+  </si>
+  <si>
+    <t>06-05-2025</t>
+  </si>
+  <si>
+    <t>00189T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan April 2025 Idpel No. 1249-1046 An. Lemb Perikanan Darat</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231302005131</t>
   </si>
   <si>
-    <t>06-05-2025</t>
-  </si>
-  <si>
     <t>00194T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Barang sesuai Kwitansi No.02/SAj/KW/IV/2025 Tanggal 8 April 2025 berupa pemeliharaan CCTV Instalasi depok</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231302005132</t>
-  </si>
-  <si>
-    <t>00189T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan April 2025 Idpel No. 1249-1046 An. Lemb Perikanan Darat</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301005196</t>
   </si>
   <si>
@@ -2498,27 +2498,36 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan April Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001051</t>
+  </si>
+  <si>
+    <t>00158T/403829/2025</t>
+  </si>
+  <si>
+    <t>10-04-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001059</t>
+  </si>
+  <si>
+    <t>00153T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001057</t>
   </si>
   <si>
     <t>00156T/403829/2025</t>
   </si>
   <si>
-    <t>10-04-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 50 Pegawai/124 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001059</t>
-  </si>
-  <si>
-    <t>00153T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501001058</t>
   </si>
   <si>
@@ -2528,15 +2537,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 137 Pegawai/401 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001051</t>
-  </si>
-  <si>
-    <t>00158T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000303</t>
   </si>
   <si>
@@ -2585,6 +2585,15 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301004024</t>
+  </si>
+  <si>
+    <t>00176T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 138 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301004026</t>
   </si>
   <si>
@@ -2594,15 +2603,6 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301004024</t>
-  </si>
-  <si>
-    <t>00176T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 138 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301004025</t>
   </si>
   <si>
@@ -2612,6 +2612,15 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303001235</t>
+  </si>
+  <si>
+    <t>00177T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 175 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303001236</t>
   </si>
   <si>
@@ -2621,15 +2630,6 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001235</t>
-  </si>
-  <si>
-    <t>00177T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 175 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302003921</t>
   </si>
   <si>
@@ -2699,6 +2699,33 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301003745</t>
+  </si>
+  <si>
+    <t>00168T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 136 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301003744</t>
+  </si>
+  <si>
+    <t>00163T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301003746</t>
+  </si>
+  <si>
+    <t>00162T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301003743</t>
   </si>
   <si>
@@ -2708,33 +2735,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 38 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301003744</t>
-  </si>
-  <si>
-    <t>00163T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301003746</t>
-  </si>
-  <si>
-    <t>00162T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301003745</t>
-  </si>
-  <si>
-    <t>00168T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 136 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303001158</t>
   </si>
   <si>
@@ -2846,6 +2846,24 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 39 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000906</t>
+  </si>
+  <si>
+    <t>00146T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 1 Pegawai.sesuai SK No. 9 Tahun 2025 tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000908</t>
+  </si>
+  <si>
+    <t>00135T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000907</t>
   </si>
   <si>
@@ -2855,24 +2873,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 102 Pegawai.Sesuai SK No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000908</t>
-  </si>
-  <si>
-    <t>00135T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000906</t>
-  </si>
-  <si>
-    <t>00146T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 1 Pegawai.sesuai SK No. 9 Tahun 2025 tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000261</t>
   </si>
   <si>
@@ -2882,45 +2882,45 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000781</t>
+  </si>
+  <si>
+    <t>00092T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-03-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000767</t>
+  </si>
+  <si>
+    <t>00094T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 36 Pegawai/106 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000766</t>
+  </si>
+  <si>
+    <t>00089T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 137 Pegawai/403 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000765</t>
   </si>
   <si>
     <t>00090T/403829/2025</t>
   </si>
   <si>
-    <t>11-03-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 39 Pegawai/ 111 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000766</t>
-  </si>
-  <si>
-    <t>00089T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 137 Pegawai/403 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000781</t>
-  </si>
-  <si>
-    <t>00092T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000767</t>
-  </si>
-  <si>
-    <t>00094T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 36 Pegawai/106 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000254</t>
   </si>
   <si>
@@ -3086,6 +3086,15 @@
     <t>Pembayaran THR Tunkin Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000889</t>
+  </si>
+  <si>
+    <t>00129T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan februari 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000888</t>
   </si>
   <si>
@@ -3104,15 +3113,6 @@
     <t>Pembayaran THR Tunkin Tahun 2025 Untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000889</t>
-  </si>
-  <si>
-    <t>00129T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan februari 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002724</t>
   </si>
   <si>
@@ -3158,6 +3158,15 @@
     <t>Pembayaran THR Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000156</t>
+  </si>
+  <si>
+    <t>00117T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 177 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000157</t>
   </si>
   <si>
@@ -3167,13 +3176,22 @@
     <t>Pembayaran THR Tahun 2025 Untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000156</t>
-  </si>
-  <si>
-    <t>00117T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 177 Pegawai</t>
+    <t xml:space="preserve"> 250231501000527</t>
+  </si>
+  <si>
+    <t>00114T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000526</t>
+  </si>
+  <si>
+    <t>00113T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 39 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231501000528</t>
@@ -3185,15 +3203,6 @@
     <t>Pembayaran THR Tahun 2025 Untuk 139 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000527</t>
-  </si>
-  <si>
-    <t>00114T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000545</t>
   </si>
   <si>
@@ -3203,6 +3212,15 @@
     <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 16 Pegawai.</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000529</t>
+  </si>
+  <si>
+    <t>00118T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000530</t>
   </si>
   <si>
@@ -3212,24 +3230,6 @@
     <t>Pembayaran THR Tahun 2025 Untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000526</t>
-  </si>
-  <si>
-    <t>00113T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 39 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000529</t>
-  </si>
-  <si>
-    <t>00118T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302002452</t>
   </si>
   <si>
@@ -3278,6 +3278,15 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000778</t>
+  </si>
+  <si>
+    <t>00110T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 177 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000777</t>
   </si>
   <si>
@@ -3290,13 +3299,22 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Maret 2025 untuk 1 Pegawai/4 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000778</t>
-  </si>
-  <si>
-    <t>00110T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 177 Pegawai</t>
+    <t xml:space="preserve"> 250231301002370</t>
+  </si>
+  <si>
+    <t>00100T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Februari 2025 untuk 37 pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301002372</t>
+  </si>
+  <si>
+    <t>00106T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301002369</t>
@@ -3308,24 +3326,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 136 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301002372</t>
-  </si>
-  <si>
-    <t>00106T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301002370</t>
-  </si>
-  <si>
-    <t>00100T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Februari 2025 untuk 37 pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002371</t>
   </si>
   <si>
@@ -3344,6 +3344,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Februari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000774</t>
+  </si>
+  <si>
+    <t>00105T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000773</t>
   </si>
   <si>
@@ -3353,15 +3362,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000774</t>
-  </si>
-  <si>
-    <t>00105T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000772</t>
   </si>
   <si>
@@ -3473,48 +3473,48 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 90 Pegawai.sesuai Sk no.9 tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000475</t>
+  </si>
+  <si>
+    <t>25-02-2025</t>
+  </si>
+  <si>
+    <t>26-02-2025</t>
+  </si>
+  <si>
+    <t>00076T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000476</t>
+  </si>
+  <si>
+    <t>00075T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 177 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000474</t>
+  </si>
+  <si>
+    <t>00074T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan Januari 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000473</t>
   </si>
   <si>
-    <t>25-02-2025</t>
-  </si>
-  <si>
-    <t>26-02-2025</t>
-  </si>
-  <si>
     <t>00073T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 175 pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000476</t>
-  </si>
-  <si>
-    <t>00075T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 177 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000475</t>
-  </si>
-  <si>
-    <t>00076T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000474</t>
-  </si>
-  <si>
-    <t>00074T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan Januari 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000180</t>
   </si>
   <si>
@@ -3563,6 +3563,36 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 2 Pegawai /8 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000434</t>
+  </si>
+  <si>
+    <t>00067T/403829/2025</t>
+  </si>
+  <si>
+    <t>18-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 36 Pegawai/106 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000432</t>
+  </si>
+  <si>
+    <t>00064T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk bulan Maret 2025 untuk 137 Pegawai/403 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000433</t>
+  </si>
+  <si>
+    <t>00065T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk Maret 2025 untuk 50 Pegawai/123 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000431</t>
   </si>
   <si>
@@ -3572,27 +3602,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 39 Pegawai/112 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000434</t>
-  </si>
-  <si>
-    <t>00067T/403829/2025</t>
-  </si>
-  <si>
-    <t>18-02-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 36 Pegawai/106 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000433</t>
-  </si>
-  <si>
-    <t>00065T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk Maret 2025 untuk 50 Pegawai/123 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000339</t>
   </si>
   <si>
@@ -3605,15 +3614,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 16 Pegawai.sesuai SK No.04/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000432</t>
-  </si>
-  <si>
-    <t>00064T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk bulan Maret 2025 untuk 137 Pegawai/403 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000118</t>
   </si>
   <si>
@@ -3644,6 +3644,15 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 138 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301001113</t>
+  </si>
+  <si>
+    <t>00061T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301001112</t>
   </si>
   <si>
@@ -3653,39 +3662,30 @@
     <t>Pembayaran tunjangan kinerja  bulan Januari tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001113</t>
-  </si>
-  <si>
-    <t>00061T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 36 Pegawai</t>
+    <t xml:space="preserve"> 250231301001062</t>
+  </si>
+  <si>
+    <t>16-02-2025</t>
+  </si>
+  <si>
+    <t>00051T/403829/2025</t>
+  </si>
+  <si>
+    <t>13-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Januari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301001061</t>
   </si>
   <si>
-    <t>16-02-2025</t>
-  </si>
-  <si>
     <t>00052T/403829/2025</t>
   </si>
   <si>
-    <t>13-02-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 37 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001062</t>
-  </si>
-  <si>
-    <t>00051T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Januari 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000122</t>
   </si>
   <si>
@@ -3698,6 +3698,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000961</t>
+  </si>
+  <si>
+    <t>00050T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000960</t>
   </si>
   <si>
@@ -3707,15 +3716,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 136 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000961</t>
-  </si>
-  <si>
-    <t>00050T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000116</t>
   </si>
   <si>
@@ -3764,6 +3764,15 @@
     <t>Pembayaran belanja barang berupa tagihan telepon bulan Februari 2025 untuk 12 invoice</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231302000796</t>
+  </si>
+  <si>
+    <t>00048T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No. 02/SAJ/KW/II/2025 Tanggal 3 Februari 2025 berupa Pemeliharaan Halaman Kantor Instalasi Riset Pengendalian Penyakit Ikan Depok</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231302000795</t>
   </si>
   <si>
@@ -3773,15 +3782,6 @@
     <t>Pembayaran Belanja Barang sesuai Kwitansi No.001/KW-PNA/II/2025 Tanggal 6 Februari 2025 berupa Pemelliharaan Talud Cijeruk</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231302000796</t>
-  </si>
-  <si>
-    <t>00048T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang sesuai Kwitansi No. 02/SAJ/KW/II/2025 Tanggal 3 Februari 2025 berupa Pemeliharaan Halaman Kantor Instalasi Riset Pengendalian Penyakit Ikan Depok</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301000882</t>
   </si>
   <si>
@@ -3893,6 +3893,15 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000432</t>
+  </si>
+  <si>
+    <t>00030T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000433</t>
   </si>
   <si>
@@ -3902,15 +3911,6 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000432</t>
-  </si>
-  <si>
-    <t>00030T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 38 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000130</t>
   </si>
   <si>
@@ -3920,6 +3920,15 @@
     <t>Pembayaran Belanja Barang sesuai Kwitansi No. 02/MSP/KW/I/2025 Tanggal 20 Januari 2025 berupa Perbaikan Kamar Mandi dan Sanitasi</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000416</t>
+  </si>
+  <si>
+    <t>00028T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja susulan bulan Desember tahun 2024 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000417</t>
   </si>
   <si>
@@ -3929,15 +3938,6 @@
     <t>Pembayaran kekurangan tunjangan kinerja bulan Desember tahun 2024 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000416</t>
-  </si>
-  <si>
-    <t>00028T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja susulan bulan Desember tahun 2024 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000261</t>
   </si>
   <si>
@@ -3950,27 +3950,27 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 17 Pegawai.sesuai SK No.B.4/BRPBATPP/KP.340/I/2025 tanggal 2 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000385</t>
+  </si>
+  <si>
+    <t>23-01-2025</t>
+  </si>
+  <si>
+    <t>00025T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000386</t>
   </si>
   <si>
-    <t>23-01-2025</t>
-  </si>
-  <si>
     <t>00026T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000385</t>
-  </si>
-  <si>
-    <t>00025T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302000370</t>
   </si>
   <si>
@@ -3995,6 +3995,27 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Februari 2025 untuk 36 Pegawai/105 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000228</t>
+  </si>
+  <si>
+    <t>00021T/403829/2025</t>
+  </si>
+  <si>
+    <t>14-01-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 138 Pegawai/406 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000227</t>
+  </si>
+  <si>
+    <t>00019T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 39 Pegawai/112 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000229</t>
   </si>
   <si>
@@ -4004,27 +4025,6 @@
     <t>Pembayaran Belanja Pegawai Berupa Gaji Induk PPPK Bulan Februari 2025 untuk 50 Pegawai/123 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000227</t>
-  </si>
-  <si>
-    <t>00019T/403829/2025</t>
-  </si>
-  <si>
-    <t>14-01-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 39 Pegawai/112 jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000228</t>
-  </si>
-  <si>
-    <t>00021T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 138 Pegawai/406 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000048</t>
   </si>
   <si>
@@ -4067,15 +4067,24 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Januari 2025 Idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000152</t>
+  </si>
+  <si>
+    <t>10-01-2025</t>
+  </si>
+  <si>
+    <t>13-01-2025</t>
+  </si>
+  <si>
+    <t>00016T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gai Susulan Bulan Desember 2024 sd Januari 2025 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000153</t>
   </si>
   <si>
-    <t>10-01-2025</t>
-  </si>
-  <si>
-    <t>13-01-2025</t>
-  </si>
-  <si>
     <t>00017T/403829/2025</t>
   </si>
   <si>
@@ -4083,15 +4092,6 @@
   </si>
   <si>
     <t>Penyediaan Uang Persediaan BALAI RISET PERIKANAN BUDIDAYA AIR TAWAR DAN PENYULUHAN PERIKANAN Tahun Anggaran 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301000152</t>
-  </si>
-  <si>
-    <t>00016T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gai Susulan Bulan Desember 2024 sd Januari 2025 untuk 1 Pegawai/4 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303000044</t>
@@ -6830,7 +6830,7 @@
         <v>211</v>
       </c>
       <c r="E65" s="1">
-        <v>655816000</v>
+        <v>200500400</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>238</v>
@@ -6839,7 +6839,7 @@
         <v>239</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>78</v>
@@ -6866,7 +6866,7 @@
         <v>211</v>
       </c>
       <c r="E66" s="1">
-        <v>200500400</v>
+        <v>655816000</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>242</v>
@@ -6875,7 +6875,7 @@
         <v>239</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>78</v>
@@ -6902,22 +6902,22 @@
         <v>211</v>
       </c>
       <c r="E67" s="1">
-        <v>168310100</v>
+        <v>144846400</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>245</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>19</v>
@@ -6929,7 +6929,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>237</v>
@@ -6938,16 +6938,16 @@
         <v>211</v>
       </c>
       <c r="E68" s="1">
-        <v>144846400</v>
+        <v>168310100</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="H68" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>78</v>
@@ -7010,7 +7010,7 @@
         <v>211</v>
       </c>
       <c r="E70" s="1">
-        <v>268443100</v>
+        <v>844985400</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>255</v>
@@ -7019,7 +7019,7 @@
         <v>239</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>78</v>
@@ -7046,7 +7046,7 @@
         <v>211</v>
       </c>
       <c r="E71" s="1">
-        <v>844985400</v>
+        <v>91372600</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>258</v>
@@ -7055,7 +7055,7 @@
         <v>239</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>78</v>
@@ -7082,7 +7082,7 @@
         <v>211</v>
       </c>
       <c r="E72" s="1">
-        <v>91372600</v>
+        <v>268443100</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>261</v>
@@ -7112,19 +7112,19 @@
         <v>263</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E73" s="1">
-        <v>153763873</v>
+        <v>213199358</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>264</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>135</v>
@@ -7148,19 +7148,19 @@
         <v>266</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E74" s="1">
-        <v>823139642</v>
+        <v>153763873</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>267</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>135</v>
@@ -7184,19 +7184,19 @@
         <v>269</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E75" s="1">
-        <v>213199358</v>
+        <v>823139642</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>270</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>135</v>
@@ -7220,7 +7220,7 @@
         <v>272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>237</v>
@@ -7232,7 +7232,7 @@
         <v>273</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>135</v>
@@ -7256,7 +7256,7 @@
         <v>275</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>237</v>
@@ -7268,7 +7268,7 @@
         <v>276</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>135</v>
@@ -7292,10 +7292,10 @@
         <v>278</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E78" s="1">
         <v>455600</v>
@@ -7304,7 +7304,7 @@
         <v>279</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>42</v>
@@ -7328,10 +7328,10 @@
         <v>281</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E79" s="1">
         <v>698200</v>
@@ -7340,7 +7340,7 @@
         <v>282</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>42</v>
@@ -7727,7 +7727,7 @@
         <v>239</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E90" s="1">
         <v>41758847</v>
@@ -7763,7 +7763,7 @@
         <v>239</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E91" s="1">
         <v>2844264</v>
@@ -8270,7 +8270,7 @@
         <v>336</v>
       </c>
       <c r="E105" s="1">
-        <v>200371400</v>
+        <v>661725600</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>370</v>
@@ -8279,7 +8279,7 @@
         <v>371</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>78</v>
@@ -8306,7 +8306,7 @@
         <v>336</v>
       </c>
       <c r="E106" s="1">
-        <v>661725600</v>
+        <v>171835300</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>374</v>
@@ -8378,7 +8378,7 @@
         <v>336</v>
       </c>
       <c r="E108" s="1">
-        <v>171835300</v>
+        <v>200371400</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>380</v>
@@ -8387,7 +8387,7 @@
         <v>371</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>78</v>
@@ -8558,7 +8558,7 @@
         <v>397</v>
       </c>
       <c r="E113" s="1">
-        <v>822658451</v>
+        <v>154096751</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>398</v>
@@ -8594,7 +8594,7 @@
         <v>397</v>
       </c>
       <c r="E114" s="1">
-        <v>154096751</v>
+        <v>822658451</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>401</v>
@@ -8630,7 +8630,7 @@
         <v>397</v>
       </c>
       <c r="E115" s="1">
-        <v>1040244280</v>
+        <v>99668220</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>404</v>
@@ -8702,7 +8702,7 @@
         <v>397</v>
       </c>
       <c r="E117" s="1">
-        <v>99668220</v>
+        <v>1040244280</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>410</v>
@@ -8774,7 +8774,7 @@
         <v>416</v>
       </c>
       <c r="E119" s="1">
-        <v>22399900</v>
+        <v>21398250</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>417</v>
@@ -8783,7 +8783,7 @@
         <v>371</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>17</v>
@@ -8810,7 +8810,7 @@
         <v>416</v>
       </c>
       <c r="E120" s="1">
-        <v>82033000</v>
+        <v>22399900</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>420</v>
@@ -8882,7 +8882,7 @@
         <v>416</v>
       </c>
       <c r="E122" s="1">
-        <v>21398250</v>
+        <v>82033000</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>426</v>
@@ -8891,7 +8891,7 @@
         <v>371</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>17</v>
@@ -8954,7 +8954,7 @@
         <v>416</v>
       </c>
       <c r="E124" s="1">
-        <v>106926550</v>
+        <v>13597650</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>432</v>
@@ -8963,7 +8963,7 @@
         <v>371</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>17</v>
@@ -8990,7 +8990,7 @@
         <v>416</v>
       </c>
       <c r="E125" s="1">
-        <v>38519000</v>
+        <v>106926550</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>435</v>
@@ -8999,7 +8999,7 @@
         <v>371</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>17</v>
@@ -9026,7 +9026,7 @@
         <v>416</v>
       </c>
       <c r="E126" s="1">
-        <v>13597650</v>
+        <v>38519000</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>438</v>
@@ -9242,7 +9242,7 @@
         <v>456</v>
       </c>
       <c r="E132" s="1">
-        <v>4595150</v>
+        <v>597550</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>463</v>
@@ -9251,7 +9251,7 @@
         <v>464</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>17</v>
@@ -9278,7 +9278,7 @@
         <v>456</v>
       </c>
       <c r="E133" s="1">
-        <v>597550</v>
+        <v>4595150</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>467</v>
@@ -9287,7 +9287,7 @@
         <v>464</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>17</v>
@@ -9422,7 +9422,7 @@
         <v>464</v>
       </c>
       <c r="E137" s="1">
-        <v>679180900</v>
+        <v>177279700</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>481</v>
@@ -9458,7 +9458,7 @@
         <v>464</v>
       </c>
       <c r="E138" s="1">
-        <v>200371400</v>
+        <v>679180900</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>485</v>
@@ -9467,7 +9467,7 @@
         <v>482</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>78</v>
@@ -9530,7 +9530,7 @@
         <v>464</v>
       </c>
       <c r="E140" s="1">
-        <v>177279700</v>
+        <v>200371400</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>491</v>
@@ -9539,7 +9539,7 @@
         <v>482</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>78</v>
@@ -9638,7 +9638,7 @@
         <v>464</v>
       </c>
       <c r="E143" s="1">
-        <v>62679696</v>
+        <v>261119293</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>502</v>
@@ -9674,7 +9674,7 @@
         <v>464</v>
       </c>
       <c r="E144" s="1">
-        <v>261119293</v>
+        <v>62679696</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>505</v>
@@ -9710,16 +9710,16 @@
         <v>464</v>
       </c>
       <c r="E145" s="1">
-        <v>230734521</v>
+        <v>261772500</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>508</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>78</v>
@@ -9746,22 +9746,22 @@
         <v>464</v>
       </c>
       <c r="E146" s="1">
-        <v>91372600</v>
+        <v>865011300</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>511</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>19</v>
@@ -9773,7 +9773,7 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>494</v>
@@ -9782,16 +9782,16 @@
         <v>464</v>
       </c>
       <c r="E147" s="1">
-        <v>865011300</v>
+        <v>91372600</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>78</v>
@@ -9818,16 +9818,16 @@
         <v>464</v>
       </c>
       <c r="E148" s="1">
-        <v>261772500</v>
+        <v>230734521</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>78</v>
@@ -9884,10 +9884,10 @@
         <v>523</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E150" s="1">
         <v>150900</v>
@@ -9926,7 +9926,7 @@
         <v>529</v>
       </c>
       <c r="E151" s="1">
-        <v>213272917</v>
+        <v>846201196</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>530</v>
@@ -9962,7 +9962,7 @@
         <v>529</v>
       </c>
       <c r="E152" s="1">
-        <v>153824056</v>
+        <v>213272917</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>533</v>
@@ -9998,7 +9998,7 @@
         <v>529</v>
       </c>
       <c r="E153" s="1">
-        <v>846201196</v>
+        <v>153824056</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>536</v>
@@ -10034,7 +10034,7 @@
         <v>529</v>
       </c>
       <c r="E154" s="1">
-        <v>279620735</v>
+        <v>1035489776</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>539</v>
@@ -10106,7 +10106,7 @@
         <v>529</v>
       </c>
       <c r="E156" s="1">
-        <v>1035489776</v>
+        <v>279620735</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>545</v>
@@ -10178,7 +10178,7 @@
         <v>548</v>
       </c>
       <c r="E158" s="1">
-        <v>15407872</v>
+        <v>119845265</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>552</v>
@@ -10187,13 +10187,13 @@
         <v>548</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>19</v>
@@ -10214,7 +10214,7 @@
         <v>548</v>
       </c>
       <c r="E159" s="1">
-        <v>119845265</v>
+        <v>15407872</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>554</v>
@@ -10223,13 +10223,13 @@
         <v>548</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>19</v>
@@ -10394,7 +10394,7 @@
         <v>556</v>
       </c>
       <c r="E164" s="1">
-        <v>933200</v>
+        <v>22220250</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>569</v>
@@ -10403,7 +10403,7 @@
         <v>570</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>17</v>
@@ -10430,7 +10430,7 @@
         <v>556</v>
       </c>
       <c r="E165" s="1">
-        <v>22220250</v>
+        <v>79464800</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>573</v>
@@ -10466,7 +10466,7 @@
         <v>556</v>
       </c>
       <c r="E166" s="1">
-        <v>79464800</v>
+        <v>441700</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>576</v>
@@ -10475,7 +10475,7 @@
         <v>570</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>17</v>
@@ -10502,7 +10502,7 @@
         <v>556</v>
       </c>
       <c r="E167" s="1">
-        <v>441700</v>
+        <v>933200</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>579</v>
@@ -10538,7 +10538,7 @@
         <v>556</v>
       </c>
       <c r="E168" s="1">
-        <v>219100</v>
+        <v>100681700</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>582</v>
@@ -10547,7 +10547,7 @@
         <v>570</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>17</v>
@@ -10574,7 +10574,7 @@
         <v>556</v>
       </c>
       <c r="E169" s="1">
-        <v>100681700</v>
+        <v>219100</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>585</v>
@@ -10583,7 +10583,7 @@
         <v>570</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>17</v>
@@ -10682,7 +10682,7 @@
         <v>570</v>
       </c>
       <c r="E172" s="1">
-        <v>29781850</v>
+        <v>20168600</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>594</v>
@@ -10718,7 +10718,7 @@
         <v>570</v>
       </c>
       <c r="E173" s="1">
-        <v>20168600</v>
+        <v>29781850</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>597</v>
@@ -11114,7 +11114,7 @@
         <v>613</v>
       </c>
       <c r="E184" s="1">
-        <v>102434200</v>
+        <v>287324950</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>633</v>
@@ -11150,7 +11150,7 @@
         <v>613</v>
       </c>
       <c r="E185" s="1">
-        <v>287324950</v>
+        <v>1037129350</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>636</v>
@@ -11186,7 +11186,7 @@
         <v>613</v>
       </c>
       <c r="E186" s="1">
-        <v>1037129350</v>
+        <v>102434200</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>639</v>
@@ -11258,7 +11258,7 @@
         <v>613</v>
       </c>
       <c r="E188" s="1">
-        <v>751528800</v>
+        <v>204525900</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>647</v>
@@ -11267,13 +11267,13 @@
         <v>646</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>474</v>
+        <v>648</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K188" s="1" t="s">
         <v>19</v>
@@ -11285,7 +11285,7 @@
         <v>186</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>646</v>
@@ -11294,16 +11294,16 @@
         <v>613</v>
       </c>
       <c r="E189" s="1">
-        <v>147826000</v>
+        <v>751528800</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>646</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>651</v>
+        <v>474</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>78</v>
@@ -11330,7 +11330,7 @@
         <v>613</v>
       </c>
       <c r="E190" s="1">
-        <v>204525900</v>
+        <v>147826000</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>654</v>
@@ -11339,7 +11339,7 @@
         <v>646</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>78</v>
@@ -11402,7 +11402,7 @@
         <v>613</v>
       </c>
       <c r="E192" s="1">
-        <v>93291700</v>
+        <v>267194900</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>660</v>
@@ -11411,7 +11411,7 @@
         <v>646</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>78</v>
@@ -11474,7 +11474,7 @@
         <v>613</v>
       </c>
       <c r="E194" s="1">
-        <v>267194900</v>
+        <v>93291700</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>666</v>
@@ -11483,7 +11483,7 @@
         <v>646</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>78</v>
@@ -11690,7 +11690,7 @@
         <v>669</v>
       </c>
       <c r="E200" s="1">
-        <v>91372600</v>
+        <v>261772500</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>687</v>
@@ -11726,7 +11726,7 @@
         <v>669</v>
       </c>
       <c r="E201" s="1">
-        <v>261772500</v>
+        <v>91372600</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>691</v>
@@ -11834,16 +11834,16 @@
         <v>669</v>
       </c>
       <c r="E204" s="1">
-        <v>144846400</v>
+        <v>679180900</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>701</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>78</v>
@@ -11870,16 +11870,16 @@
         <v>669</v>
       </c>
       <c r="E205" s="1">
-        <v>177279700</v>
+        <v>200371400</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>704</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>78</v>
@@ -11906,16 +11906,16 @@
         <v>669</v>
       </c>
       <c r="E206" s="1">
-        <v>200371400</v>
+        <v>177279700</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>707</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>78</v>
@@ -11942,16 +11942,16 @@
         <v>669</v>
       </c>
       <c r="E207" s="1">
-        <v>679180900</v>
+        <v>144846400</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>710</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>78</v>
@@ -11978,7 +11978,7 @@
         <v>713</v>
       </c>
       <c r="E208" s="1">
-        <v>34899150</v>
+        <v>279581387</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>714</v>
@@ -11987,7 +11987,7 @@
         <v>713</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>17</v>
@@ -12014,7 +12014,7 @@
         <v>713</v>
       </c>
       <c r="E209" s="1">
-        <v>279581387</v>
+        <v>34899150</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>717</v>
@@ -12023,7 +12023,7 @@
         <v>713</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>17</v>
@@ -12302,7 +12302,7 @@
         <v>730</v>
       </c>
       <c r="E217" s="1">
-        <v>212914412</v>
+        <v>158091056</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>744</v>
@@ -12338,7 +12338,7 @@
         <v>730</v>
       </c>
       <c r="E218" s="1">
-        <v>158091056</v>
+        <v>74276700</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>747</v>
@@ -12347,7 +12347,7 @@
         <v>730</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>17</v>
@@ -12374,7 +12374,7 @@
         <v>730</v>
       </c>
       <c r="E219" s="1">
-        <v>74276700</v>
+        <v>212914412</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>750</v>
@@ -12383,7 +12383,7 @@
         <v>730</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>17</v>
@@ -12410,7 +12410,7 @@
         <v>730</v>
       </c>
       <c r="E220" s="1">
-        <v>100933077</v>
+        <v>1912000</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>754</v>
@@ -12419,13 +12419,13 @@
         <v>753</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="K220" s="1" t="s">
         <v>19</v>
@@ -12446,7 +12446,7 @@
         <v>730</v>
       </c>
       <c r="E221" s="1">
-        <v>1912000</v>
+        <v>100933077</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>756</v>
@@ -12455,13 +12455,13 @@
         <v>753</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="K221" s="1" t="s">
         <v>19</v>
@@ -12698,7 +12698,7 @@
         <v>688</v>
       </c>
       <c r="E228" s="1">
-        <v>3160500</v>
+        <v>337800</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>778</v>
@@ -12734,7 +12734,7 @@
         <v>688</v>
       </c>
       <c r="E229" s="1">
-        <v>337800</v>
+        <v>3160500</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>781</v>
@@ -13202,7 +13202,7 @@
         <v>811</v>
       </c>
       <c r="E242" s="1">
-        <v>200371400</v>
+        <v>177618600</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>828</v>
@@ -13211,7 +13211,7 @@
         <v>829</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>78</v>
@@ -13274,7 +13274,7 @@
         <v>811</v>
       </c>
       <c r="E244" s="1">
-        <v>688714100</v>
+        <v>200371400</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>835</v>
@@ -13283,7 +13283,7 @@
         <v>829</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>78</v>
@@ -13310,7 +13310,7 @@
         <v>811</v>
       </c>
       <c r="E245" s="1">
-        <v>177618600</v>
+        <v>688714100</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>838</v>
@@ -13526,7 +13526,7 @@
         <v>853</v>
       </c>
       <c r="E251" s="1">
-        <v>158436845</v>
+        <v>845082696</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>857</v>
@@ -13562,7 +13562,7 @@
         <v>853</v>
       </c>
       <c r="E252" s="1">
-        <v>845082696</v>
+        <v>158436845</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>860</v>
@@ -13634,7 +13634,7 @@
         <v>853</v>
       </c>
       <c r="E254" s="1">
-        <v>99929015</v>
+        <v>1055833082</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>866</v>
@@ -13670,7 +13670,7 @@
         <v>853</v>
       </c>
       <c r="E255" s="1">
-        <v>1055833082</v>
+        <v>99929015</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>869</v>
@@ -13958,7 +13958,7 @@
         <v>885</v>
       </c>
       <c r="E263" s="1">
-        <v>24294250</v>
+        <v>90092300</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>895</v>
@@ -14066,7 +14066,7 @@
         <v>885</v>
       </c>
       <c r="E266" s="1">
-        <v>90092300</v>
+        <v>24294250</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>904</v>
@@ -14462,7 +14462,7 @@
         <v>937</v>
       </c>
       <c r="E277" s="1">
-        <v>258570562</v>
+        <v>2548731</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>944</v>
@@ -14534,7 +14534,7 @@
         <v>937</v>
       </c>
       <c r="E279" s="1">
-        <v>2548731</v>
+        <v>258570562</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>950</v>
@@ -14606,7 +14606,7 @@
         <v>937</v>
       </c>
       <c r="E281" s="1">
-        <v>177359200</v>
+        <v>200371400</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>956</v>
@@ -14615,7 +14615,7 @@
         <v>957</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>78</v>
@@ -14642,7 +14642,7 @@
         <v>937</v>
       </c>
       <c r="E282" s="1">
-        <v>689018800</v>
+        <v>149250700</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>960</v>
@@ -14651,7 +14651,7 @@
         <v>957</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>78</v>
@@ -14678,7 +14678,7 @@
         <v>937</v>
       </c>
       <c r="E283" s="1">
-        <v>200371400</v>
+        <v>689018800</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>963</v>
@@ -14687,7 +14687,7 @@
         <v>957</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>78</v>
@@ -14714,7 +14714,7 @@
         <v>937</v>
       </c>
       <c r="E284" s="1">
-        <v>149250700</v>
+        <v>177359200</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>966</v>
@@ -14723,7 +14723,7 @@
         <v>957</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>78</v>
@@ -15326,7 +15326,7 @@
         <v>1010</v>
       </c>
       <c r="E301" s="1">
-        <v>667850</v>
+        <v>703000</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>1024</v>
@@ -15362,7 +15362,7 @@
         <v>1010</v>
       </c>
       <c r="E302" s="1">
-        <v>287324950</v>
+        <v>667850</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>1027</v>
@@ -15371,7 +15371,7 @@
         <v>1015</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>929</v>
+        <v>16</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>17</v>
@@ -15398,7 +15398,7 @@
         <v>1010</v>
       </c>
       <c r="E303" s="1">
-        <v>703000</v>
+        <v>287324950</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>1030</v>
@@ -15407,7 +15407,7 @@
         <v>1015</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>16</v>
+        <v>929</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>17</v>
@@ -15578,7 +15578,7 @@
         <v>1015</v>
       </c>
       <c r="E308" s="1">
-        <v>267194900</v>
+        <v>960197300</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>1048</v>
@@ -15587,7 +15587,7 @@
         <v>1044</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>933</v>
+        <v>1045</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>78</v>
@@ -15614,7 +15614,7 @@
         <v>1015</v>
       </c>
       <c r="E309" s="1">
-        <v>960197300</v>
+        <v>267194900</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>1051</v>
@@ -15623,7 +15623,7 @@
         <v>1044</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>78</v>
@@ -15650,7 +15650,7 @@
         <v>1015</v>
       </c>
       <c r="E310" s="1">
-        <v>762330900</v>
+        <v>4313300</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>1054</v>
@@ -15686,7 +15686,7 @@
         <v>1015</v>
       </c>
       <c r="E311" s="1">
-        <v>4313300</v>
+        <v>193894600</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>1057</v>
@@ -15722,7 +15722,7 @@
         <v>1015</v>
       </c>
       <c r="E312" s="1">
-        <v>63500000</v>
+        <v>762330900</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>1060</v>
@@ -15731,7 +15731,7 @@
         <v>1044</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>995</v>
+        <v>1045</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>78</v>
@@ -15758,7 +15758,7 @@
         <v>1015</v>
       </c>
       <c r="E313" s="1">
-        <v>151924700</v>
+        <v>63500000</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>1063</v>
@@ -15767,7 +15767,7 @@
         <v>1044</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>933</v>
+        <v>995</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>78</v>
@@ -15794,7 +15794,7 @@
         <v>1015</v>
       </c>
       <c r="E314" s="1">
-        <v>193894600</v>
+        <v>204133200</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>1066</v>
@@ -15803,7 +15803,7 @@
         <v>1044</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>78</v>
@@ -15830,7 +15830,7 @@
         <v>1015</v>
       </c>
       <c r="E315" s="1">
-        <v>204133200</v>
+        <v>151924700</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>1069</v>
@@ -16046,7 +16046,7 @@
         <v>1072</v>
       </c>
       <c r="E321" s="1">
-        <v>5246000</v>
+        <v>1067934069</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>1088</v>
@@ -16055,13 +16055,13 @@
         <v>957</v>
       </c>
       <c r="H321" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J321" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="I321" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J321" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="K321" s="1" t="s">
         <v>19</v>
@@ -16073,7 +16073,7 @@
         <v>319</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>1072</v>
@@ -16082,16 +16082,16 @@
         <v>1072</v>
       </c>
       <c r="E322" s="1">
-        <v>1067934069</v>
+        <v>5246000</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>957</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>135</v>
+        <v>1092</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>17</v>
@@ -16118,7 +16118,7 @@
         <v>1072</v>
       </c>
       <c r="E323" s="1">
-        <v>94750900</v>
+        <v>25170300</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>1095</v>
@@ -16190,7 +16190,7 @@
         <v>1072</v>
       </c>
       <c r="E325" s="1">
-        <v>25170300</v>
+        <v>94750900</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>1101</v>
@@ -16298,7 +16298,7 @@
         <v>1072</v>
       </c>
       <c r="E328" s="1">
-        <v>44072100</v>
+        <v>279548291</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>1110</v>
@@ -16307,7 +16307,7 @@
         <v>957</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>17</v>
@@ -16334,7 +16334,7 @@
         <v>1072</v>
       </c>
       <c r="E329" s="1">
-        <v>279548291</v>
+        <v>44072100</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>1113</v>
@@ -16343,7 +16343,7 @@
         <v>957</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>17</v>
@@ -16523,7 +16523,7 @@
         <v>1121</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>17</v>
@@ -16766,7 +16766,7 @@
         <v>1154</v>
       </c>
       <c r="E341" s="1">
-        <v>116066650</v>
+        <v>279584469</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>1155</v>
@@ -16775,7 +16775,7 @@
         <v>1153</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>17</v>
@@ -16838,7 +16838,7 @@
         <v>1154</v>
       </c>
       <c r="E343" s="1">
-        <v>279584469</v>
+        <v>41365850</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>1161</v>
@@ -16847,7 +16847,7 @@
         <v>1153</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>17</v>
@@ -16874,7 +16874,7 @@
         <v>1154</v>
       </c>
       <c r="E344" s="1">
-        <v>41365850</v>
+        <v>116066650</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>1164</v>
@@ -16883,7 +16883,7 @@
         <v>1153</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>17</v>
@@ -17054,22 +17054,22 @@
         <v>1168</v>
       </c>
       <c r="E349" s="1">
-        <v>177151200</v>
+        <v>149250700</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>1183</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J349" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="K349" s="1" t="s">
         <v>19</v>
@@ -17081,7 +17081,7 @@
         <v>347</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>1170</v>
@@ -17090,16 +17090,16 @@
         <v>1168</v>
       </c>
       <c r="E350" s="1">
-        <v>149250700</v>
+        <v>689692300</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>78</v>
@@ -17162,22 +17162,22 @@
         <v>1168</v>
       </c>
       <c r="E352" s="1">
-        <v>62679696</v>
+        <v>177151200</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>1193</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J352" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="K352" s="1" t="s">
         <v>19</v>
@@ -17189,7 +17189,7 @@
         <v>350</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>1170</v>
@@ -17198,16 +17198,16 @@
         <v>1168</v>
       </c>
       <c r="E353" s="1">
-        <v>689692300</v>
+        <v>62679696</v>
       </c>
       <c r="F353" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G353" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="G353" s="1" t="s">
-        <v>1180</v>
-      </c>
       <c r="H353" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>78</v>
@@ -17240,7 +17240,7 @@
         <v>1200</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="H354" s="1" t="s">
         <v>101</v>
@@ -17267,7 +17267,7 @@
         <v>1203</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="E355" s="1">
         <v>258570562</v>
@@ -17303,7 +17303,7 @@
         <v>1180</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E356" s="1">
         <v>837896759</v>
@@ -17339,10 +17339,10 @@
         <v>1180</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E357" s="1">
-        <v>213243288</v>
+        <v>158575478</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>1210</v>
@@ -17375,10 +17375,10 @@
         <v>1180</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E358" s="1">
-        <v>158575478</v>
+        <v>213243288</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>1213</v>
@@ -17414,7 +17414,7 @@
         <v>1180</v>
       </c>
       <c r="E359" s="1">
-        <v>22608400</v>
+        <v>24034050</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>1217</v>
@@ -17423,7 +17423,7 @@
         <v>1218</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>17</v>
@@ -17450,7 +17450,7 @@
         <v>1180</v>
       </c>
       <c r="E360" s="1">
-        <v>24034050</v>
+        <v>22608400</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>1221</v>
@@ -17459,7 +17459,7 @@
         <v>1218</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>17</v>
@@ -17522,16 +17522,16 @@
         <v>1180</v>
       </c>
       <c r="E362" s="1">
-        <v>89459600</v>
+        <v>33188550</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>1228</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>17</v>
@@ -17558,16 +17558,16 @@
         <v>1180</v>
       </c>
       <c r="E363" s="1">
-        <v>33188550</v>
+        <v>89459600</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>1231</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>17</v>
@@ -17699,7 +17699,7 @@
         <v>1242</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E367" s="1">
         <v>60825925</v>
@@ -17735,7 +17735,7 @@
         <v>1242</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E368" s="1">
         <v>2844264</v>
@@ -17774,7 +17774,7 @@
         <v>1242</v>
       </c>
       <c r="E369" s="1">
-        <v>34511892</v>
+        <v>12740000</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>1250</v>
@@ -17810,7 +17810,7 @@
         <v>1242</v>
       </c>
       <c r="E370" s="1">
-        <v>12740000</v>
+        <v>34511892</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>1253</v>
@@ -18206,7 +18206,7 @@
         <v>1289</v>
       </c>
       <c r="E381" s="1">
-        <v>3915950</v>
+        <v>161741108</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>1293</v>
@@ -18242,7 +18242,7 @@
         <v>1289</v>
       </c>
       <c r="E382" s="1">
-        <v>161741108</v>
+        <v>3915950</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>1296</v>
@@ -18314,7 +18314,7 @@
         <v>1284</v>
       </c>
       <c r="E384" s="1">
-        <v>679200</v>
+        <v>3915950</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>1302</v>
@@ -18323,7 +18323,7 @@
         <v>1288</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>803</v>
+        <v>135</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>17</v>
@@ -18350,7 +18350,7 @@
         <v>1284</v>
       </c>
       <c r="E385" s="1">
-        <v>3915950</v>
+        <v>679200</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>1305</v>
@@ -18359,7 +18359,7 @@
         <v>1288</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>135</v>
+        <v>803</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>17</v>
@@ -18422,7 +18422,7 @@
         <v>1312</v>
       </c>
       <c r="E387" s="1">
-        <v>346500</v>
+        <v>4759600</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>1313</v>
@@ -18431,7 +18431,7 @@
         <v>1308</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>42</v>
+        <v>1092</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>17</v>
@@ -18458,7 +18458,7 @@
         <v>1312</v>
       </c>
       <c r="E388" s="1">
-        <v>4759600</v>
+        <v>346500</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>1316</v>
@@ -18467,7 +18467,7 @@
         <v>1308</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>1089</v>
+        <v>42</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>17</v>
@@ -18566,22 +18566,22 @@
         <v>1289</v>
       </c>
       <c r="E391" s="1">
-        <v>199981800</v>
+        <v>694524200</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>1327</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J391" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="K391" s="1" t="s">
         <v>19</v>
@@ -18593,7 +18593,7 @@
         <v>389</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>1322</v>
@@ -18605,10 +18605,10 @@
         <v>176866300</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="H392" s="1" t="s">
         <v>97</v>
@@ -18638,16 +18638,16 @@
         <v>1289</v>
       </c>
       <c r="E393" s="1">
-        <v>694524200</v>
+        <v>199981800</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>1334</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>78</v>
@@ -18680,7 +18680,7 @@
         <v>1337</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="H394" s="1" t="s">
         <v>97</v>
@@ -18752,7 +18752,7 @@
         <v>1343</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="H396" s="1" t="s">
         <v>97</v>
@@ -18788,7 +18788,7 @@
         <v>1348</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="H397" s="1" t="s">
         <v>17</v>
@@ -18818,7 +18818,7 @@
         <v>1352</v>
       </c>
       <c r="E398" s="1">
-        <v>120000000</v>
+        <v>4759600</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>1353</v>
@@ -18827,13 +18827,13 @@
         <v>1351</v>
       </c>
       <c r="H398" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J398" s="1" t="s">
         <v>1354</v>
-      </c>
-      <c r="I398" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J398" s="1" t="s">
-        <v>1355</v>
       </c>
       <c r="K398" s="1" t="s">
         <v>19</v>
@@ -18845,7 +18845,7 @@
         <v>396</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>1351</v>
@@ -18854,16 +18854,16 @@
         <v>1352</v>
       </c>
       <c r="E399" s="1">
-        <v>4759600</v>
+        <v>120000000</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>1089</v>
+        <v>1357</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>17</v>

--- a/Database/DAFTAR SP2D SATKER.xlsx
+++ b/Database/DAFTAR SP2D SATKER.xlsx
@@ -725,28 +725,40 @@
     <t>00363T/403829/2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530041992</t>
+  </si>
+  <si>
+    <t>19-08-2025</t>
+  </si>
+  <si>
+    <t>00340T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-08-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 131 Pegawai/384 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530041993</t>
   </si>
   <si>
-    <t>19-08-2025</t>
-  </si>
-  <si>
     <t>00335T/403829/2025</t>
   </si>
   <si>
-    <t>11-08-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 50 Pegawai/125 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530041992</t>
-  </si>
-  <si>
-    <t>00340T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 131 Pegawai/384 Jiwa</t>
+    <t xml:space="preserve"> 259991530041991</t>
+  </si>
+  <si>
+    <t>00354T/403829/2025</t>
+  </si>
+  <si>
+    <t>15-08-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 37 Pegawai/103 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991530041994</t>
@@ -758,18 +770,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 35 Pegawai/101 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530041991</t>
-  </si>
-  <si>
-    <t>00354T/403829/2025</t>
-  </si>
-  <si>
-    <t>15-08-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 37 Pegawai/103 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991525018157</t>
   </si>
   <si>
@@ -779,6 +779,15 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk bulan September 2025 untuk 4 Pegawai/16 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991531008985</t>
+  </si>
+  <si>
+    <t>00336T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025  untuk 63 Pegawai/181 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991531008984</t>
   </si>
   <si>
@@ -797,13 +806,22 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 23 Pegawai/52 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991531008985</t>
-  </si>
-  <si>
-    <t>00336T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025  untuk 63 Pegawai/181 jiwa</t>
+    <t xml:space="preserve"> 259991310471406</t>
+  </si>
+  <si>
+    <t>00361T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310471404</t>
+  </si>
+  <si>
+    <t>00357T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan JULI tahun 2025 untuk 134 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991310471405</t>
@@ -815,24 +833,6 @@
     <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310471406</t>
-  </si>
-  <si>
-    <t>00361T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 35 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310471404</t>
-  </si>
-  <si>
-    <t>00357T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan JULI tahun 2025 untuk 134 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330150985</t>
   </si>
   <si>
@@ -1121,21 +1121,39 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juli Tahun 2025 untuk 91 Pegawai.Sesuai Sk No 9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530020755</t>
+  </si>
+  <si>
+    <t>17-07-2025</t>
+  </si>
+  <si>
+    <t>00299T/403829/2025</t>
+  </si>
+  <si>
+    <t>09-07-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Agustus 2025 untuk 50 Pegawai/124 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530020754</t>
   </si>
   <si>
-    <t>17-07-2025</t>
-  </si>
-  <si>
     <t>00309T/403829/2025</t>
   </si>
   <si>
-    <t>09-07-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Agustus 2025 untuk 132 Pegawai/388 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530020756</t>
+  </si>
+  <si>
+    <t>00301T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Agustus 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530020753</t>
   </si>
   <si>
@@ -1145,24 +1163,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji induk Bulan Agustus 2025 untuk 38 Pegawai/107 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530020756</t>
-  </si>
-  <si>
-    <t>00301T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Agustus 2025 untuk 35 Pegawai/101 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530020755</t>
-  </si>
-  <si>
-    <t>00299T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Agustus 2025 untuk 50 Pegawai/124 jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991531004439</t>
   </si>
   <si>
@@ -1205,25 +1205,43 @@
     <t>Pembayaran Belanja Barang sesuai SPD No. 0023-0037/BRPBATPP/KP.440/VII/2025 Tanggal 19 April 2025 sd 07 Juli 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310239038</t>
+  </si>
+  <si>
+    <t>11-07-2025</t>
+  </si>
+  <si>
+    <t>00315T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 134 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310239039</t>
   </si>
   <si>
-    <t>11-07-2025</t>
-  </si>
-  <si>
     <t>00318T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 35 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310239038</t>
-  </si>
-  <si>
-    <t>00315T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 134 Pegawai</t>
+    <t xml:space="preserve"> 259991330071753</t>
+  </si>
+  <si>
+    <t>00316T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 174 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991330071754</t>
+  </si>
+  <si>
+    <t>00317T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330071755</t>
@@ -1235,24 +1253,6 @@
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330071754</t>
-  </si>
-  <si>
-    <t>00317T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991330071753</t>
-  </si>
-  <si>
-    <t>00316T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 174 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310238647</t>
   </si>
   <si>
@@ -1262,45 +1262,45 @@
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310222991</t>
+  </si>
+  <si>
+    <t>10-07-2025</t>
+  </si>
+  <si>
+    <t>00314T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 37 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310222990</t>
+  </si>
+  <si>
+    <t>00313T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 132 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310222992</t>
+  </si>
+  <si>
+    <t>00304T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310222993</t>
   </si>
   <si>
-    <t>10-07-2025</t>
-  </si>
-  <si>
     <t>00305T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 34 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310222991</t>
-  </si>
-  <si>
-    <t>00314T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 37 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310222992</t>
-  </si>
-  <si>
-    <t>00304T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310222990</t>
-  </si>
-  <si>
-    <t>00313T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 132 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991305050216</t>
   </si>
   <si>
@@ -1310,6 +1310,24 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991330066246</t>
+  </si>
+  <si>
+    <t>00312T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 172 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991330066247</t>
+  </si>
+  <si>
+    <t>00306T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 62 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991330066248</t>
   </si>
   <si>
@@ -1319,24 +1337,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 22 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330066246</t>
-  </si>
-  <si>
-    <t>00312T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juni 2025 untuk 172 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991330066247</t>
-  </si>
-  <si>
-    <t>00306T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juni 2025  untuk 62 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310213072</t>
   </si>
   <si>
@@ -1403,27 +1403,27 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 1 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991330045565</t>
+  </si>
+  <si>
+    <t>00292T/403829/2025</t>
+  </si>
+  <si>
+    <t>01-07-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991330045564</t>
   </si>
   <si>
     <t>00291T/403829/2025</t>
   </si>
   <si>
-    <t>01-07-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330045565</t>
-  </si>
-  <si>
-    <t>00292T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310150031</t>
   </si>
   <si>
@@ -1454,48 +1454,48 @@
     <t>00288T/403829/2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530018167</t>
+  </si>
+  <si>
+    <t>25-06-2025</t>
+  </si>
+  <si>
+    <t>00271T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 135 Pegawai/396 jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991530018168</t>
+  </si>
+  <si>
+    <t>00265T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991530018169</t>
+  </si>
+  <si>
+    <t>00267T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530018166</t>
   </si>
   <si>
-    <t>25-06-2025</t>
-  </si>
-  <si>
     <t>00270T/403829/2025</t>
   </si>
   <si>
-    <t>11-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 39 Pegawai/111 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530018167</t>
-  </si>
-  <si>
-    <t>00271T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 135 Pegawai/396 jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530018169</t>
-  </si>
-  <si>
-    <t>00267T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 35 Pegawai/101 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991530018168</t>
-  </si>
-  <si>
-    <t>00265T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310116799</t>
   </si>
   <si>
@@ -1520,6 +1520,15 @@
     <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530011369</t>
+  </si>
+  <si>
+    <t>00285T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 16 Pegawai.Sesuai Sk No. B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530011368</t>
   </si>
   <si>
@@ -1529,13 +1538,34 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 103 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530011369</t>
-  </si>
-  <si>
-    <t>00285T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 16 Pegawai.Sesuai Sk No. B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+    <t xml:space="preserve"> 259991531001971</t>
+  </si>
+  <si>
+    <t>00287T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001949</t>
+  </si>
+  <si>
+    <t>00268T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001947</t>
+  </si>
+  <si>
+    <t>00282T/403829/2025</t>
+  </si>
+  <si>
+    <t>19-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991531001948</t>
@@ -1547,36 +1577,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 63 Pegawai/181 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991531001947</t>
-  </si>
-  <si>
-    <t>00282T/403829/2025</t>
-  </si>
-  <si>
-    <t>19-06-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001949</t>
-  </si>
-  <si>
-    <t>00268T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001971</t>
-  </si>
-  <si>
-    <t>00287T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991525004591</t>
   </si>
   <si>
@@ -1598,37 +1598,55 @@
     <t>Penjualan Belanja Pegawai berupa Kekurangan Gaji Bulan Januari 2025 untuk 1 Pegawai/3 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310059125</t>
+  </si>
+  <si>
+    <t>13-06-2025</t>
+  </si>
+  <si>
+    <t>16-06-2025</t>
+  </si>
+  <si>
+    <t>00277T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310059126</t>
+  </si>
+  <si>
+    <t>00280T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310059124</t>
   </si>
   <si>
-    <t>13-06-2025</t>
-  </si>
-  <si>
-    <t>16-06-2025</t>
-  </si>
-  <si>
     <t>00275T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 137 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310059125</t>
-  </si>
-  <si>
-    <t>00277T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310059126</t>
-  </si>
-  <si>
-    <t>00280T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 35 Pegawai</t>
+    <t xml:space="preserve"> 259991330013161</t>
+  </si>
+  <si>
+    <t>00278T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991330013162</t>
+  </si>
+  <si>
+    <t>00279T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330013160</t>
@@ -1640,24 +1658,6 @@
     <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 173 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330013162</t>
-  </si>
-  <si>
-    <t>00279T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 23 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991330013161</t>
-  </si>
-  <si>
-    <t>00278T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991320016562</t>
   </si>
   <si>
@@ -1670,18 +1670,18 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Mei 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310050295</t>
+  </si>
+  <si>
+    <t>00274T/403829/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310050294</t>
   </si>
   <si>
     <t>00273T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310050295</t>
-  </si>
-  <si>
-    <t>00274T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310039873</t>
   </si>
   <si>
@@ -1721,15 +1721,24 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 11 Pegawai/41 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310036823</t>
+  </si>
+  <si>
+    <t>00252T/403829/2025</t>
+  </si>
+  <si>
+    <t>05-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 2 Pegawai/5 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310036822</t>
   </si>
   <si>
     <t>00256T/403829/2025</t>
   </si>
   <si>
-    <t>05-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 38 Jiwa</t>
   </si>
   <si>
@@ -1751,13 +1760,13 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji bulan Mei 2025 untuk 2 pegawai/ 4 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310036823</t>
-  </si>
-  <si>
-    <t>00252T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 2 Pegawai/5 Jiwa</t>
+    <t xml:space="preserve"> 259991330008175</t>
+  </si>
+  <si>
+    <t>00253T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Juni 2025 untuk 1 Pegawai/1 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991330008176</t>
@@ -1769,15 +1778,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 171 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330008175</t>
-  </si>
-  <si>
-    <t>00253T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Juni 2025 untuk 1 Pegawai/1 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330008177</t>
   </si>
   <si>
@@ -1796,6 +1796,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310033060</t>
+  </si>
+  <si>
+    <t>00248T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310033061</t>
   </si>
   <si>
@@ -1805,15 +1814,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 34 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310033060</t>
-  </si>
-  <si>
-    <t>00248T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330007277</t>
   </si>
   <si>
@@ -1913,6 +1913,15 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 35 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303002008</t>
+  </si>
+  <si>
+    <t>00242T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 23 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303002007</t>
   </si>
   <si>
@@ -1931,15 +1940,6 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 173 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303002008</t>
-  </si>
-  <si>
-    <t>00242T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 23 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000975</t>
   </si>
   <si>
@@ -1952,39 +1952,39 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001439</t>
+  </si>
+  <si>
+    <t>26-05-2025</t>
+  </si>
+  <si>
+    <t>00228T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 137 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001414</t>
+  </si>
+  <si>
+    <t>00234T/403829/2025</t>
+  </si>
+  <si>
+    <t>SPM Gaji 13 PPPK</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 35 PPPK.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001413</t>
   </si>
   <si>
-    <t>26-05-2025</t>
-  </si>
-  <si>
     <t>00232T/403829/2025</t>
   </si>
   <si>
-    <t>SPM Gaji 13 PPPK</t>
-  </si>
-  <si>
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 50 PPPK.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001439</t>
-  </si>
-  <si>
-    <t>00228T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 137 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001414</t>
-  </si>
-  <si>
-    <t>00234T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 35 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000406</t>
   </si>
   <si>
@@ -1994,6 +1994,24 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000384</t>
+  </si>
+  <si>
+    <t>00235T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 23 PPPK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231503000382</t>
+  </si>
+  <si>
+    <t>00229T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 173 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000383</t>
   </si>
   <si>
@@ -2003,24 +2021,6 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 63 PPPK.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000382</t>
-  </si>
-  <si>
-    <t>00229T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 173 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231503000384</t>
-  </si>
-  <si>
-    <t>00235T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 23 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000959</t>
   </si>
   <si>
@@ -2072,30 +2072,30 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000352</t>
+  </si>
+  <si>
+    <t>21-05-2025</t>
+  </si>
+  <si>
+    <t>00204T/403829/2025</t>
+  </si>
+  <si>
+    <t>08-05-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 23 Pegawai/52 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000351</t>
   </si>
   <si>
-    <t>21-05-2025</t>
-  </si>
-  <si>
     <t>00202T/403829/2025</t>
   </si>
   <si>
-    <t>08-05-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji induk PPPK Bulan Juni 2025 untuk 63 Pegawai/181 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000352</t>
-  </si>
-  <si>
-    <t>00204T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 23 Pegawai/52 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000350</t>
   </si>
   <si>
@@ -2117,6 +2117,33 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 2 Pegawai/8 jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001209</t>
+  </si>
+  <si>
+    <t>00203T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001201</t>
+  </si>
+  <si>
+    <t>00205T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001208</t>
+  </si>
+  <si>
+    <t>00201T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001202</t>
   </si>
   <si>
@@ -2126,54 +2153,27 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 135 Pegawai/ 396 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001208</t>
-  </si>
-  <si>
-    <t>00201T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001201</t>
-  </si>
-  <si>
-    <t>00205T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001209</t>
-  </si>
-  <si>
-    <t>00203T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 35 Pegawai/101 Jiwa</t>
+    <t xml:space="preserve"> 250231303001770</t>
+  </si>
+  <si>
+    <t>20-05-2025</t>
+  </si>
+  <si>
+    <t>00219T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai Berupa Uang Makan PPPK Bulan April 2025 untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303001771</t>
   </si>
   <si>
-    <t>20-05-2025</t>
-  </si>
-  <si>
     <t>00222T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001770</t>
-  </si>
-  <si>
-    <t>00219T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai Berupa Uang Makan PPPK Bulan April 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303001766</t>
   </si>
   <si>
@@ -2246,6 +2246,15 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 173 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301005717</t>
+  </si>
+  <si>
+    <t>00212T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301005718</t>
   </si>
   <si>
@@ -2264,30 +2273,21 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025  untuk 135 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005717</t>
-  </si>
-  <si>
-    <t>00212T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 50 Pegawai</t>
+    <t xml:space="preserve"> 250231301005583</t>
+  </si>
+  <si>
+    <t>14-05-2025</t>
+  </si>
+  <si>
+    <t>00209T/403829/2025</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301005582</t>
   </si>
   <si>
-    <t>14-05-2025</t>
-  </si>
-  <si>
     <t>00210T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005583</t>
-  </si>
-  <si>
-    <t>00209T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302005378</t>
   </si>
   <si>
@@ -2345,27 +2345,27 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025 untuk 38 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231302005131</t>
+  </si>
+  <si>
+    <t>06-05-2025</t>
+  </si>
+  <si>
+    <t>00194T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No.02/SAj/KW/IV/2025 Tanggal 8 April 2025 berupa pemeliharaan CCTV Instalasi depok</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231302005132</t>
   </si>
   <si>
-    <t>06-05-2025</t>
-  </si>
-  <si>
     <t>00189T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan April 2025 Idpel No. 1249-1046 An. Lemb Perikanan Darat</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231302005131</t>
-  </si>
-  <si>
-    <t>00194T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang sesuai Kwitansi No.02/SAj/KW/IV/2025 Tanggal 8 April 2025 berupa pemeliharaan CCTV Instalasi depok</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301005196</t>
   </si>
   <si>
@@ -2498,45 +2498,45 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan April Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001057</t>
+  </si>
+  <si>
+    <t>00156T/403829/2025</t>
+  </si>
+  <si>
+    <t>10-04-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001059</t>
+  </si>
+  <si>
+    <t>00153T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001058</t>
+  </si>
+  <si>
+    <t>00159T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 137 Pegawai/401 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001051</t>
   </si>
   <si>
     <t>00158T/403829/2025</t>
   </si>
   <si>
-    <t>10-04-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 39 Pegawai/111 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001059</t>
-  </si>
-  <si>
-    <t>00153T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001057</t>
-  </si>
-  <si>
-    <t>00156T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001058</t>
-  </si>
-  <si>
-    <t>00159T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 137 Pegawai/401 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000303</t>
   </si>
   <si>
@@ -2585,6 +2585,15 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301004026</t>
+  </si>
+  <si>
+    <t>00175T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301004024</t>
   </si>
   <si>
@@ -2594,15 +2603,6 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 138 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301004026</t>
-  </si>
-  <si>
-    <t>00175T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301004025</t>
   </si>
   <si>
@@ -2612,6 +2612,15 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303001236</t>
+  </si>
+  <si>
+    <t>00179T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303001235</t>
   </si>
   <si>
@@ -2621,15 +2630,6 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 175 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001236</t>
-  </si>
-  <si>
-    <t>00179T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 23 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302003921</t>
   </si>
   <si>
@@ -2699,6 +2699,33 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301003743</t>
+  </si>
+  <si>
+    <t>00167T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301003744</t>
+  </si>
+  <si>
+    <t>00163T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301003746</t>
+  </si>
+  <si>
+    <t>00162T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301003745</t>
   </si>
   <si>
@@ -2708,33 +2735,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 136 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301003744</t>
-  </si>
-  <si>
-    <t>00163T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301003746</t>
-  </si>
-  <si>
-    <t>00162T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301003743</t>
-  </si>
-  <si>
-    <t>00167T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 38 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303001158</t>
   </si>
   <si>
@@ -2846,6 +2846,24 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 39 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000907</t>
+  </si>
+  <si>
+    <t>00145T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 102 Pegawai.Sesuai SK No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000908</t>
+  </si>
+  <si>
+    <t>00135T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000906</t>
   </si>
   <si>
@@ -2855,24 +2873,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 1 Pegawai.sesuai SK No. 9 Tahun 2025 tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000908</t>
-  </si>
-  <si>
-    <t>00135T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000907</t>
-  </si>
-  <si>
-    <t>00145T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 102 Pegawai.Sesuai SK No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000261</t>
   </si>
   <si>
@@ -2882,15 +2882,33 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000765</t>
+  </si>
+  <si>
+    <t>00090T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-03-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 39 Pegawai/ 111 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000766</t>
+  </si>
+  <si>
+    <t>00089T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 137 Pegawai/403 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000781</t>
   </si>
   <si>
     <t>00092T/403829/2025</t>
   </si>
   <si>
-    <t>11-03-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 50 Pegawai/124 Jiwa</t>
   </si>
   <si>
@@ -2903,24 +2921,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 36 Pegawai/106 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000766</t>
-  </si>
-  <si>
-    <t>00089T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 137 Pegawai/403 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000765</t>
-  </si>
-  <si>
-    <t>00090T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 39 Pegawai/ 111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000254</t>
   </si>
   <si>
@@ -3086,6 +3086,24 @@
     <t>Pembayaran THR Tunkin Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000888</t>
+  </si>
+  <si>
+    <t>00130T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000887</t>
+  </si>
+  <si>
+    <t>00126T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tunkin Tahun 2025 Untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000889</t>
   </si>
   <si>
@@ -3095,24 +3113,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan februari 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000888</t>
-  </si>
-  <si>
-    <t>00130T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000887</t>
-  </si>
-  <si>
-    <t>00126T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tunkin Tahun 2025 Untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002724</t>
   </si>
   <si>
@@ -3158,6 +3158,15 @@
     <t>Pembayaran THR Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000157</t>
+  </si>
+  <si>
+    <t>00119T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000156</t>
   </si>
   <si>
@@ -3167,13 +3176,13 @@
     <t>Pembayaran THR Tahun 2025 Untuk 177 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000157</t>
-  </si>
-  <si>
-    <t>00119T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 63 Pegawai</t>
+    <t xml:space="preserve"> 250231501000528</t>
+  </si>
+  <si>
+    <t>00116T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 139 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231501000527</t>
@@ -3185,6 +3194,24 @@
     <t>Pembayaran THR Tahun 2025 Untuk 1 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000545</t>
+  </si>
+  <si>
+    <t>00121T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 16 Pegawai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000530</t>
+  </si>
+  <si>
+    <t>00120T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000526</t>
   </si>
   <si>
@@ -3194,24 +3221,6 @@
     <t>Pembayaran THR Tahun 2025 Untuk 39 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000528</t>
-  </si>
-  <si>
-    <t>00116T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 139 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000545</t>
-  </si>
-  <si>
-    <t>00121T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 16 Pegawai.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000529</t>
   </si>
   <si>
@@ -3221,15 +3230,6 @@
     <t>Pembayaran THR Tahun 2025 Untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000530</t>
-  </si>
-  <si>
-    <t>00120T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 36 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302002452</t>
   </si>
   <si>
@@ -3278,6 +3278,18 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000777</t>
+  </si>
+  <si>
+    <t>00096T/403829/2025</t>
+  </si>
+  <si>
+    <t>GAJI SUSULAN</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Maret 2025 untuk 1 Pegawai/4 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000778</t>
   </si>
   <si>
@@ -3287,16 +3299,22 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 177 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000777</t>
-  </si>
-  <si>
-    <t>00096T/403829/2025</t>
-  </si>
-  <si>
-    <t>GAJI SUSULAN</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Maret 2025 untuk 1 Pegawai/4 jiwa</t>
+    <t xml:space="preserve"> 250231301002369</t>
+  </si>
+  <si>
+    <t>00103T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 136 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301002372</t>
+  </si>
+  <si>
+    <t>00106T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301002370</t>
@@ -3308,24 +3326,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Februari 2025 untuk 37 pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301002372</t>
-  </si>
-  <si>
-    <t>00106T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301002369</t>
-  </si>
-  <si>
-    <t>00103T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 136 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002371</t>
   </si>
   <si>
@@ -3344,6 +3344,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Februari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000773</t>
+  </si>
+  <si>
+    <t>00099T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000774</t>
   </si>
   <si>
@@ -3353,15 +3362,6 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000773</t>
-  </si>
-  <si>
-    <t>00099T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000772</t>
   </si>
   <si>
@@ -3473,30 +3473,39 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 90 Pegawai.sesuai Sk no.9 tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000473</t>
+  </si>
+  <si>
+    <t>25-02-2025</t>
+  </si>
+  <si>
+    <t>26-02-2025</t>
+  </si>
+  <si>
+    <t>00073T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 175 pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000476</t>
+  </si>
+  <si>
+    <t>00075T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 177 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000475</t>
   </si>
   <si>
-    <t>25-02-2025</t>
-  </si>
-  <si>
-    <t>26-02-2025</t>
-  </si>
-  <si>
     <t>00076T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000476</t>
-  </si>
-  <si>
-    <t>00075T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 177 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000474</t>
   </si>
   <si>
@@ -3506,15 +3515,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan Januari 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000473</t>
-  </si>
-  <si>
-    <t>00073T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 175 pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000180</t>
   </si>
   <si>
@@ -3563,6 +3563,15 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 2 Pegawai /8 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000431</t>
+  </si>
+  <si>
+    <t>00062T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 39 Pegawai/112 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000434</t>
   </si>
   <si>
@@ -3575,6 +3584,27 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 36 Pegawai/106 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000433</t>
+  </si>
+  <si>
+    <t>00065T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk Maret 2025 untuk 50 Pegawai/123 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000339</t>
+  </si>
+  <si>
+    <t>00069T/403829/2025</t>
+  </si>
+  <si>
+    <t>20-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 16 Pegawai.sesuai SK No.04/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000432</t>
   </si>
   <si>
@@ -3584,36 +3614,6 @@
     <t>Pembayaran Belanja Pegawai Berupa Gaji Induk bulan Maret 2025 untuk 137 Pegawai/403 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000433</t>
-  </si>
-  <si>
-    <t>00065T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk Maret 2025 untuk 50 Pegawai/123 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000431</t>
-  </si>
-  <si>
-    <t>00062T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 39 Pegawai/112 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000339</t>
-  </si>
-  <si>
-    <t>00069T/403829/2025</t>
-  </si>
-  <si>
-    <t>20-02-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 16 Pegawai.sesuai SK No.04/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000118</t>
   </si>
   <si>
@@ -3644,6 +3644,15 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 138 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301001112</t>
+  </si>
+  <si>
+    <t>00060T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Januari tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301001113</t>
   </si>
   <si>
@@ -3653,39 +3662,30 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001112</t>
-  </si>
-  <si>
-    <t>00060T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja  bulan Januari tahun 2025 untuk 50 Pegawai</t>
+    <t xml:space="preserve"> 250231301001061</t>
+  </si>
+  <si>
+    <t>16-02-2025</t>
+  </si>
+  <si>
+    <t>00052T/403829/2025</t>
+  </si>
+  <si>
+    <t>13-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 37 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301001062</t>
   </si>
   <si>
-    <t>16-02-2025</t>
-  </si>
-  <si>
     <t>00051T/403829/2025</t>
   </si>
   <si>
-    <t>13-02-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Januari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001061</t>
-  </si>
-  <si>
-    <t>00052T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 37 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000122</t>
   </si>
   <si>
@@ -3698,6 +3698,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000960</t>
+  </si>
+  <si>
+    <t>00058T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 136 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000961</t>
   </si>
   <si>
@@ -3707,15 +3716,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000960</t>
-  </si>
-  <si>
-    <t>00058T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 136 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000116</t>
   </si>
   <si>
@@ -3764,6 +3764,15 @@
     <t>Pembayaran belanja barang berupa tagihan telepon bulan Februari 2025 untuk 12 invoice</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231302000795</t>
+  </si>
+  <si>
+    <t>00049T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No.001/KW-PNA/II/2025 Tanggal 6 Februari 2025 berupa Pemelliharaan Talud Cijeruk</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231302000796</t>
   </si>
   <si>
@@ -3773,15 +3782,6 @@
     <t>Pembayaran Belanja Barang sesuai Kwitansi No. 02/SAJ/KW/II/2025 Tanggal 3 Februari 2025 berupa Pemeliharaan Halaman Kantor Instalasi Riset Pengendalian Penyakit Ikan Depok</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231302000795</t>
-  </si>
-  <si>
-    <t>00049T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang sesuai Kwitansi No.001/KW-PNA/II/2025 Tanggal 6 Februari 2025 berupa Pemelliharaan Talud Cijeruk</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301000882</t>
   </si>
   <si>
@@ -3893,6 +3893,15 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000433</t>
+  </si>
+  <si>
+    <t>00031T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000432</t>
   </si>
   <si>
@@ -3902,15 +3911,6 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 38 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000433</t>
-  </si>
-  <si>
-    <t>00031T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000130</t>
   </si>
   <si>
@@ -3920,6 +3920,15 @@
     <t>Pembayaran Belanja Barang sesuai Kwitansi No. 02/MSP/KW/I/2025 Tanggal 20 Januari 2025 berupa Perbaikan Kamar Mandi dan Sanitasi</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000417</t>
+  </si>
+  <si>
+    <t>00032T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran kekurangan tunjangan kinerja bulan Desember tahun 2024 untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000416</t>
   </si>
   <si>
@@ -3929,15 +3938,6 @@
     <t>Pembayaran tunjangan kinerja susulan bulan Desember tahun 2024 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000417</t>
-  </si>
-  <si>
-    <t>00032T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran kekurangan tunjangan kinerja bulan Desember tahun 2024 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000261</t>
   </si>
   <si>
@@ -3950,27 +3950,27 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 17 Pegawai.sesuai SK No.B.4/BRPBATPP/KP.340/I/2025 tanggal 2 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000386</t>
+  </si>
+  <si>
+    <t>23-01-2025</t>
+  </si>
+  <si>
+    <t>00026T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000385</t>
   </si>
   <si>
-    <t>23-01-2025</t>
-  </si>
-  <si>
     <t>00025T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000386</t>
-  </si>
-  <si>
-    <t>00026T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302000370</t>
   </si>
   <si>
@@ -3995,36 +3995,36 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Februari 2025 untuk 36 Pegawai/105 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000229</t>
+  </si>
+  <si>
+    <t>00010T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk PPPK Bulan Februari 2025 untuk 50 Pegawai/123 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000227</t>
+  </si>
+  <si>
+    <t>00019T/403829/2025</t>
+  </si>
+  <si>
+    <t>14-01-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 39 Pegawai/112 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000228</t>
   </si>
   <si>
     <t>00021T/403829/2025</t>
   </si>
   <si>
-    <t>14-01-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 138 Pegawai/406 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000227</t>
-  </si>
-  <si>
-    <t>00019T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 39 Pegawai/112 jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000229</t>
-  </si>
-  <si>
-    <t>00010T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai Berupa Gaji Induk PPPK Bulan Februari 2025 untuk 50 Pegawai/123 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000048</t>
   </si>
   <si>
@@ -4067,31 +4067,31 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Januari 2025 Idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000153</t>
+  </si>
+  <si>
+    <t>10-01-2025</t>
+  </si>
+  <si>
+    <t>13-01-2025</t>
+  </si>
+  <si>
+    <t>00017T/403829/2025</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>Penyediaan Uang Persediaan BALAI RISET PERIKANAN BUDIDAYA AIR TAWAR DAN PENYULUHAN PERIKANAN Tahun Anggaran 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000152</t>
   </si>
   <si>
-    <t>10-01-2025</t>
-  </si>
-  <si>
-    <t>13-01-2025</t>
-  </si>
-  <si>
     <t>00016T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Gai Susulan Bulan Desember 2024 sd Januari 2025 untuk 1 Pegawai/4 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301000153</t>
-  </si>
-  <si>
-    <t>00017T/403829/2025</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>Penyediaan Uang Persediaan BALAI RISET PERIKANAN BUDIDAYA AIR TAWAR DAN PENYULUHAN PERIKANAN Tahun Anggaran 2025</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303000044</t>
@@ -6830,7 +6830,7 @@
         <v>211</v>
       </c>
       <c r="E65" s="1">
-        <v>200500400</v>
+        <v>655816000</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>238</v>
@@ -6839,7 +6839,7 @@
         <v>239</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>78</v>
@@ -6866,7 +6866,7 @@
         <v>211</v>
       </c>
       <c r="E66" s="1">
-        <v>655816000</v>
+        <v>200500400</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>242</v>
@@ -6875,7 +6875,7 @@
         <v>239</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>78</v>
@@ -6902,22 +6902,22 @@
         <v>211</v>
       </c>
       <c r="E67" s="1">
-        <v>144846400</v>
+        <v>168310100</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>245</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>19</v>
@@ -6929,7 +6929,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>237</v>
@@ -6938,16 +6938,16 @@
         <v>211</v>
       </c>
       <c r="E68" s="1">
-        <v>168310100</v>
+        <v>144846400</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>78</v>
@@ -7010,7 +7010,7 @@
         <v>211</v>
       </c>
       <c r="E70" s="1">
-        <v>844985400</v>
+        <v>268443100</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>255</v>
@@ -7019,7 +7019,7 @@
         <v>239</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>78</v>
@@ -7046,7 +7046,7 @@
         <v>211</v>
       </c>
       <c r="E71" s="1">
-        <v>91372600</v>
+        <v>844985400</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>258</v>
@@ -7055,7 +7055,7 @@
         <v>239</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>78</v>
@@ -7082,7 +7082,7 @@
         <v>211</v>
       </c>
       <c r="E72" s="1">
-        <v>268443100</v>
+        <v>91372600</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>261</v>
@@ -7112,19 +7112,19 @@
         <v>263</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E73" s="1">
-        <v>213199358</v>
+        <v>153763873</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>264</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>135</v>
@@ -7148,19 +7148,19 @@
         <v>266</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E74" s="1">
-        <v>153763873</v>
+        <v>823139642</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>267</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>135</v>
@@ -7184,19 +7184,19 @@
         <v>269</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E75" s="1">
-        <v>823139642</v>
+        <v>213199358</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>270</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>135</v>
@@ -7220,7 +7220,7 @@
         <v>272</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>237</v>
@@ -7232,7 +7232,7 @@
         <v>273</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>135</v>
@@ -7256,7 +7256,7 @@
         <v>275</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>237</v>
@@ -7268,7 +7268,7 @@
         <v>276</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>135</v>
@@ -7292,10 +7292,10 @@
         <v>278</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E78" s="1">
         <v>455600</v>
@@ -7304,7 +7304,7 @@
         <v>279</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>42</v>
@@ -7328,10 +7328,10 @@
         <v>281</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E79" s="1">
         <v>698200</v>
@@ -7340,7 +7340,7 @@
         <v>282</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>42</v>
@@ -7727,7 +7727,7 @@
         <v>239</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E90" s="1">
         <v>41758847</v>
@@ -7763,7 +7763,7 @@
         <v>239</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E91" s="1">
         <v>2844264</v>
@@ -8270,7 +8270,7 @@
         <v>336</v>
       </c>
       <c r="E105" s="1">
-        <v>661725600</v>
+        <v>200371400</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>370</v>
@@ -8279,7 +8279,7 @@
         <v>371</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>78</v>
@@ -8306,7 +8306,7 @@
         <v>336</v>
       </c>
       <c r="E106" s="1">
-        <v>171835300</v>
+        <v>661725600</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>374</v>
@@ -8378,7 +8378,7 @@
         <v>336</v>
       </c>
       <c r="E108" s="1">
-        <v>200371400</v>
+        <v>171835300</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>380</v>
@@ -8387,7 +8387,7 @@
         <v>371</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>78</v>
@@ -8558,7 +8558,7 @@
         <v>397</v>
       </c>
       <c r="E113" s="1">
-        <v>154096751</v>
+        <v>822658451</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>398</v>
@@ -8594,7 +8594,7 @@
         <v>397</v>
       </c>
       <c r="E114" s="1">
-        <v>822658451</v>
+        <v>154096751</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>401</v>
@@ -8630,7 +8630,7 @@
         <v>397</v>
       </c>
       <c r="E115" s="1">
-        <v>99668220</v>
+        <v>1040244280</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>404</v>
@@ -8702,7 +8702,7 @@
         <v>397</v>
       </c>
       <c r="E117" s="1">
-        <v>1040244280</v>
+        <v>99668220</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>410</v>
@@ -8774,7 +8774,7 @@
         <v>416</v>
       </c>
       <c r="E119" s="1">
-        <v>21398250</v>
+        <v>22399900</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>417</v>
@@ -8783,7 +8783,7 @@
         <v>371</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>17</v>
@@ -8810,7 +8810,7 @@
         <v>416</v>
       </c>
       <c r="E120" s="1">
-        <v>22399900</v>
+        <v>82033000</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>420</v>
@@ -8882,7 +8882,7 @@
         <v>416</v>
       </c>
       <c r="E122" s="1">
-        <v>82033000</v>
+        <v>21398250</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>426</v>
@@ -8891,7 +8891,7 @@
         <v>371</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>17</v>
@@ -8954,7 +8954,7 @@
         <v>416</v>
       </c>
       <c r="E124" s="1">
-        <v>13597650</v>
+        <v>106926550</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>432</v>
@@ -8963,7 +8963,7 @@
         <v>371</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>17</v>
@@ -8990,7 +8990,7 @@
         <v>416</v>
       </c>
       <c r="E125" s="1">
-        <v>106926550</v>
+        <v>38519000</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>435</v>
@@ -8999,7 +8999,7 @@
         <v>371</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>17</v>
@@ -9026,7 +9026,7 @@
         <v>416</v>
       </c>
       <c r="E126" s="1">
-        <v>38519000</v>
+        <v>13597650</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>438</v>
@@ -9242,7 +9242,7 @@
         <v>456</v>
       </c>
       <c r="E132" s="1">
-        <v>597550</v>
+        <v>4595150</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>463</v>
@@ -9251,7 +9251,7 @@
         <v>464</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>17</v>
@@ -9278,7 +9278,7 @@
         <v>456</v>
       </c>
       <c r="E133" s="1">
-        <v>4595150</v>
+        <v>597550</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>467</v>
@@ -9287,7 +9287,7 @@
         <v>464</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>17</v>
@@ -9422,7 +9422,7 @@
         <v>464</v>
       </c>
       <c r="E137" s="1">
-        <v>177279700</v>
+        <v>679180900</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>481</v>
@@ -9458,7 +9458,7 @@
         <v>464</v>
       </c>
       <c r="E138" s="1">
-        <v>679180900</v>
+        <v>200371400</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>485</v>
@@ -9467,7 +9467,7 @@
         <v>482</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>78</v>
@@ -9530,7 +9530,7 @@
         <v>464</v>
       </c>
       <c r="E140" s="1">
-        <v>200371400</v>
+        <v>177279700</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>491</v>
@@ -9539,7 +9539,7 @@
         <v>482</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>78</v>
@@ -9638,7 +9638,7 @@
         <v>464</v>
       </c>
       <c r="E143" s="1">
-        <v>261119293</v>
+        <v>62679696</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>502</v>
@@ -9674,7 +9674,7 @@
         <v>464</v>
       </c>
       <c r="E144" s="1">
-        <v>62679696</v>
+        <v>261119293</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>505</v>
@@ -9710,16 +9710,16 @@
         <v>464</v>
       </c>
       <c r="E145" s="1">
-        <v>261772500</v>
+        <v>230734521</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>508</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>78</v>
@@ -9746,22 +9746,22 @@
         <v>464</v>
       </c>
       <c r="E146" s="1">
-        <v>865011300</v>
+        <v>91372600</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>511</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>19</v>
@@ -9773,7 +9773,7 @@
         <v>144</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>494</v>
@@ -9782,16 +9782,16 @@
         <v>464</v>
       </c>
       <c r="E147" s="1">
-        <v>91372600</v>
+        <v>865011300</v>
       </c>
       <c r="F147" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G147" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G147" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="H147" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>78</v>
@@ -9818,16 +9818,16 @@
         <v>464</v>
       </c>
       <c r="E148" s="1">
-        <v>230734521</v>
+        <v>261772500</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>78</v>
@@ -9884,10 +9884,10 @@
         <v>523</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E150" s="1">
         <v>150900</v>
@@ -9926,7 +9926,7 @@
         <v>529</v>
       </c>
       <c r="E151" s="1">
-        <v>846201196</v>
+        <v>213272917</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>530</v>
@@ -9962,7 +9962,7 @@
         <v>529</v>
       </c>
       <c r="E152" s="1">
-        <v>213272917</v>
+        <v>153824056</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>533</v>
@@ -9998,7 +9998,7 @@
         <v>529</v>
       </c>
       <c r="E153" s="1">
-        <v>153824056</v>
+        <v>846201196</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>536</v>
@@ -10034,7 +10034,7 @@
         <v>529</v>
       </c>
       <c r="E154" s="1">
-        <v>1035489776</v>
+        <v>279620735</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>539</v>
@@ -10106,7 +10106,7 @@
         <v>529</v>
       </c>
       <c r="E156" s="1">
-        <v>279620735</v>
+        <v>1035489776</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>545</v>
@@ -10178,7 +10178,7 @@
         <v>548</v>
       </c>
       <c r="E158" s="1">
-        <v>119845265</v>
+        <v>15407872</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>552</v>
@@ -10187,13 +10187,13 @@
         <v>548</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>19</v>
@@ -10214,7 +10214,7 @@
         <v>548</v>
       </c>
       <c r="E159" s="1">
-        <v>15407872</v>
+        <v>119845265</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>554</v>
@@ -10223,13 +10223,13 @@
         <v>548</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>19</v>
@@ -10394,7 +10394,7 @@
         <v>556</v>
       </c>
       <c r="E164" s="1">
-        <v>22220250</v>
+        <v>933200</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>569</v>
@@ -10403,7 +10403,7 @@
         <v>570</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>17</v>
@@ -10430,7 +10430,7 @@
         <v>556</v>
       </c>
       <c r="E165" s="1">
-        <v>79464800</v>
+        <v>22220250</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>573</v>
@@ -10466,7 +10466,7 @@
         <v>556</v>
       </c>
       <c r="E166" s="1">
-        <v>441700</v>
+        <v>79464800</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>576</v>
@@ -10475,7 +10475,7 @@
         <v>570</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>17</v>
@@ -10502,7 +10502,7 @@
         <v>556</v>
       </c>
       <c r="E167" s="1">
-        <v>933200</v>
+        <v>441700</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>579</v>
@@ -10538,7 +10538,7 @@
         <v>556</v>
       </c>
       <c r="E168" s="1">
-        <v>100681700</v>
+        <v>219100</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>582</v>
@@ -10547,7 +10547,7 @@
         <v>570</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>17</v>
@@ -10574,7 +10574,7 @@
         <v>556</v>
       </c>
       <c r="E169" s="1">
-        <v>219100</v>
+        <v>100681700</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>585</v>
@@ -10583,7 +10583,7 @@
         <v>570</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>17</v>
@@ -10682,7 +10682,7 @@
         <v>570</v>
       </c>
       <c r="E172" s="1">
-        <v>20168600</v>
+        <v>29781850</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>594</v>
@@ -10718,7 +10718,7 @@
         <v>570</v>
       </c>
       <c r="E173" s="1">
-        <v>29781850</v>
+        <v>20168600</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>597</v>
@@ -11114,7 +11114,7 @@
         <v>613</v>
       </c>
       <c r="E184" s="1">
-        <v>287324950</v>
+        <v>102434200</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>633</v>
@@ -11150,7 +11150,7 @@
         <v>613</v>
       </c>
       <c r="E185" s="1">
-        <v>1037129350</v>
+        <v>287324950</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>636</v>
@@ -11186,7 +11186,7 @@
         <v>613</v>
       </c>
       <c r="E186" s="1">
-        <v>102434200</v>
+        <v>1037129350</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>639</v>
@@ -11258,7 +11258,7 @@
         <v>613</v>
       </c>
       <c r="E188" s="1">
-        <v>204525900</v>
+        <v>751528800</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>647</v>
@@ -11267,13 +11267,13 @@
         <v>646</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>648</v>
+        <v>474</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K188" s="1" t="s">
         <v>19</v>
@@ -11285,7 +11285,7 @@
         <v>186</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>646</v>
@@ -11294,16 +11294,16 @@
         <v>613</v>
       </c>
       <c r="E189" s="1">
-        <v>751528800</v>
+        <v>147826000</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>646</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>474</v>
+        <v>651</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>78</v>
@@ -11330,7 +11330,7 @@
         <v>613</v>
       </c>
       <c r="E190" s="1">
-        <v>147826000</v>
+        <v>204525900</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>654</v>
@@ -11339,7 +11339,7 @@
         <v>646</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>78</v>
@@ -11402,7 +11402,7 @@
         <v>613</v>
       </c>
       <c r="E192" s="1">
-        <v>267194900</v>
+        <v>93291700</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>660</v>
@@ -11411,7 +11411,7 @@
         <v>646</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>78</v>
@@ -11474,7 +11474,7 @@
         <v>613</v>
       </c>
       <c r="E194" s="1">
-        <v>93291700</v>
+        <v>267194900</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>666</v>
@@ -11483,7 +11483,7 @@
         <v>646</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>78</v>
@@ -11690,7 +11690,7 @@
         <v>669</v>
       </c>
       <c r="E200" s="1">
-        <v>261772500</v>
+        <v>91372600</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>687</v>
@@ -11726,7 +11726,7 @@
         <v>669</v>
       </c>
       <c r="E201" s="1">
-        <v>91372600</v>
+        <v>261772500</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>691</v>
@@ -11834,16 +11834,16 @@
         <v>669</v>
       </c>
       <c r="E204" s="1">
-        <v>679180900</v>
+        <v>144846400</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>701</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>78</v>
@@ -11870,16 +11870,16 @@
         <v>669</v>
       </c>
       <c r="E205" s="1">
-        <v>200371400</v>
+        <v>177279700</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>704</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>78</v>
@@ -11906,16 +11906,16 @@
         <v>669</v>
       </c>
       <c r="E206" s="1">
-        <v>177279700</v>
+        <v>200371400</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>707</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>78</v>
@@ -11942,16 +11942,16 @@
         <v>669</v>
       </c>
       <c r="E207" s="1">
-        <v>144846400</v>
+        <v>679180900</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>710</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>78</v>
@@ -11978,7 +11978,7 @@
         <v>713</v>
       </c>
       <c r="E208" s="1">
-        <v>279581387</v>
+        <v>34899150</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>714</v>
@@ -11987,7 +11987,7 @@
         <v>713</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>17</v>
@@ -12014,7 +12014,7 @@
         <v>713</v>
       </c>
       <c r="E209" s="1">
-        <v>34899150</v>
+        <v>279581387</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>717</v>
@@ -12023,7 +12023,7 @@
         <v>713</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>17</v>
@@ -12302,7 +12302,7 @@
         <v>730</v>
       </c>
       <c r="E217" s="1">
-        <v>158091056</v>
+        <v>212914412</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>744</v>
@@ -12338,7 +12338,7 @@
         <v>730</v>
       </c>
       <c r="E218" s="1">
-        <v>74276700</v>
+        <v>158091056</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>747</v>
@@ -12347,7 +12347,7 @@
         <v>730</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>17</v>
@@ -12374,7 +12374,7 @@
         <v>730</v>
       </c>
       <c r="E219" s="1">
-        <v>212914412</v>
+        <v>74276700</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>750</v>
@@ -12383,7 +12383,7 @@
         <v>730</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>17</v>
@@ -12410,7 +12410,7 @@
         <v>730</v>
       </c>
       <c r="E220" s="1">
-        <v>1912000</v>
+        <v>100933077</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>754</v>
@@ -12419,13 +12419,13 @@
         <v>753</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="K220" s="1" t="s">
         <v>19</v>
@@ -12446,7 +12446,7 @@
         <v>730</v>
       </c>
       <c r="E221" s="1">
-        <v>100933077</v>
+        <v>1912000</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>756</v>
@@ -12455,13 +12455,13 @@
         <v>753</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="K221" s="1" t="s">
         <v>19</v>
@@ -12698,7 +12698,7 @@
         <v>688</v>
       </c>
       <c r="E228" s="1">
-        <v>337800</v>
+        <v>3160500</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>778</v>
@@ -12734,7 +12734,7 @@
         <v>688</v>
       </c>
       <c r="E229" s="1">
-        <v>3160500</v>
+        <v>337800</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>781</v>
@@ -13202,7 +13202,7 @@
         <v>811</v>
       </c>
       <c r="E242" s="1">
-        <v>177618600</v>
+        <v>200371400</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>828</v>
@@ -13211,7 +13211,7 @@
         <v>829</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>78</v>
@@ -13274,7 +13274,7 @@
         <v>811</v>
       </c>
       <c r="E244" s="1">
-        <v>200371400</v>
+        <v>688714100</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>835</v>
@@ -13283,7 +13283,7 @@
         <v>829</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>78</v>
@@ -13310,7 +13310,7 @@
         <v>811</v>
       </c>
       <c r="E245" s="1">
-        <v>688714100</v>
+        <v>177618600</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>838</v>
@@ -13526,7 +13526,7 @@
         <v>853</v>
       </c>
       <c r="E251" s="1">
-        <v>845082696</v>
+        <v>158436845</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>857</v>
@@ -13562,7 +13562,7 @@
         <v>853</v>
       </c>
       <c r="E252" s="1">
-        <v>158436845</v>
+        <v>845082696</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>860</v>
@@ -13634,7 +13634,7 @@
         <v>853</v>
       </c>
       <c r="E254" s="1">
-        <v>1055833082</v>
+        <v>99929015</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>866</v>
@@ -13670,7 +13670,7 @@
         <v>853</v>
       </c>
       <c r="E255" s="1">
-        <v>99929015</v>
+        <v>1055833082</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>869</v>
@@ -13958,7 +13958,7 @@
         <v>885</v>
       </c>
       <c r="E263" s="1">
-        <v>90092300</v>
+        <v>24294250</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>895</v>
@@ -14066,7 +14066,7 @@
         <v>885</v>
       </c>
       <c r="E266" s="1">
-        <v>24294250</v>
+        <v>90092300</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>904</v>
@@ -14462,7 +14462,7 @@
         <v>937</v>
       </c>
       <c r="E277" s="1">
-        <v>2548731</v>
+        <v>258570562</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>944</v>
@@ -14534,7 +14534,7 @@
         <v>937</v>
       </c>
       <c r="E279" s="1">
-        <v>258570562</v>
+        <v>2548731</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>950</v>
@@ -14606,7 +14606,7 @@
         <v>937</v>
       </c>
       <c r="E281" s="1">
-        <v>200371400</v>
+        <v>177359200</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>956</v>
@@ -14615,7 +14615,7 @@
         <v>957</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>78</v>
@@ -14642,7 +14642,7 @@
         <v>937</v>
       </c>
       <c r="E282" s="1">
-        <v>149250700</v>
+        <v>689018800</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>960</v>
@@ -14651,7 +14651,7 @@
         <v>957</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>78</v>
@@ -14678,7 +14678,7 @@
         <v>937</v>
       </c>
       <c r="E283" s="1">
-        <v>689018800</v>
+        <v>200371400</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>963</v>
@@ -14687,7 +14687,7 @@
         <v>957</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>78</v>
@@ -14714,7 +14714,7 @@
         <v>937</v>
       </c>
       <c r="E284" s="1">
-        <v>177359200</v>
+        <v>149250700</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>966</v>
@@ -14723,7 +14723,7 @@
         <v>957</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>78</v>
@@ -15326,7 +15326,7 @@
         <v>1010</v>
       </c>
       <c r="E301" s="1">
-        <v>703000</v>
+        <v>667850</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>1024</v>
@@ -15362,7 +15362,7 @@
         <v>1010</v>
       </c>
       <c r="E302" s="1">
-        <v>667850</v>
+        <v>287324950</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>1027</v>
@@ -15371,7 +15371,7 @@
         <v>1015</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>16</v>
+        <v>929</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>17</v>
@@ -15398,7 +15398,7 @@
         <v>1010</v>
       </c>
       <c r="E303" s="1">
-        <v>287324950</v>
+        <v>703000</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>1030</v>
@@ -15407,7 +15407,7 @@
         <v>1015</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>929</v>
+        <v>16</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>17</v>
@@ -15578,7 +15578,7 @@
         <v>1015</v>
       </c>
       <c r="E308" s="1">
-        <v>960197300</v>
+        <v>267194900</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>1048</v>
@@ -15587,7 +15587,7 @@
         <v>1044</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>78</v>
@@ -15614,7 +15614,7 @@
         <v>1015</v>
       </c>
       <c r="E309" s="1">
-        <v>267194900</v>
+        <v>960197300</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>1051</v>
@@ -15623,7 +15623,7 @@
         <v>1044</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>933</v>
+        <v>1045</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>78</v>
@@ -15650,7 +15650,7 @@
         <v>1015</v>
       </c>
       <c r="E310" s="1">
-        <v>4313300</v>
+        <v>762330900</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>1054</v>
@@ -15686,7 +15686,7 @@
         <v>1015</v>
       </c>
       <c r="E311" s="1">
-        <v>193894600</v>
+        <v>4313300</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>1057</v>
@@ -15722,7 +15722,7 @@
         <v>1015</v>
       </c>
       <c r="E312" s="1">
-        <v>762330900</v>
+        <v>63500000</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>1060</v>
@@ -15731,7 +15731,7 @@
         <v>1044</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>1045</v>
+        <v>995</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>78</v>
@@ -15758,7 +15758,7 @@
         <v>1015</v>
       </c>
       <c r="E313" s="1">
-        <v>63500000</v>
+        <v>151924700</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>1063</v>
@@ -15767,7 +15767,7 @@
         <v>1044</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>995</v>
+        <v>933</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>78</v>
@@ -15794,7 +15794,7 @@
         <v>1015</v>
       </c>
       <c r="E314" s="1">
-        <v>204133200</v>
+        <v>193894600</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>1066</v>
@@ -15803,7 +15803,7 @@
         <v>1044</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>933</v>
+        <v>1045</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>78</v>
@@ -15830,7 +15830,7 @@
         <v>1015</v>
       </c>
       <c r="E315" s="1">
-        <v>151924700</v>
+        <v>204133200</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>1069</v>
@@ -16046,7 +16046,7 @@
         <v>1072</v>
       </c>
       <c r="E321" s="1">
-        <v>1067934069</v>
+        <v>5246000</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>1088</v>
@@ -16055,13 +16055,13 @@
         <v>957</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>135</v>
+        <v>1089</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="K321" s="1" t="s">
         <v>19</v>
@@ -16073,7 +16073,7 @@
         <v>319</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>1072</v>
@@ -16082,16 +16082,16 @@
         <v>1072</v>
       </c>
       <c r="E322" s="1">
-        <v>5246000</v>
+        <v>1067934069</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>957</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>1092</v>
+        <v>135</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>17</v>
@@ -16118,7 +16118,7 @@
         <v>1072</v>
       </c>
       <c r="E323" s="1">
-        <v>25170300</v>
+        <v>94750900</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>1095</v>
@@ -16190,7 +16190,7 @@
         <v>1072</v>
       </c>
       <c r="E325" s="1">
-        <v>94750900</v>
+        <v>25170300</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>1101</v>
@@ -16298,7 +16298,7 @@
         <v>1072</v>
       </c>
       <c r="E328" s="1">
-        <v>279548291</v>
+        <v>44072100</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>1110</v>
@@ -16307,7 +16307,7 @@
         <v>957</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>17</v>
@@ -16334,7 +16334,7 @@
         <v>1072</v>
       </c>
       <c r="E329" s="1">
-        <v>44072100</v>
+        <v>279548291</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>1113</v>
@@ -16343,7 +16343,7 @@
         <v>957</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>17</v>
@@ -16523,7 +16523,7 @@
         <v>1121</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>17</v>
@@ -16766,7 +16766,7 @@
         <v>1154</v>
       </c>
       <c r="E341" s="1">
-        <v>279584469</v>
+        <v>116066650</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>1155</v>
@@ -16775,7 +16775,7 @@
         <v>1153</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>17</v>
@@ -16838,7 +16838,7 @@
         <v>1154</v>
       </c>
       <c r="E343" s="1">
-        <v>41365850</v>
+        <v>279584469</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>1161</v>
@@ -16847,7 +16847,7 @@
         <v>1153</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>17</v>
@@ -16874,7 +16874,7 @@
         <v>1154</v>
       </c>
       <c r="E344" s="1">
-        <v>116066650</v>
+        <v>41365850</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>1164</v>
@@ -16883,7 +16883,7 @@
         <v>1153</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>17</v>
@@ -17054,22 +17054,22 @@
         <v>1168</v>
       </c>
       <c r="E349" s="1">
-        <v>149250700</v>
+        <v>177151200</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>1183</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J349" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K349" s="1" t="s">
         <v>19</v>
@@ -17081,7 +17081,7 @@
         <v>347</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>1170</v>
@@ -17090,16 +17090,16 @@
         <v>1168</v>
       </c>
       <c r="E350" s="1">
-        <v>689692300</v>
+        <v>149250700</v>
       </c>
       <c r="F350" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G350" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="G350" s="1" t="s">
-        <v>1180</v>
-      </c>
       <c r="H350" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>78</v>
@@ -17162,22 +17162,22 @@
         <v>1168</v>
       </c>
       <c r="E352" s="1">
-        <v>177151200</v>
+        <v>62679696</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>1193</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J352" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="K352" s="1" t="s">
         <v>19</v>
@@ -17189,7 +17189,7 @@
         <v>350</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>1170</v>
@@ -17198,16 +17198,16 @@
         <v>1168</v>
       </c>
       <c r="E353" s="1">
-        <v>62679696</v>
+        <v>689692300</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1197</v>
+        <v>1180</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>78</v>
@@ -17240,7 +17240,7 @@
         <v>1200</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="H354" s="1" t="s">
         <v>101</v>
@@ -17267,7 +17267,7 @@
         <v>1203</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="E355" s="1">
         <v>258570562</v>
@@ -17303,7 +17303,7 @@
         <v>1180</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E356" s="1">
         <v>837896759</v>
@@ -17339,10 +17339,10 @@
         <v>1180</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E357" s="1">
-        <v>158575478</v>
+        <v>213243288</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>1210</v>
@@ -17375,10 +17375,10 @@
         <v>1180</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E358" s="1">
-        <v>213243288</v>
+        <v>158575478</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>1213</v>
@@ -17414,7 +17414,7 @@
         <v>1180</v>
       </c>
       <c r="E359" s="1">
-        <v>24034050</v>
+        <v>22608400</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>1217</v>
@@ -17423,7 +17423,7 @@
         <v>1218</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>17</v>
@@ -17450,7 +17450,7 @@
         <v>1180</v>
       </c>
       <c r="E360" s="1">
-        <v>22608400</v>
+        <v>24034050</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>1221</v>
@@ -17459,7 +17459,7 @@
         <v>1218</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>17</v>
@@ -17522,16 +17522,16 @@
         <v>1180</v>
       </c>
       <c r="E362" s="1">
-        <v>33188550</v>
+        <v>89459600</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>1228</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>17</v>
@@ -17558,16 +17558,16 @@
         <v>1180</v>
       </c>
       <c r="E363" s="1">
-        <v>89459600</v>
+        <v>33188550</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>1231</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>17</v>
@@ -17699,7 +17699,7 @@
         <v>1242</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E367" s="1">
         <v>60825925</v>
@@ -17735,7 +17735,7 @@
         <v>1242</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="E368" s="1">
         <v>2844264</v>
@@ -17774,7 +17774,7 @@
         <v>1242</v>
       </c>
       <c r="E369" s="1">
-        <v>12740000</v>
+        <v>34511892</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>1250</v>
@@ -17810,7 +17810,7 @@
         <v>1242</v>
       </c>
       <c r="E370" s="1">
-        <v>34511892</v>
+        <v>12740000</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>1253</v>
@@ -18206,7 +18206,7 @@
         <v>1289</v>
       </c>
       <c r="E381" s="1">
-        <v>161741108</v>
+        <v>3915950</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>1293</v>
@@ -18242,7 +18242,7 @@
         <v>1289</v>
       </c>
       <c r="E382" s="1">
-        <v>3915950</v>
+        <v>161741108</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>1296</v>
@@ -18314,7 +18314,7 @@
         <v>1284</v>
       </c>
       <c r="E384" s="1">
-        <v>3915950</v>
+        <v>679200</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>1302</v>
@@ -18323,7 +18323,7 @@
         <v>1288</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>135</v>
+        <v>803</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>17</v>
@@ -18350,7 +18350,7 @@
         <v>1284</v>
       </c>
       <c r="E385" s="1">
-        <v>679200</v>
+        <v>3915950</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>1305</v>
@@ -18359,7 +18359,7 @@
         <v>1288</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>803</v>
+        <v>135</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>17</v>
@@ -18422,7 +18422,7 @@
         <v>1312</v>
       </c>
       <c r="E387" s="1">
-        <v>4759600</v>
+        <v>346500</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>1313</v>
@@ -18431,7 +18431,7 @@
         <v>1308</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>1092</v>
+        <v>42</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>17</v>
@@ -18458,7 +18458,7 @@
         <v>1312</v>
       </c>
       <c r="E388" s="1">
-        <v>346500</v>
+        <v>4759600</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>1316</v>
@@ -18467,7 +18467,7 @@
         <v>1308</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>42</v>
+        <v>1089</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>17</v>
@@ -18566,22 +18566,22 @@
         <v>1289</v>
       </c>
       <c r="E391" s="1">
-        <v>694524200</v>
+        <v>199981800</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>1327</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>78</v>
       </c>
       <c r="J391" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="K391" s="1" t="s">
         <v>19</v>
@@ -18593,7 +18593,7 @@
         <v>389</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>1322</v>
@@ -18605,10 +18605,10 @@
         <v>176866300</v>
       </c>
       <c r="F392" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G392" s="1" t="s">
         <v>1331</v>
-      </c>
-      <c r="G392" s="1" t="s">
-        <v>1328</v>
       </c>
       <c r="H392" s="1" t="s">
         <v>97</v>
@@ -18638,16 +18638,16 @@
         <v>1289</v>
       </c>
       <c r="E393" s="1">
-        <v>199981800</v>
+        <v>694524200</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>1334</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>78</v>
@@ -18680,7 +18680,7 @@
         <v>1337</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="H394" s="1" t="s">
         <v>97</v>
@@ -18752,7 +18752,7 @@
         <v>1343</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="H396" s="1" t="s">
         <v>97</v>
@@ -18788,7 +18788,7 @@
         <v>1348</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="H397" s="1" t="s">
         <v>17</v>
@@ -18818,7 +18818,7 @@
         <v>1352</v>
       </c>
       <c r="E398" s="1">
-        <v>4759600</v>
+        <v>120000000</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>1353</v>
@@ -18827,13 +18827,13 @@
         <v>1351</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>1092</v>
+        <v>1354</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J398" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K398" s="1" t="s">
         <v>19</v>
@@ -18845,7 +18845,7 @@
         <v>396</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>1351</v>
@@ -18854,16 +18854,16 @@
         <v>1352</v>
       </c>
       <c r="E399" s="1">
-        <v>120000000</v>
+        <v>4759600</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>1357</v>
+        <v>1089</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>17</v>

--- a/Database/DAFTAR SP2D SATKER.xlsx
+++ b/Database/DAFTAR SP2D SATKER.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. SEMPUR\Realisasi_SAKTI\TA2025\Database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ACC7CFB-FCA1-481A-8FB8-476643FE3923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1487">
   <si>
     <t>DAFTAR SP2D SATKER</t>
   </si>
@@ -1714,18 +1709,27 @@
     <t>00288T/403829/2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530018166</t>
+  </si>
+  <si>
+    <t>25-06-2025</t>
+  </si>
+  <si>
+    <t>00270T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530018167</t>
   </si>
   <si>
-    <t>25-06-2025</t>
-  </si>
-  <si>
     <t>00271T/403829/2025</t>
   </si>
   <si>
-    <t>11-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 135 Pegawai/396 jiwa</t>
   </si>
   <si>
@@ -1747,15 +1751,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 35 Pegawai/101 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530018166</t>
-  </si>
-  <si>
-    <t>00270T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310116799</t>
   </si>
   <si>
@@ -1780,6 +1775,15 @@
     <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991530011368</t>
+  </si>
+  <si>
+    <t>00286T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 103 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991530011369</t>
   </si>
   <si>
@@ -1789,13 +1793,34 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 16 Pegawai.Sesuai Sk No. B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991530011368</t>
-  </si>
-  <si>
-    <t>00286T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 103 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
+    <t xml:space="preserve"> 259991531001947</t>
+  </si>
+  <si>
+    <t>00282T/403829/2025</t>
+  </si>
+  <si>
+    <t>19-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001949</t>
+  </si>
+  <si>
+    <t>00268T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991531001948</t>
+  </si>
+  <si>
+    <t>00266T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 63 Pegawai/181 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 259991531001971</t>
@@ -1807,36 +1832,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Juni Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991531001949</t>
-  </si>
-  <si>
-    <t>00268T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 23 Pegawai/52 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001947</t>
-  </si>
-  <si>
-    <t>00282T/403829/2025</t>
-  </si>
-  <si>
-    <t>19-06-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juli 2025 untuk 173 Pegawai/538 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991531001948</t>
-  </si>
-  <si>
-    <t>00266T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juli 2025 untuk 63 Pegawai/181 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991525004591</t>
   </si>
   <si>
@@ -1858,39 +1853,39 @@
     <t>Penjualan Belanja Pegawai berupa Kekurangan Gaji Bulan Januari 2025 untuk 1 Pegawai/3 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310059126</t>
+  </si>
+  <si>
+    <t>13-06-2025</t>
+  </si>
+  <si>
+    <t>16-06-2025</t>
+  </si>
+  <si>
+    <t>00280T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310059124</t>
+  </si>
+  <si>
+    <t>00275T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 137 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310059125</t>
   </si>
   <si>
-    <t>13-06-2025</t>
-  </si>
-  <si>
-    <t>16-06-2025</t>
-  </si>
-  <si>
     <t>00277T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310059126</t>
-  </si>
-  <si>
-    <t>00280T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Mei tahun 2025 untuk 35 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310059124</t>
-  </si>
-  <si>
-    <t>00275T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja  bulan Mei tahun 2025 untuk 137 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330013161</t>
   </si>
   <si>
@@ -1930,18 +1925,18 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Mei 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310050294</t>
+  </si>
+  <si>
+    <t>00273T/403829/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310050295</t>
   </si>
   <si>
     <t>00274T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310050294</t>
-  </si>
-  <si>
-    <t>00273T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310039873</t>
   </si>
   <si>
@@ -1981,36 +1976,36 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 11 Pegawai/41 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310036822</t>
+  </si>
+  <si>
+    <t>00256T/403829/2025</t>
+  </si>
+  <si>
+    <t>05-06-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 38 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 259991310036825</t>
+  </si>
+  <si>
+    <t>00257T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 136 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310036823</t>
   </si>
   <si>
     <t>00252T/403829/2025</t>
   </si>
   <si>
-    <t>05-06-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan April 2025 sd Mei 2025 untuk 2 Pegawai/5 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310036822</t>
-  </si>
-  <si>
-    <t>00256T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 38 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 259991310036825</t>
-  </si>
-  <si>
-    <t>00257T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 136 jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991310036824</t>
   </si>
   <si>
@@ -2020,6 +2015,15 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji bulan Mei 2025 untuk 2 pegawai/ 4 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991330008177</t>
+  </si>
+  <si>
+    <t>00255T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Februari 2025 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991330008175</t>
   </si>
   <si>
@@ -2038,15 +2042,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 171 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991330008177</t>
-  </si>
-  <si>
-    <t>00255T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Februari 2025 untuk 1 Pegawai/4 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991305011756</t>
   </si>
   <si>
@@ -2056,6 +2051,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Mei 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 259991310033061</t>
+  </si>
+  <si>
+    <t>00250T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 259991310033060</t>
   </si>
   <si>
@@ -2065,15 +2069,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 259991310033061</t>
-  </si>
-  <si>
-    <t>00250T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Mei 2025 untuk 34 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 259991330007277</t>
   </si>
   <si>
@@ -2155,6 +2150,15 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 137 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301006634</t>
+  </si>
+  <si>
+    <t>00241T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 35 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301006633</t>
   </si>
   <si>
@@ -2164,13 +2168,22 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301006634</t>
-  </si>
-  <si>
-    <t>00241T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 35 Pegawai</t>
+    <t xml:space="preserve"> 250231303002006</t>
+  </si>
+  <si>
+    <t>00238T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 173 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303002007</t>
+  </si>
+  <si>
+    <t>00240T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303002008</t>
@@ -2182,24 +2195,6 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303002007</t>
-  </si>
-  <si>
-    <t>00240T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303002006</t>
-  </si>
-  <si>
-    <t>00238T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 173 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000975</t>
   </si>
   <si>
@@ -2212,39 +2207,39 @@
     <t>Pembayaran Tukin ke-13 Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001414</t>
+  </si>
+  <si>
+    <t>26-05-2025</t>
+  </si>
+  <si>
+    <t>00234T/403829/2025</t>
+  </si>
+  <si>
+    <t>SPM Gaji 13 PPPK</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 35 PPPK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001413</t>
+  </si>
+  <si>
+    <t>00232T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 50 PPPK.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001439</t>
   </si>
   <si>
-    <t>26-05-2025</t>
-  </si>
-  <si>
     <t>00228T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 137 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001414</t>
-  </si>
-  <si>
-    <t>00234T/403829/2025</t>
-  </si>
-  <si>
-    <t>SPM Gaji 13 PPPK</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 35 PPPK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501001413</t>
-  </si>
-  <si>
-    <t>00232T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 50 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000406</t>
   </si>
   <si>
@@ -2263,6 +2258,15 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 23 PPPK.</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000383</t>
+  </si>
+  <si>
+    <t>00233T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 63 PPPK.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000382</t>
   </si>
   <si>
@@ -2272,15 +2276,6 @@
     <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 173 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000383</t>
-  </si>
-  <si>
-    <t>00233T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Gaji ke-13 Tahun 2025 Untuk 63 PPPK.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000959</t>
   </si>
   <si>
@@ -2302,27 +2297,27 @@
     <t>Pembayaran tunjangan kinerja bulan Juni tahun 2025 untuk 39 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001344</t>
+  </si>
+  <si>
+    <t>22-05-2025</t>
+  </si>
+  <si>
+    <t>00224T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 103 Pegawai.sesuai Sk No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001339</t>
   </si>
   <si>
-    <t>22-05-2025</t>
-  </si>
-  <si>
     <t>00223T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001344</t>
-  </si>
-  <si>
-    <t>00224T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 103 Pegawai.sesuai Sk No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000370</t>
   </si>
   <si>
@@ -2332,42 +2327,42 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Mei Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000351</t>
+  </si>
+  <si>
+    <t>21-05-2025</t>
+  </si>
+  <si>
+    <t>00202T/403829/2025</t>
+  </si>
+  <si>
+    <t>08-05-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji induk PPPK Bulan Juni 2025 untuk 63 Pegawai/181 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231503000350</t>
+  </si>
+  <si>
+    <t>00207T/403829/2025</t>
+  </si>
+  <si>
+    <t>09-05-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 173 Pegawai/536 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000352</t>
   </si>
   <si>
-    <t>21-05-2025</t>
-  </si>
-  <si>
     <t>00204T/403829/2025</t>
   </si>
   <si>
-    <t>08-05-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 23 Pegawai/52 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000351</t>
-  </si>
-  <si>
-    <t>00202T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji induk PPPK Bulan Juni 2025 untuk 63 Pegawai/181 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231503000350</t>
-  </si>
-  <si>
-    <t>00207T/403829/2025</t>
-  </si>
-  <si>
-    <t>09-05-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 173 Pegawai/536 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000342</t>
   </si>
   <si>
@@ -2377,6 +2372,15 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 2 Pegawai/8 jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001201</t>
+  </si>
+  <si>
+    <t>00205T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001209</t>
   </si>
   <si>
@@ -2386,15 +2390,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Juni 2025 untuk 35 Pegawai/101 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001201</t>
-  </si>
-  <si>
-    <t>00205T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa  Gaji Induk Bulan Juni 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501001208</t>
   </si>
   <si>
@@ -2413,25 +2408,34 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Juni 2025 untuk 135 Pegawai/ 396 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303001771</t>
+  </si>
+  <si>
+    <t>20-05-2025</t>
+  </si>
+  <si>
+    <t>00222T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303001770</t>
   </si>
   <si>
-    <t>20-05-2025</t>
-  </si>
-  <si>
     <t>00219T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai Berupa Uang Makan PPPK Bulan April 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001771</t>
-  </si>
-  <si>
-    <t>00222T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 63 Pegawai</t>
+    <t xml:space="preserve"> 250231303001765</t>
+  </si>
+  <si>
+    <t>00220T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan April 2025 untuk 23 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303001766</t>
@@ -2443,15 +2447,6 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001765</t>
-  </si>
-  <si>
-    <t>00220T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan April 2025 untuk 23 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301006005</t>
   </si>
   <si>
@@ -2533,21 +2528,21 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025  untuk 135 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301005582</t>
+  </si>
+  <si>
+    <t>14-05-2025</t>
+  </si>
+  <si>
+    <t>00210T/403829/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301005583</t>
   </si>
   <si>
-    <t>14-05-2025</t>
-  </si>
-  <si>
     <t>00209T/403829/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005582</t>
-  </si>
-  <si>
-    <t>00210T/403829/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302005378</t>
   </si>
   <si>
@@ -2578,6 +2573,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301005291</t>
+  </si>
+  <si>
+    <t>00197T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301005293</t>
   </si>
   <si>
@@ -2596,15 +2600,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan April 2025 untuk 49 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301005291</t>
-  </si>
-  <si>
-    <t>00197T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan April 2025 untuk 38 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302005131</t>
   </si>
   <si>
@@ -2758,27 +2753,36 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan April Tahun 2025 untuk 91 Pegawai.sesuai Sk No.9 Tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501001059</t>
+  </si>
+  <si>
+    <t>00153T/403829/2025</t>
+  </si>
+  <si>
+    <t>10-04-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501001051</t>
+  </si>
+  <si>
+    <t>00158T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 39 Pegawai/111 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501001057</t>
   </si>
   <si>
     <t>00156T/403829/2025</t>
   </si>
   <si>
-    <t>10-04-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 50 Pegawai/124 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001059</t>
-  </si>
-  <si>
-    <t>00153T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 36 Pegawai/105 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501001058</t>
   </si>
   <si>
@@ -2788,15 +2792,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 137 Pegawai/401 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501001051</t>
-  </si>
-  <si>
-    <t>00158T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 39 Pegawai/111 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000303</t>
   </si>
   <si>
@@ -2806,6 +2801,24 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 2 Pegawai/8 jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000275</t>
+  </si>
+  <si>
+    <t>00154T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPk Bulan Mei 2025 untuk 23 Pegawai/52 Jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231503000273</t>
+  </si>
+  <si>
+    <t>00160T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 173 Pegawai/535 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000274</t>
   </si>
   <si>
@@ -2815,24 +2828,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Mei 2025 untuk 63 Pegawai/181 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000275</t>
-  </si>
-  <si>
-    <t>00154T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPk Bulan Mei 2025 untuk 23 Pegawai/52 Jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231503000273</t>
-  </si>
-  <si>
-    <t>00160T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Mei 2025 untuk 173 Pegawai/535 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303001237</t>
   </si>
   <si>
@@ -2845,6 +2840,24 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 63 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301004024</t>
+  </si>
+  <si>
+    <t>00176T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 138 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231301004025</t>
+  </si>
+  <si>
+    <t>00174T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301004026</t>
   </si>
   <si>
@@ -2854,22 +2867,13 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301004024</t>
-  </si>
-  <si>
-    <t>00176T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 138 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301004025</t>
-  </si>
-  <si>
-    <t>00174T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 50 Pegawai</t>
+    <t xml:space="preserve"> 250231303001235</t>
+  </si>
+  <si>
+    <t>00177T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 175 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303001236</t>
@@ -2881,15 +2885,6 @@
     <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001235</t>
-  </si>
-  <si>
-    <t>00177T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Maret tahun 2025 untuk 175 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302003921</t>
   </si>
   <si>
@@ -2959,6 +2954,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301003744</t>
+  </si>
+  <si>
+    <t>00163T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301003743</t>
   </si>
   <si>
@@ -2968,13 +2972,13 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 38 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301003744</t>
-  </si>
-  <si>
-    <t>00163T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 49 Pegawai</t>
+    <t xml:space="preserve"> 250231301003745</t>
+  </si>
+  <si>
+    <t>00168T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 136 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301003746</t>
@@ -2986,13 +2990,22 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 36 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301003745</t>
-  </si>
-  <si>
-    <t>00168T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 136 Pegawai</t>
+    <t xml:space="preserve"> 250231303001156</t>
+  </si>
+  <si>
+    <t>00169T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 172 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303001157</t>
+  </si>
+  <si>
+    <t>00164T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 63 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303001158</t>
@@ -3004,24 +3017,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 23 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303001156</t>
-  </si>
-  <si>
-    <t>00169T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Maret 2025 untuk 172 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303001157</t>
-  </si>
-  <si>
-    <t>00164T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Maret 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302003522</t>
   </si>
   <si>
@@ -3106,6 +3101,15 @@
     <t>Pembayaran tunjangan kinerja bulan April tahun 2025 untuk 39 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000906</t>
+  </si>
+  <si>
+    <t>00146T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 1 Pegawai.sesuai SK No. 9 Tahun 2025 tanggal 6 Januari 2025</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000907</t>
   </si>
   <si>
@@ -3124,15 +3128,6 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 16 Pegawai.sesuai Sk No.B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000906</t>
-  </si>
-  <si>
-    <t>00146T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 1 Pegawai.sesuai SK No. 9 Tahun 2025 tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000261</t>
   </si>
   <si>
@@ -3142,15 +3137,24 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Maret Tahun 2025 untuk 91 Pegawai.Sesuai Sk No.9 tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000781</t>
+  </si>
+  <si>
+    <t>00092T/403829/2025</t>
+  </si>
+  <si>
+    <t>11-03-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 50 Pegawai/124 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000765</t>
   </si>
   <si>
     <t>00090T/403829/2025</t>
   </si>
   <si>
-    <t>11-03-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 39 Pegawai/ 111 Jiwa</t>
   </si>
   <si>
@@ -3163,15 +3167,6 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 137 Pegawai/403 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000781</t>
-  </si>
-  <si>
-    <t>00092T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 50 Pegawai/124 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000767</t>
   </si>
   <si>
@@ -3205,6 +3200,15 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 23 Pegawai/52 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231503000255</t>
+  </si>
+  <si>
+    <t>00093T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 63 Pegawai/181 jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231503000254</t>
   </si>
   <si>
@@ -3217,36 +3221,27 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan April 2025 untuk 173 Pegawai/536 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231503000255</t>
-  </si>
-  <si>
-    <t>00093T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan April 2025 untuk 63 Pegawai/181 jiwa</t>
+    <t xml:space="preserve"> 250231301003008</t>
+  </si>
+  <si>
+    <t>20-03-2025</t>
+  </si>
+  <si>
+    <t>00138T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 1 Pegawai.sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301003009</t>
   </si>
   <si>
-    <t>20-03-2025</t>
-  </si>
-  <si>
     <t>00139T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 102 Pegawai.sesuai SK No 9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301003008</t>
-  </si>
-  <si>
-    <t>00138T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 1 Pegawai.sesuai Sk No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000979</t>
   </si>
   <si>
@@ -3256,27 +3251,27 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 91 Pegawai.sesuai SK No.9 Tahun 2025 Tanggal 6 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000752</t>
+  </si>
+  <si>
+    <t>00142T/403829/2025</t>
+  </si>
+  <si>
+    <t>SPM THR PPNPN</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 102 Pegawai.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000753</t>
   </si>
   <si>
     <t>00141T/403829/2025</t>
   </si>
   <si>
-    <t>SPM THR PPNPN</t>
-  </si>
-  <si>
     <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 1 Pegawai.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000752</t>
-  </si>
-  <si>
-    <t>00142T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 102 Pegawai.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231503000215</t>
   </si>
   <si>
@@ -3343,6 +3338,24 @@
     <t>Pembayaran THR Tunkin Tahun 2025 Untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000889</t>
+  </si>
+  <si>
+    <t>00129T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan februari 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000887</t>
+  </si>
+  <si>
+    <t>00126T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tunkin Tahun 2025 Untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000888</t>
   </si>
   <si>
@@ -3352,24 +3365,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000887</t>
-  </si>
-  <si>
-    <t>00126T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tunkin Tahun 2025 Untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000889</t>
-  </si>
-  <si>
-    <t>00129T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan februari 2025 untuk 1 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002724</t>
   </si>
   <si>
@@ -3433,6 +3428,33 @@
     <t>Pembayaran THR Tahun 2025 Untuk 177 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000529</t>
+  </si>
+  <si>
+    <t>00118T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000526</t>
+  </si>
+  <si>
+    <t>00113T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 39 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231501000527</t>
+  </si>
+  <si>
+    <t>00114T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 1 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000528</t>
   </si>
   <si>
@@ -3442,13 +3464,13 @@
     <t>Pembayaran THR Tahun 2025 Untuk 139 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000527</t>
-  </si>
-  <si>
-    <t>00114T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 1 Pegawai</t>
+    <t xml:space="preserve"> 250231501000530</t>
+  </si>
+  <si>
+    <t>00120T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran THR Tahun 2025 Untuk 36 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231501000545</t>
@@ -3460,33 +3482,6 @@
     <t>Pembayaran THR Keagamaan Tahun 2025 Untuk 16 Pegawai.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000530</t>
-  </si>
-  <si>
-    <t>00120T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 36 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000526</t>
-  </si>
-  <si>
-    <t>00113T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 39 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231501000529</t>
-  </si>
-  <si>
-    <t>00118T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran THR Tahun 2025 Untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302002452</t>
   </si>
   <si>
@@ -3508,6 +3503,15 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Februari 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301002383</t>
+  </si>
+  <si>
+    <t>00109T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 139 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301002384</t>
   </si>
   <si>
@@ -3517,13 +3521,25 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 49 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301002383</t>
-  </si>
-  <si>
-    <t>00109T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 139 Pegawai</t>
+    <t xml:space="preserve"> 250231303000777</t>
+  </si>
+  <si>
+    <t>00096T/403829/2025</t>
+  </si>
+  <si>
+    <t>GAJI SUSULAN</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Maret 2025 untuk 1 Pegawai/4 jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000778</t>
+  </si>
+  <si>
+    <t>00110T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 177 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303000776</t>
@@ -3535,27 +3551,6 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000777</t>
-  </si>
-  <si>
-    <t>00096T/403829/2025</t>
-  </si>
-  <si>
-    <t>GAJI SUSULAN</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Maret 2025 untuk 1 Pegawai/4 jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000778</t>
-  </si>
-  <si>
-    <t>00110T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 177 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002369</t>
   </si>
   <si>
@@ -3574,6 +3569,15 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 36 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301002371</t>
+  </si>
+  <si>
+    <t>00104T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301002370</t>
   </si>
   <si>
@@ -3583,15 +3587,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Februari 2025 untuk 37 pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301002371</t>
-  </si>
-  <si>
-    <t>00104T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 50 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002373</t>
   </si>
   <si>
@@ -3601,6 +3596,24 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Februari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000772</t>
+  </si>
+  <si>
+    <t>00102T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa uang Makan Bulan februari 2025 untuk 174 pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000774</t>
+  </si>
+  <si>
+    <t>00105T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000773</t>
   </si>
   <si>
@@ -3610,24 +3623,6 @@
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan februari 2025 untuk 63 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000774</t>
-  </si>
-  <si>
-    <t>00105T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000772</t>
-  </si>
-  <si>
-    <t>00102T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa uang Makan Bulan februari 2025 untuk 174 pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231301002328</t>
   </si>
   <si>
@@ -3730,15 +3725,33 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 90 Pegawai.sesuai Sk no.9 tahun 2025 tanggal 6 januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231303000475</t>
+  </si>
+  <si>
+    <t>25-02-2025</t>
+  </si>
+  <si>
+    <t>26-02-2025</t>
+  </si>
+  <si>
+    <t>00076T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 250231303000474</t>
+  </si>
+  <si>
+    <t>00074T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan Januari 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231303000473</t>
   </si>
   <si>
-    <t>25-02-2025</t>
-  </si>
-  <si>
-    <t>26-02-2025</t>
-  </si>
-  <si>
     <t>00073T/403829/2025</t>
   </si>
   <si>
@@ -3754,24 +3767,6 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 177 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231303000475</t>
-  </si>
-  <si>
-    <t>00076T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231303000474</t>
-  </si>
-  <si>
-    <t>00074T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan Januari 2025 untuk 63 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000180</t>
   </si>
   <si>
@@ -3820,6 +3815,18 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 2 Pegawai /8 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000434</t>
+  </si>
+  <si>
+    <t>00067T/403829/2025</t>
+  </si>
+  <si>
+    <t>18-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 36 Pegawai/106 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000431</t>
   </si>
   <si>
@@ -3829,16 +3836,16 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 39 Pegawai/112 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000434</t>
-  </si>
-  <si>
-    <t>00067T/403829/2025</t>
-  </si>
-  <si>
-    <t>18-02-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Maret 2025 untuk 36 Pegawai/106 Jiwa</t>
+    <t xml:space="preserve"> 250231501000339</t>
+  </si>
+  <si>
+    <t>00069T/403829/2025</t>
+  </si>
+  <si>
+    <t>20-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 16 Pegawai.sesuai SK No.04/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231501000433</t>
@@ -3850,18 +3857,6 @@
     <t>Pembayaran Belanja Pegawai Berupa Gaji Induk Maret 2025 untuk 50 Pegawai/123 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000339</t>
-  </si>
-  <si>
-    <t>00069T/403829/2025</t>
-  </si>
-  <si>
-    <t>20-02-2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Februari Tahun 2025 untuk 16 Pegawai.sesuai SK No.04/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231501000432</t>
   </si>
   <si>
@@ -3901,6 +3896,15 @@
     <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 138 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301001113</t>
+  </si>
+  <si>
+    <t>00061T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301001112</t>
   </si>
   <si>
@@ -3910,39 +3914,30 @@
     <t>Pembayaran tunjangan kinerja  bulan Januari tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001113</t>
-  </si>
-  <si>
-    <t>00061T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Januari tahun 2025 untuk 36 Pegawai</t>
+    <t xml:space="preserve"> 250231301001062</t>
+  </si>
+  <si>
+    <t>16-02-2025</t>
+  </si>
+  <si>
+    <t>00051T/403829/2025</t>
+  </si>
+  <si>
+    <t>13-02-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Januari 2025 untuk 36 Pegawai</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231301001061</t>
   </si>
   <si>
-    <t>16-02-2025</t>
-  </si>
-  <si>
     <t>00052T/403829/2025</t>
   </si>
   <si>
-    <t>13-02-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Januari 2025 untuk 37 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301001062</t>
-  </si>
-  <si>
-    <t>00051T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Uang Makan bulan Januari 2025 untuk 36 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231305000122</t>
   </si>
   <si>
@@ -4150,6 +4145,15 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 2 Pegawai</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000432</t>
+  </si>
+  <si>
+    <t>00030T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000433</t>
   </si>
   <si>
@@ -4159,15 +4163,6 @@
     <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 1 Pegawai</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000432</t>
-  </si>
-  <si>
-    <t>00030T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran tunjangan kinerja bulan Februari tahun 2025 untuk 38 Pegawai</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231303000130</t>
   </si>
   <si>
@@ -4207,27 +4202,27 @@
     <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Januari Tahun 2025 untuk 17 Pegawai.sesuai SK No.B.4/BRPBATPP/KP.340/I/2025 tanggal 2 Januari 2025</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000385</t>
+  </si>
+  <si>
+    <t>23-01-2025</t>
+  </si>
+  <si>
+    <t>00025T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000386</t>
   </si>
   <si>
-    <t>23-01-2025</t>
-  </si>
-  <si>
     <t>00026T/403829/2025</t>
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231301000385</t>
-  </si>
-  <si>
-    <t>00025T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2024 untuk 1 Pegawai/4 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231302000370</t>
   </si>
   <si>
@@ -4252,6 +4247,18 @@
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Februari 2025 untuk 36 Pegawai/105 Jiwa</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231501000228</t>
+  </si>
+  <si>
+    <t>00021T/403829/2025</t>
+  </si>
+  <si>
+    <t>14-01-2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 138 Pegawai/406 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231501000229</t>
   </si>
   <si>
@@ -4267,21 +4274,9 @@
     <t>00019T/403829/2025</t>
   </si>
   <si>
-    <t>14-01-2025</t>
-  </si>
-  <si>
     <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 39 Pegawai/112 jiwa</t>
   </si>
   <si>
-    <t xml:space="preserve"> 250231501000228</t>
-  </si>
-  <si>
-    <t>00021T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan februari 2025 untuk 138 Pegawai/406 Jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 250231507000048</t>
   </si>
   <si>
@@ -4324,15 +4319,24 @@
     <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Januari 2025 Idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
   </si>
   <si>
+    <t xml:space="preserve"> 250231301000152</t>
+  </si>
+  <si>
+    <t>10-01-2025</t>
+  </si>
+  <si>
+    <t>13-01-2025</t>
+  </si>
+  <si>
+    <t>00016T/403829/2025</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gai Susulan Bulan Desember 2024 sd Januari 2025 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 250231301000153</t>
   </si>
   <si>
-    <t>10-01-2025</t>
-  </si>
-  <si>
-    <t>13-01-2025</t>
-  </si>
-  <si>
     <t>00017T/403829/2025</t>
   </si>
   <si>
@@ -4340,15 +4344,6 @@
   </si>
   <si>
     <t>Penyediaan Uang Persediaan BALAI RISET PERIKANAN BUDIDAYA AIR TAWAR DAN PENYULUHAN PERIKANAN Tahun Anggaran 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 250231301000152</t>
-  </si>
-  <si>
-    <t>00016T/403829/2025</t>
-  </si>
-  <si>
-    <t>Pembayaran Belanja Pegawai berupa Gai Susulan Bulan Desember 2024 sd Januari 2025 untuk 1 Pegawai/4 Jiwa</t>
   </si>
   <si>
     <t xml:space="preserve"> 250231303000044</t>
@@ -4486,9 +4481,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -4499,44 +4499,37 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -4826,19 +4819,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:L436"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -4876,7 +4872,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -4912,7 +4908,7 @@
       </c>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -4948,7 +4944,7 @@
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -4984,7 +4980,7 @@
       </c>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -5020,7 +5016,7 @@
       </c>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -5056,7 +5052,7 @@
       </c>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -5092,7 +5088,7 @@
       </c>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -5128,7 +5124,7 @@
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -5164,7 +5160,7 @@
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -5200,7 +5196,7 @@
       </c>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -5236,7 +5232,7 @@
       </c>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -5272,7 +5268,7 @@
       </c>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -5308,7 +5304,7 @@
       </c>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -5344,7 +5340,7 @@
       </c>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -5380,7 +5376,7 @@
       </c>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -5416,7 +5412,7 @@
       </c>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -5452,7 +5448,7 @@
       </c>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -5488,7 +5484,7 @@
       </c>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -5524,7 +5520,7 @@
       </c>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -5560,7 +5556,7 @@
       </c>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -5596,7 +5592,7 @@
       </c>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -5632,7 +5628,7 @@
       </c>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -5668,7 +5664,7 @@
       </c>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -5704,7 +5700,7 @@
       </c>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -5740,7 +5736,7 @@
       </c>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -5776,7 +5772,7 @@
       </c>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -5812,7 +5808,7 @@
       </c>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -5848,7 +5844,7 @@
       </c>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -5884,7 +5880,7 @@
       </c>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -5920,7 +5916,7 @@
       </c>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -5956,7 +5952,7 @@
       </c>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -5992,7 +5988,7 @@
       </c>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -6028,7 +6024,7 @@
       </c>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -6064,7 +6060,7 @@
       </c>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -6100,7 +6096,7 @@
       </c>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -6136,7 +6132,7 @@
       </c>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -6172,7 +6168,7 @@
       </c>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -6208,7 +6204,7 @@
       </c>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -6244,7 +6240,7 @@
       </c>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -6280,7 +6276,7 @@
       </c>
       <c r="L42" s="1"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -6316,7 +6312,7 @@
       </c>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -6352,7 +6348,7 @@
       </c>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -6388,7 +6384,7 @@
       </c>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -6424,7 +6420,7 @@
       </c>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -6460,7 +6456,7 @@
       </c>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -6496,7 +6492,7 @@
       </c>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -6532,7 +6528,7 @@
       </c>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -6568,7 +6564,7 @@
       </c>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -6604,7 +6600,7 @@
       </c>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -6640,7 +6636,7 @@
       </c>
       <c r="L52" s="1"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -6676,7 +6672,7 @@
       </c>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -6712,7 +6708,7 @@
       </c>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -6748,7 +6744,7 @@
       </c>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -6784,7 +6780,7 @@
       </c>
       <c r="L56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -6820,7 +6816,7 @@
       </c>
       <c r="L57" s="1"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -6856,7 +6852,7 @@
       </c>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -6892,7 +6888,7 @@
       </c>
       <c r="L59" s="1"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -6928,7 +6924,7 @@
       </c>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -6964,7 +6960,7 @@
       </c>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -7000,7 +6996,7 @@
       </c>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -7036,7 +7032,7 @@
       </c>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -7072,7 +7068,7 @@
       </c>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -7108,7 +7104,7 @@
       </c>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -7144,7 +7140,7 @@
       </c>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -7180,7 +7176,7 @@
       </c>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -7216,7 +7212,7 @@
       </c>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -7252,7 +7248,7 @@
       </c>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -7288,7 +7284,7 @@
       </c>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -7324,7 +7320,7 @@
       </c>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -7360,7 +7356,7 @@
       </c>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -7396,7 +7392,7 @@
       </c>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -7432,7 +7428,7 @@
       </c>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -7468,7 +7464,7 @@
       </c>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -7504,7 +7500,7 @@
       </c>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -7540,7 +7536,7 @@
       </c>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -7576,7 +7572,7 @@
       </c>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -7612,7 +7608,7 @@
       </c>
       <c r="L79" s="1"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -7648,7 +7644,7 @@
       </c>
       <c r="L80" s="1"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -7684,7 +7680,7 @@
       </c>
       <c r="L81" s="1"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -7720,7 +7716,7 @@
       </c>
       <c r="L82" s="1"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -7756,7 +7752,7 @@
       </c>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -7792,7 +7788,7 @@
       </c>
       <c r="L84" s="1"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -7828,7 +7824,7 @@
       </c>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -7864,7 +7860,7 @@
       </c>
       <c r="L86" s="1"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -7900,7 +7896,7 @@
       </c>
       <c r="L87" s="1"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -7936,7 +7932,7 @@
       </c>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -7972,7 +7968,7 @@
       </c>
       <c r="L89" s="1"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -8008,7 +8004,7 @@
       </c>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -8044,7 +8040,7 @@
       </c>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -8080,7 +8076,7 @@
       </c>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -8116,7 +8112,7 @@
       </c>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -8152,7 +8148,7 @@
       </c>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -8188,7 +8184,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -8224,7 +8220,7 @@
       </c>
       <c r="L96" s="1"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -8260,7 +8256,7 @@
       </c>
       <c r="L97" s="1"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -8296,7 +8292,7 @@
       </c>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -8332,7 +8328,7 @@
       </c>
       <c r="L99" s="1"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -8368,7 +8364,7 @@
       </c>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -8404,7 +8400,7 @@
       </c>
       <c r="L101" s="1"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -8440,7 +8436,7 @@
       </c>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -8476,7 +8472,7 @@
       </c>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -8512,7 +8508,7 @@
       </c>
       <c r="L104" s="1"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -8548,7 +8544,7 @@
       </c>
       <c r="L105" s="1"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -8584,7 +8580,7 @@
       </c>
       <c r="L106" s="1"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -8620,7 +8616,7 @@
       </c>
       <c r="L107" s="1"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -8656,7 +8652,7 @@
       </c>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -8692,7 +8688,7 @@
       </c>
       <c r="L109" s="1"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -8728,7 +8724,7 @@
       </c>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -8764,7 +8760,7 @@
       </c>
       <c r="L111" s="1"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -8800,7 +8796,7 @@
       </c>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -8836,7 +8832,7 @@
       </c>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -8872,7 +8868,7 @@
       </c>
       <c r="L114" s="1"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -8908,7 +8904,7 @@
       </c>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -8944,7 +8940,7 @@
       </c>
       <c r="L116" s="1"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -8980,7 +8976,7 @@
       </c>
       <c r="L117" s="1"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -9016,7 +9012,7 @@
       </c>
       <c r="L118" s="1"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -9052,7 +9048,7 @@
       </c>
       <c r="L119" s="1"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -9088,7 +9084,7 @@
       </c>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -9124,7 +9120,7 @@
       </c>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -9160,7 +9156,7 @@
       </c>
       <c r="L122" s="1"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -9196,7 +9192,7 @@
       </c>
       <c r="L123" s="1"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -9232,7 +9228,7 @@
       </c>
       <c r="L124" s="1"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -9268,7 +9264,7 @@
       </c>
       <c r="L125" s="1"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -9304,7 +9300,7 @@
       </c>
       <c r="L126" s="1"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -9340,7 +9336,7 @@
       </c>
       <c r="L127" s="1"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -9376,7 +9372,7 @@
       </c>
       <c r="L128" s="1"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -9412,7 +9408,7 @@
       </c>
       <c r="L129" s="1"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -9448,7 +9444,7 @@
       </c>
       <c r="L130" s="1"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -9484,7 +9480,7 @@
       </c>
       <c r="L131" s="1"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -9520,7 +9516,7 @@
       </c>
       <c r="L132" s="1"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -9556,7 +9552,7 @@
       </c>
       <c r="L133" s="1"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -9592,7 +9588,7 @@
       </c>
       <c r="L134" s="1"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -9628,7 +9624,7 @@
       </c>
       <c r="L135" s="1"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -9664,7 +9660,7 @@
       </c>
       <c r="L136" s="1"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -9700,7 +9696,7 @@
       </c>
       <c r="L137" s="1"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -9736,7 +9732,7 @@
       </c>
       <c r="L138" s="1"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -9772,7 +9768,7 @@
       </c>
       <c r="L139" s="1"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -9808,7 +9804,7 @@
       </c>
       <c r="L140" s="1"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -9844,7 +9840,7 @@
       </c>
       <c r="L141" s="1"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -9880,7 +9876,7 @@
       </c>
       <c r="L142" s="1"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -9916,7 +9912,7 @@
       </c>
       <c r="L143" s="1"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -9952,7 +9948,7 @@
       </c>
       <c r="L144" s="1"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -9988,7 +9984,7 @@
       </c>
       <c r="L145" s="1"/>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -10024,7 +10020,7 @@
       </c>
       <c r="L146" s="1"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -10060,7 +10056,7 @@
       </c>
       <c r="L147" s="1"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -10096,7 +10092,7 @@
       </c>
       <c r="L148" s="1"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -10132,7 +10128,7 @@
       </c>
       <c r="L149" s="1"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -10168,7 +10164,7 @@
       </c>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -10204,7 +10200,7 @@
       </c>
       <c r="L151" s="1"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -10240,7 +10236,7 @@
       </c>
       <c r="L152" s="1"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -10276,7 +10272,7 @@
       </c>
       <c r="L153" s="1"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -10312,7 +10308,7 @@
       </c>
       <c r="L154" s="1"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12">
       <c r="A155" s="3">
         <v>152</v>
       </c>
@@ -10348,7 +10344,7 @@
       </c>
       <c r="L155" s="1"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -10384,7 +10380,7 @@
       </c>
       <c r="L156" s="1"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -10420,7 +10416,7 @@
       </c>
       <c r="L157" s="1"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -10456,7 +10452,7 @@
       </c>
       <c r="L158" s="1"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -10492,7 +10488,7 @@
       </c>
       <c r="L159" s="1"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -10528,7 +10524,7 @@
       </c>
       <c r="L160" s="1"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -10542,7 +10538,7 @@
         <v>549</v>
       </c>
       <c r="E161" s="1">
-        <v>679180900</v>
+        <v>177279700</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>566</v>
@@ -10564,7 +10560,7 @@
       </c>
       <c r="L161" s="1"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -10578,7 +10574,7 @@
         <v>549</v>
       </c>
       <c r="E162" s="1">
-        <v>200371400</v>
+        <v>679180900</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>570</v>
@@ -10587,7 +10583,7 @@
         <v>567</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>59</v>
@@ -10600,7 +10596,7 @@
       </c>
       <c r="L162" s="1"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -10614,7 +10610,7 @@
         <v>549</v>
       </c>
       <c r="E163" s="1">
-        <v>144846400</v>
+        <v>200371400</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>573</v>
@@ -10636,7 +10632,7 @@
       </c>
       <c r="L163" s="1"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -10650,7 +10646,7 @@
         <v>549</v>
       </c>
       <c r="E164" s="1">
-        <v>177279700</v>
+        <v>144846400</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>576</v>
@@ -10659,7 +10655,7 @@
         <v>567</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>59</v>
@@ -10672,7 +10668,7 @@
       </c>
       <c r="L164" s="1"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -10708,7 +10704,7 @@
       </c>
       <c r="L165" s="1"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -10744,7 +10740,7 @@
       </c>
       <c r="L166" s="1"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -10758,7 +10754,7 @@
         <v>549</v>
       </c>
       <c r="E167" s="1">
-        <v>62679696</v>
+        <v>261119293</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>587</v>
@@ -10780,7 +10776,7 @@
       </c>
       <c r="L167" s="1"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -10794,7 +10790,7 @@
         <v>549</v>
       </c>
       <c r="E168" s="1">
-        <v>261119293</v>
+        <v>62679696</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>590</v>
@@ -10816,7 +10812,7 @@
       </c>
       <c r="L168" s="1"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -10830,34 +10826,34 @@
         <v>549</v>
       </c>
       <c r="E169" s="1">
-        <v>230734521</v>
+        <v>865011300</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>593</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K169" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L169" s="1"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12">
       <c r="A170" s="3">
         <v>167</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>579</v>
@@ -10869,7 +10865,7 @@
         <v>91372600</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>567</v>
@@ -10881,19 +10877,19 @@
         <v>59</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K170" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L170" s="1"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12">
       <c r="A171" s="3">
         <v>168</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>579</v>
@@ -10902,16 +10898,16 @@
         <v>549</v>
       </c>
       <c r="E171" s="1">
-        <v>865011300</v>
+        <v>261772500</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>59</v>
@@ -10924,7 +10920,7 @@
       </c>
       <c r="L171" s="1"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -10938,16 +10934,16 @@
         <v>549</v>
       </c>
       <c r="E172" s="1">
-        <v>261772500</v>
+        <v>230734521</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>603</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>59</v>
@@ -10960,7 +10956,7 @@
       </c>
       <c r="L172" s="1"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -10996,7 +10992,7 @@
       </c>
       <c r="L173" s="1"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12">
       <c r="A174" s="3">
         <v>171</v>
       </c>
@@ -11004,10 +11000,10 @@
         <v>608</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E174" s="1">
         <v>150900</v>
@@ -11032,7 +11028,7 @@
       </c>
       <c r="L174" s="1"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -11046,7 +11042,7 @@
         <v>614</v>
       </c>
       <c r="E175" s="1">
-        <v>213272917</v>
+        <v>153824056</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>615</v>
@@ -11068,7 +11064,7 @@
       </c>
       <c r="L175" s="1"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12">
       <c r="A176" s="3">
         <v>173</v>
       </c>
@@ -11082,7 +11078,7 @@
         <v>614</v>
       </c>
       <c r="E176" s="1">
-        <v>153824056</v>
+        <v>846201196</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>618</v>
@@ -11104,7 +11100,7 @@
       </c>
       <c r="L176" s="1"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -11118,7 +11114,7 @@
         <v>614</v>
       </c>
       <c r="E177" s="1">
-        <v>846201196</v>
+        <v>213272917</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>621</v>
@@ -11140,7 +11136,7 @@
       </c>
       <c r="L177" s="1"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -11176,7 +11172,7 @@
       </c>
       <c r="L178" s="1"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -11212,7 +11208,7 @@
       </c>
       <c r="L179" s="1"/>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -11248,7 +11244,7 @@
       </c>
       <c r="L180" s="1"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -11284,7 +11280,7 @@
       </c>
       <c r="L181" s="1"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -11298,7 +11294,7 @@
         <v>633</v>
       </c>
       <c r="E182" s="1">
-        <v>15407872</v>
+        <v>119845265</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>637</v>
@@ -11307,20 +11303,20 @@
         <v>633</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L182" s="1"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -11334,7 +11330,7 @@
         <v>633</v>
       </c>
       <c r="E183" s="1">
-        <v>119845265</v>
+        <v>15407872</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>639</v>
@@ -11343,20 +11339,20 @@
         <v>633</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="K183" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L183" s="1"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -11392,7 +11388,7 @@
       </c>
       <c r="L184" s="1"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -11428,7 +11424,7 @@
       </c>
       <c r="L185" s="1"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -11464,7 +11460,7 @@
       </c>
       <c r="L186" s="1"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -11500,7 +11496,7 @@
       </c>
       <c r="L187" s="1"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -11514,7 +11510,7 @@
         <v>641</v>
       </c>
       <c r="E188" s="1">
-        <v>933200</v>
+        <v>22220250</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>654</v>
@@ -11523,7 +11519,7 @@
         <v>655</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>17</v>
@@ -11536,7 +11532,7 @@
       </c>
       <c r="L188" s="1"/>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -11550,7 +11546,7 @@
         <v>641</v>
       </c>
       <c r="E189" s="1">
-        <v>22220250</v>
+        <v>79464800</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>658</v>
@@ -11572,7 +11568,7 @@
       </c>
       <c r="L189" s="1"/>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -11586,7 +11582,7 @@
         <v>641</v>
       </c>
       <c r="E190" s="1">
-        <v>79464800</v>
+        <v>933200</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>661</v>
@@ -11595,7 +11591,7 @@
         <v>655</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>17</v>
@@ -11608,7 +11604,7 @@
       </c>
       <c r="L190" s="1"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -11644,7 +11640,7 @@
       </c>
       <c r="L191" s="1"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -11658,7 +11654,7 @@
         <v>641</v>
       </c>
       <c r="E192" s="1">
-        <v>219100</v>
+        <v>1542200</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>667</v>
@@ -11680,7 +11676,7 @@
       </c>
       <c r="L192" s="1"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -11694,7 +11690,7 @@
         <v>641</v>
       </c>
       <c r="E193" s="1">
-        <v>100681700</v>
+        <v>219100</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>670</v>
@@ -11703,7 +11699,7 @@
         <v>655</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>17</v>
@@ -11716,7 +11712,7 @@
       </c>
       <c r="L193" s="1"/>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -11730,7 +11726,7 @@
         <v>641</v>
       </c>
       <c r="E194" s="1">
-        <v>1542200</v>
+        <v>100681700</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>673</v>
@@ -11739,7 +11735,7 @@
         <v>655</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>17</v>
@@ -11752,7 +11748,7 @@
       </c>
       <c r="L194" s="1"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -11788,7 +11784,7 @@
       </c>
       <c r="L195" s="1"/>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -11802,7 +11798,7 @@
         <v>655</v>
       </c>
       <c r="E196" s="1">
-        <v>29781850</v>
+        <v>20168600</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>679</v>
@@ -11824,7 +11820,7 @@
       </c>
       <c r="L196" s="1"/>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -11838,7 +11834,7 @@
         <v>655</v>
       </c>
       <c r="E197" s="1">
-        <v>20168600</v>
+        <v>29781850</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>682</v>
@@ -11860,7 +11856,7 @@
       </c>
       <c r="L197" s="1"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -11896,7 +11892,7 @@
       </c>
       <c r="L198" s="1"/>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -11932,7 +11928,7 @@
       </c>
       <c r="L199" s="1"/>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -11968,7 +11964,7 @@
       </c>
       <c r="L200" s="1"/>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -12004,7 +12000,7 @@
       </c>
       <c r="L201" s="1"/>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -12040,7 +12036,7 @@
       </c>
       <c r="L202" s="1"/>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -12076,7 +12072,7 @@
       </c>
       <c r="L203" s="1"/>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -12112,7 +12108,7 @@
       </c>
       <c r="L204" s="1"/>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -12148,7 +12144,7 @@
       </c>
       <c r="L205" s="1"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -12162,7 +12158,7 @@
         <v>698</v>
       </c>
       <c r="E206" s="1">
-        <v>218910000</v>
+        <v>157576000</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>712</v>
@@ -12184,7 +12180,7 @@
       </c>
       <c r="L206" s="1"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -12198,7 +12194,7 @@
         <v>698</v>
       </c>
       <c r="E207" s="1">
-        <v>157576000</v>
+        <v>218910000</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>715</v>
@@ -12220,7 +12216,7 @@
       </c>
       <c r="L207" s="1"/>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -12234,7 +12230,7 @@
         <v>698</v>
       </c>
       <c r="E208" s="1">
-        <v>102434200</v>
+        <v>1037129350</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>718</v>
@@ -12256,7 +12252,7 @@
       </c>
       <c r="L208" s="1"/>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -12292,7 +12288,7 @@
       </c>
       <c r="L209" s="1"/>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -12306,7 +12302,7 @@
         <v>698</v>
       </c>
       <c r="E210" s="1">
-        <v>1037129350</v>
+        <v>102434200</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>724</v>
@@ -12328,7 +12324,7 @@
       </c>
       <c r="L210" s="1"/>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -12364,7 +12360,7 @@
       </c>
       <c r="L211" s="1"/>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -12378,7 +12374,7 @@
         <v>698</v>
       </c>
       <c r="E212" s="1">
-        <v>751528800</v>
+        <v>147826000</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>732</v>
@@ -12387,25 +12383,25 @@
         <v>731</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>559</v>
+        <v>733</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K212" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L212" s="1"/>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12">
       <c r="A213" s="3">
         <v>210</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>731</v>
@@ -12414,16 +12410,16 @@
         <v>698</v>
       </c>
       <c r="E213" s="1">
-        <v>147826000</v>
+        <v>204525900</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>731</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>59</v>
@@ -12436,7 +12432,7 @@
       </c>
       <c r="L213" s="1"/>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -12450,7 +12446,7 @@
         <v>698</v>
       </c>
       <c r="E214" s="1">
-        <v>204525900</v>
+        <v>751528800</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>739</v>
@@ -12459,7 +12455,7 @@
         <v>731</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>736</v>
+        <v>559</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>59</v>
@@ -12472,7 +12468,7 @@
       </c>
       <c r="L214" s="1"/>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -12508,7 +12504,7 @@
       </c>
       <c r="L215" s="1"/>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -12531,7 +12527,7 @@
         <v>731</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>59</v>
@@ -12544,7 +12540,7 @@
       </c>
       <c r="L216" s="1"/>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -12558,7 +12554,7 @@
         <v>698</v>
       </c>
       <c r="E217" s="1">
-        <v>943434400</v>
+        <v>267194900</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>748</v>
@@ -12567,7 +12563,7 @@
         <v>731</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>559</v>
+        <v>733</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>59</v>
@@ -12580,7 +12576,7 @@
       </c>
       <c r="L217" s="1"/>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -12594,7 +12590,7 @@
         <v>698</v>
       </c>
       <c r="E218" s="1">
-        <v>267194900</v>
+        <v>943434400</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>751</v>
@@ -12603,7 +12599,7 @@
         <v>731</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>736</v>
+        <v>559</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>59</v>
@@ -12616,7 +12612,7 @@
       </c>
       <c r="L218" s="1"/>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -12652,7 +12648,7 @@
       </c>
       <c r="L219" s="1"/>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -12688,7 +12684,7 @@
       </c>
       <c r="L220" s="1"/>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -12702,7 +12698,7 @@
         <v>754</v>
       </c>
       <c r="E221" s="1">
-        <v>62679696</v>
+        <v>261119293</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>762</v>
@@ -12724,7 +12720,7 @@
       </c>
       <c r="L221" s="1"/>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -12738,7 +12734,7 @@
         <v>754</v>
       </c>
       <c r="E222" s="1">
-        <v>261119293</v>
+        <v>62679696</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>765</v>
@@ -12760,7 +12756,7 @@
       </c>
       <c r="L222" s="1"/>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -12796,7 +12792,7 @@
       </c>
       <c r="L223" s="1"/>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -12810,7 +12806,7 @@
         <v>754</v>
       </c>
       <c r="E224" s="1">
-        <v>91372600</v>
+        <v>261772500</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>772</v>
@@ -12832,7 +12828,7 @@
       </c>
       <c r="L224" s="1"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -12846,34 +12842,34 @@
         <v>754</v>
       </c>
       <c r="E225" s="1">
-        <v>261772500</v>
+        <v>867229400</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>776</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="K225" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L225" s="1"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12">
       <c r="A226" s="3">
         <v>223</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>771</v>
@@ -12882,16 +12878,16 @@
         <v>754</v>
       </c>
       <c r="E226" s="1">
-        <v>867229400</v>
+        <v>91372600</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>59</v>
@@ -12904,7 +12900,7 @@
       </c>
       <c r="L226" s="1"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -12924,7 +12920,7 @@
         <v>783</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>63</v>
@@ -12940,7 +12936,7 @@
       </c>
       <c r="L227" s="1"/>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -12954,16 +12950,16 @@
         <v>754</v>
       </c>
       <c r="E228" s="1">
-        <v>144846400</v>
+        <v>177279700</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>786</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>59</v>
@@ -12976,7 +12972,7 @@
       </c>
       <c r="L228" s="1"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -12990,16 +12986,16 @@
         <v>754</v>
       </c>
       <c r="E229" s="1">
-        <v>177279700</v>
+        <v>144846400</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>789</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>59</v>
@@ -13012,7 +13008,7 @@
       </c>
       <c r="L229" s="1"/>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -13048,7 +13044,7 @@
       </c>
       <c r="L230" s="1"/>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -13068,7 +13064,7 @@
         <v>795</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>63</v>
@@ -13084,7 +13080,7 @@
       </c>
       <c r="L231" s="1"/>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -13098,7 +13094,7 @@
         <v>798</v>
       </c>
       <c r="E232" s="1">
-        <v>34899150</v>
+        <v>279581387</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>799</v>
@@ -13107,7 +13103,7 @@
         <v>798</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>17</v>
@@ -13120,7 +13116,7 @@
       </c>
       <c r="L232" s="1"/>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -13134,7 +13130,7 @@
         <v>798</v>
       </c>
       <c r="E233" s="1">
-        <v>279581387</v>
+        <v>34899150</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>802</v>
@@ -13143,7 +13139,7 @@
         <v>798</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>17</v>
@@ -13156,7 +13152,7 @@
       </c>
       <c r="L233" s="1"/>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -13170,7 +13166,7 @@
         <v>798</v>
       </c>
       <c r="E234" s="1">
-        <v>99954715</v>
+        <v>12928000</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>805</v>
@@ -13179,7 +13175,7 @@
         <v>798</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>17</v>
@@ -13192,7 +13188,7 @@
       </c>
       <c r="L234" s="1"/>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -13206,7 +13202,7 @@
         <v>798</v>
       </c>
       <c r="E235" s="1">
-        <v>12928000</v>
+        <v>99954715</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>808</v>
@@ -13215,7 +13211,7 @@
         <v>798</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>17</v>
@@ -13228,7 +13224,7 @@
       </c>
       <c r="L235" s="1"/>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -13264,7 +13260,7 @@
       </c>
       <c r="L236" s="1"/>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -13300,7 +13296,7 @@
       </c>
       <c r="L237" s="1"/>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -13336,7 +13332,7 @@
       </c>
       <c r="L238" s="1"/>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -13372,7 +13368,7 @@
       </c>
       <c r="L239" s="1"/>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -13408,7 +13404,7 @@
       </c>
       <c r="L240" s="1"/>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -13444,7 +13440,7 @@
       </c>
       <c r="L241" s="1"/>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -13480,7 +13476,7 @@
       </c>
       <c r="L242" s="1"/>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -13516,7 +13512,7 @@
       </c>
       <c r="L243" s="1"/>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -13530,7 +13526,7 @@
         <v>815</v>
       </c>
       <c r="E244" s="1">
-        <v>100933077</v>
+        <v>1912000</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>839</v>
@@ -13539,20 +13535,20 @@
         <v>838</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="K244" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L244" s="1"/>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -13566,7 +13562,7 @@
         <v>815</v>
       </c>
       <c r="E245" s="1">
-        <v>1912000</v>
+        <v>100933077</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>841</v>
@@ -13575,20 +13571,20 @@
         <v>838</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K245" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L245" s="1"/>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -13624,7 +13620,7 @@
       </c>
       <c r="L246" s="1"/>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -13660,7 +13656,7 @@
       </c>
       <c r="L247" s="1"/>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -13696,7 +13692,7 @@
       </c>
       <c r="L248" s="1"/>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -13710,7 +13706,7 @@
         <v>773</v>
       </c>
       <c r="E249" s="1">
-        <v>19114400</v>
+        <v>20537250</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>853</v>
@@ -13719,7 +13715,7 @@
         <v>849</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>17</v>
@@ -13732,7 +13728,7 @@
       </c>
       <c r="L249" s="1"/>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -13746,7 +13742,7 @@
         <v>773</v>
       </c>
       <c r="E250" s="1">
-        <v>27114200</v>
+        <v>19114400</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>856</v>
@@ -13768,7 +13764,7 @@
       </c>
       <c r="L250" s="1"/>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -13782,7 +13778,7 @@
         <v>773</v>
       </c>
       <c r="E251" s="1">
-        <v>20537250</v>
+        <v>27114200</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>859</v>
@@ -13791,7 +13787,7 @@
         <v>849</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>17</v>
@@ -13804,7 +13800,7 @@
       </c>
       <c r="L251" s="1"/>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -13840,7 +13836,7 @@
       </c>
       <c r="L252" s="1"/>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -13876,7 +13872,7 @@
       </c>
       <c r="L253" s="1"/>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -13912,7 +13908,7 @@
       </c>
       <c r="L254" s="1"/>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -13948,7 +13944,7 @@
       </c>
       <c r="L255" s="1"/>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -13984,7 +13980,7 @@
       </c>
       <c r="L256" s="1"/>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -14020,7 +14016,7 @@
       </c>
       <c r="L257" s="1"/>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -14056,7 +14052,7 @@
       </c>
       <c r="L258" s="1"/>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -14092,7 +14088,7 @@
       </c>
       <c r="L259" s="1"/>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -14128,7 +14124,7 @@
       </c>
       <c r="L260" s="1"/>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -14164,7 +14160,7 @@
       </c>
       <c r="L261" s="1"/>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -14200,7 +14196,7 @@
       </c>
       <c r="L262" s="1"/>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -14236,7 +14232,7 @@
       </c>
       <c r="L263" s="1"/>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -14272,7 +14268,7 @@
       </c>
       <c r="L264" s="1"/>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -14308,7 +14304,7 @@
       </c>
       <c r="L265" s="1"/>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -14322,7 +14318,7 @@
         <v>896</v>
       </c>
       <c r="E266" s="1">
-        <v>200371400</v>
+        <v>149240400</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>913</v>
@@ -14344,7 +14340,7 @@
       </c>
       <c r="L266" s="1"/>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -14358,7 +14354,7 @@
         <v>896</v>
       </c>
       <c r="E267" s="1">
-        <v>149240400</v>
+        <v>177618600</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>917</v>
@@ -14367,7 +14363,7 @@
         <v>914</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>59</v>
@@ -14380,7 +14376,7 @@
       </c>
       <c r="L267" s="1"/>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -14394,7 +14390,7 @@
         <v>896</v>
       </c>
       <c r="E268" s="1">
-        <v>688714100</v>
+        <v>200371400</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>920</v>
@@ -14403,7 +14399,7 @@
         <v>914</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>59</v>
@@ -14416,7 +14412,7 @@
       </c>
       <c r="L268" s="1"/>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -14430,7 +14426,7 @@
         <v>896</v>
       </c>
       <c r="E269" s="1">
-        <v>177618600</v>
+        <v>688714100</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>923</v>
@@ -14452,7 +14448,7 @@
       </c>
       <c r="L269" s="1"/>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -14488,7 +14484,7 @@
       </c>
       <c r="L270" s="1"/>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -14502,7 +14498,7 @@
         <v>896</v>
       </c>
       <c r="E271" s="1">
-        <v>261772500</v>
+        <v>91372600</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>929</v>
@@ -14524,7 +14520,7 @@
       </c>
       <c r="L271" s="1"/>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -14538,7 +14534,7 @@
         <v>896</v>
       </c>
       <c r="E272" s="1">
-        <v>91372600</v>
+        <v>865040100</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>932</v>
@@ -14547,7 +14543,7 @@
         <v>914</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>59</v>
@@ -14560,7 +14556,7 @@
       </c>
       <c r="L272" s="1"/>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -14574,7 +14570,7 @@
         <v>896</v>
       </c>
       <c r="E273" s="1">
-        <v>865040100</v>
+        <v>261772500</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>935</v>
@@ -14583,7 +14579,7 @@
         <v>914</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>59</v>
@@ -14596,7 +14592,7 @@
       </c>
       <c r="L273" s="1"/>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -14632,7 +14628,7 @@
       </c>
       <c r="L274" s="1"/>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -14646,7 +14642,7 @@
         <v>938</v>
       </c>
       <c r="E275" s="1">
-        <v>158436845</v>
+        <v>845082696</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>942</v>
@@ -14668,7 +14664,7 @@
       </c>
       <c r="L275" s="1"/>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -14682,7 +14678,7 @@
         <v>938</v>
       </c>
       <c r="E276" s="1">
-        <v>845082696</v>
+        <v>212695655</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>945</v>
@@ -14704,7 +14700,7 @@
       </c>
       <c r="L276" s="1"/>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -14718,7 +14714,7 @@
         <v>938</v>
       </c>
       <c r="E277" s="1">
-        <v>212695655</v>
+        <v>158436845</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>948</v>
@@ -14740,7 +14736,7 @@
       </c>
       <c r="L277" s="1"/>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -14754,7 +14750,7 @@
         <v>938</v>
       </c>
       <c r="E278" s="1">
-        <v>99929015</v>
+        <v>1055833082</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>951</v>
@@ -14776,7 +14772,7 @@
       </c>
       <c r="L278" s="1"/>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -14790,7 +14786,7 @@
         <v>938</v>
       </c>
       <c r="E279" s="1">
-        <v>1055833082</v>
+        <v>99929015</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>954</v>
@@ -14812,7 +14808,7 @@
       </c>
       <c r="L279" s="1"/>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -14848,7 +14844,7 @@
       </c>
       <c r="L280" s="1"/>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12">
       <c r="A281" s="3">
         <v>278</v>
       </c>
@@ -14884,7 +14880,7 @@
       </c>
       <c r="L281" s="1"/>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12">
       <c r="A282" s="3">
         <v>279</v>
       </c>
@@ -14920,7 +14916,7 @@
       </c>
       <c r="L282" s="1"/>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12">
       <c r="A283" s="3">
         <v>280</v>
       </c>
@@ -14956,7 +14952,7 @@
       </c>
       <c r="L283" s="1"/>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12">
       <c r="A284" s="3">
         <v>281</v>
       </c>
@@ -14992,7 +14988,7 @@
       </c>
       <c r="L284" s="1"/>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12">
       <c r="A285" s="3">
         <v>282</v>
       </c>
@@ -15028,7 +15024,7 @@
       </c>
       <c r="L285" s="1"/>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12">
       <c r="A286" s="3">
         <v>283</v>
       </c>
@@ -15064,7 +15060,7 @@
       </c>
       <c r="L286" s="1"/>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12">
       <c r="A287" s="3">
         <v>284</v>
       </c>
@@ -15078,7 +15074,7 @@
         <v>970</v>
       </c>
       <c r="E287" s="1">
-        <v>24294250</v>
+        <v>32629000</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>980</v>
@@ -15087,7 +15083,7 @@
         <v>914</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>17</v>
@@ -15100,7 +15096,7 @@
       </c>
       <c r="L287" s="1"/>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12">
       <c r="A288" s="3">
         <v>285</v>
       </c>
@@ -15114,7 +15110,7 @@
         <v>970</v>
       </c>
       <c r="E288" s="1">
-        <v>32629000</v>
+        <v>24294250</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>983</v>
@@ -15123,7 +15119,7 @@
         <v>914</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>17</v>
@@ -15136,7 +15132,7 @@
       </c>
       <c r="L288" s="1"/>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12">
       <c r="A289" s="3">
         <v>286</v>
       </c>
@@ -15150,7 +15146,7 @@
         <v>970</v>
       </c>
       <c r="E289" s="1">
-        <v>24034050</v>
+        <v>90092300</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>986</v>
@@ -15159,7 +15155,7 @@
         <v>914</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>17</v>
@@ -15172,7 +15168,7 @@
       </c>
       <c r="L289" s="1"/>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12">
       <c r="A290" s="3">
         <v>287</v>
       </c>
@@ -15186,7 +15182,7 @@
         <v>970</v>
       </c>
       <c r="E290" s="1">
-        <v>90092300</v>
+        <v>24034050</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>989</v>
@@ -15195,7 +15191,7 @@
         <v>914</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>17</v>
@@ -15208,7 +15204,7 @@
       </c>
       <c r="L290" s="1"/>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12">
       <c r="A291" s="3">
         <v>288</v>
       </c>
@@ -15222,7 +15218,7 @@
         <v>970</v>
       </c>
       <c r="E291" s="1">
-        <v>15352000</v>
+        <v>114527250</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>992</v>
@@ -15231,7 +15227,7 @@
         <v>914</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>17</v>
@@ -15244,7 +15240,7 @@
       </c>
       <c r="L291" s="1"/>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12">
       <c r="A292" s="3">
         <v>289</v>
       </c>
@@ -15258,7 +15254,7 @@
         <v>970</v>
       </c>
       <c r="E292" s="1">
-        <v>114527250</v>
+        <v>41541600</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>995</v>
@@ -15267,7 +15263,7 @@
         <v>914</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>17</v>
@@ -15280,7 +15276,7 @@
       </c>
       <c r="L292" s="1"/>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12">
       <c r="A293" s="3">
         <v>290</v>
       </c>
@@ -15294,7 +15290,7 @@
         <v>970</v>
       </c>
       <c r="E293" s="1">
-        <v>41541600</v>
+        <v>15352000</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>998</v>
@@ -15316,7 +15312,7 @@
       </c>
       <c r="L293" s="1"/>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12">
       <c r="A294" s="3">
         <v>291</v>
       </c>
@@ -15352,7 +15348,7 @@
       </c>
       <c r="L294" s="1"/>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12">
       <c r="A295" s="3">
         <v>292</v>
       </c>
@@ -15388,7 +15384,7 @@
       </c>
       <c r="L295" s="1"/>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12">
       <c r="A296" s="3">
         <v>293</v>
       </c>
@@ -15424,7 +15420,7 @@
       </c>
       <c r="L296" s="1"/>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12">
       <c r="A297" s="3">
         <v>294</v>
       </c>
@@ -15460,7 +15456,7 @@
       </c>
       <c r="L297" s="1"/>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12">
       <c r="A298" s="3">
         <v>295</v>
       </c>
@@ -15496,7 +15492,7 @@
       </c>
       <c r="L298" s="1"/>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12">
       <c r="A299" s="3">
         <v>296</v>
       </c>
@@ -15532,7 +15528,7 @@
       </c>
       <c r="L299" s="1"/>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12">
       <c r="A300" s="3">
         <v>297</v>
       </c>
@@ -15568,7 +15564,7 @@
       </c>
       <c r="L300" s="1"/>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12">
       <c r="A301" s="3">
         <v>298</v>
       </c>
@@ -15582,7 +15578,7 @@
         <v>1022</v>
       </c>
       <c r="E301" s="1">
-        <v>258570562</v>
+        <v>2548731</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>1029</v>
@@ -15604,7 +15600,7 @@
       </c>
       <c r="L301" s="1"/>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12">
       <c r="A302" s="3">
         <v>299</v>
       </c>
@@ -15618,7 +15614,7 @@
         <v>1022</v>
       </c>
       <c r="E302" s="1">
-        <v>62679696</v>
+        <v>258570562</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>1032</v>
@@ -15640,7 +15636,7 @@
       </c>
       <c r="L302" s="1"/>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12">
       <c r="A303" s="3">
         <v>300</v>
       </c>
@@ -15654,7 +15650,7 @@
         <v>1022</v>
       </c>
       <c r="E303" s="1">
-        <v>2548731</v>
+        <v>62679696</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>1035</v>
@@ -15676,7 +15672,7 @@
       </c>
       <c r="L303" s="1"/>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12">
       <c r="A304" s="3">
         <v>301</v>
       </c>
@@ -15712,7 +15708,7 @@
       </c>
       <c r="L304" s="1"/>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12">
       <c r="A305" s="3">
         <v>302</v>
       </c>
@@ -15726,7 +15722,7 @@
         <v>1022</v>
       </c>
       <c r="E305" s="1">
-        <v>177359200</v>
+        <v>200371400</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>1041</v>
@@ -15735,7 +15731,7 @@
         <v>1042</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>59</v>
@@ -15748,7 +15744,7 @@
       </c>
       <c r="L305" s="1"/>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12">
       <c r="A306" s="3">
         <v>303</v>
       </c>
@@ -15762,7 +15758,7 @@
         <v>1022</v>
       </c>
       <c r="E306" s="1">
-        <v>689018800</v>
+        <v>177359200</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>1045</v>
@@ -15784,7 +15780,7 @@
       </c>
       <c r="L306" s="1"/>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12">
       <c r="A307" s="3">
         <v>304</v>
       </c>
@@ -15798,7 +15794,7 @@
         <v>1022</v>
       </c>
       <c r="E307" s="1">
-        <v>200371400</v>
+        <v>689018800</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>1048</v>
@@ -15807,7 +15803,7 @@
         <v>1042</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>59</v>
@@ -15820,7 +15816,7 @@
       </c>
       <c r="L307" s="1"/>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12">
       <c r="A308" s="3">
         <v>305</v>
       </c>
@@ -15856,7 +15852,7 @@
       </c>
       <c r="L308" s="1"/>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12">
       <c r="A309" s="3">
         <v>306</v>
       </c>
@@ -15892,7 +15888,7 @@
       </c>
       <c r="L309" s="1"/>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12">
       <c r="A310" s="3">
         <v>307</v>
       </c>
@@ -15928,7 +15924,7 @@
       </c>
       <c r="L310" s="1"/>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12">
       <c r="A311" s="3">
         <v>308</v>
       </c>
@@ -15942,34 +15938,34 @@
         <v>1022</v>
       </c>
       <c r="E311" s="1">
-        <v>865047300</v>
+        <v>261772500</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>1062</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1063</v>
+        <v>1042</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J311" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="K311" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L311" s="1"/>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12">
       <c r="A312" s="3">
         <v>309</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>1021</v>
@@ -15978,16 +15974,16 @@
         <v>1022</v>
       </c>
       <c r="E312" s="1">
-        <v>261772500</v>
+        <v>865047300</v>
       </c>
       <c r="F312" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G312" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="G312" s="1" t="s">
-        <v>1042</v>
-      </c>
       <c r="H312" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>59</v>
@@ -16000,7 +15996,7 @@
       </c>
       <c r="L312" s="1"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12">
       <c r="A313" s="3">
         <v>310</v>
       </c>
@@ -16014,7 +16010,7 @@
         <v>1069</v>
       </c>
       <c r="E313" s="1">
-        <v>258570562</v>
+        <v>2548731</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>1070</v>
@@ -16036,7 +16032,7 @@
       </c>
       <c r="L313" s="1"/>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12">
       <c r="A314" s="3">
         <v>311</v>
       </c>
@@ -16050,7 +16046,7 @@
         <v>1069</v>
       </c>
       <c r="E314" s="1">
-        <v>2548731</v>
+        <v>258570562</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>1073</v>
@@ -16072,7 +16068,7 @@
       </c>
       <c r="L314" s="1"/>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12">
       <c r="A315" s="3">
         <v>312</v>
       </c>
@@ -16108,7 +16104,7 @@
       </c>
       <c r="L315" s="1"/>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12">
       <c r="A316" s="3">
         <v>313</v>
       </c>
@@ -16122,7 +16118,7 @@
         <v>1069</v>
       </c>
       <c r="E316" s="1">
-        <v>2600000</v>
+        <v>263800000</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>1079</v>
@@ -16144,7 +16140,7 @@
       </c>
       <c r="L316" s="1"/>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12">
       <c r="A317" s="3">
         <v>314</v>
       </c>
@@ -16158,7 +16154,7 @@
         <v>1069</v>
       </c>
       <c r="E317" s="1">
-        <v>263800000</v>
+        <v>2600000</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>1083</v>
@@ -16180,7 +16176,7 @@
       </c>
       <c r="L317" s="1"/>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12">
       <c r="A318" s="3">
         <v>315</v>
       </c>
@@ -16216,7 +16212,7 @@
       </c>
       <c r="L318" s="1"/>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12">
       <c r="A319" s="3">
         <v>316</v>
       </c>
@@ -16252,7 +16248,7 @@
       </c>
       <c r="L319" s="1"/>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12">
       <c r="A320" s="3">
         <v>317</v>
       </c>
@@ -16288,7 +16284,7 @@
       </c>
       <c r="L320" s="1"/>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12">
       <c r="A321" s="3">
         <v>318</v>
       </c>
@@ -16324,7 +16320,7 @@
       </c>
       <c r="L321" s="1"/>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12">
       <c r="A322" s="3">
         <v>319</v>
       </c>
@@ -16360,7 +16356,7 @@
       </c>
       <c r="L322" s="1"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12">
       <c r="A323" s="3">
         <v>320</v>
       </c>
@@ -16396,7 +16392,7 @@
       </c>
       <c r="L323" s="1"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12">
       <c r="A324" s="3">
         <v>321</v>
       </c>
@@ -16432,7 +16428,7 @@
       </c>
       <c r="L324" s="1"/>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12">
       <c r="A325" s="3">
         <v>322</v>
       </c>
@@ -16446,7 +16442,7 @@
         <v>1094</v>
       </c>
       <c r="E325" s="1">
-        <v>667850</v>
+        <v>703000</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>1108</v>
@@ -16468,7 +16464,7 @@
       </c>
       <c r="L325" s="1"/>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12">
       <c r="A326" s="3">
         <v>323</v>
       </c>
@@ -16504,7 +16500,7 @@
       </c>
       <c r="L326" s="1"/>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12">
       <c r="A327" s="3">
         <v>324</v>
       </c>
@@ -16518,7 +16514,7 @@
         <v>1094</v>
       </c>
       <c r="E327" s="1">
-        <v>703000</v>
+        <v>667850</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>1114</v>
@@ -16540,7 +16536,7 @@
       </c>
       <c r="L327" s="1"/>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12">
       <c r="A328" s="3">
         <v>325</v>
       </c>
@@ -16576,7 +16572,7 @@
       </c>
       <c r="L328" s="1"/>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12">
       <c r="A329" s="3">
         <v>326</v>
       </c>
@@ -16612,7 +16608,7 @@
       </c>
       <c r="L329" s="1"/>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12">
       <c r="A330" s="3">
         <v>327</v>
       </c>
@@ -16648,7 +16644,7 @@
       </c>
       <c r="L330" s="1"/>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12">
       <c r="A331" s="3">
         <v>328</v>
       </c>
@@ -16684,7 +16680,7 @@
       </c>
       <c r="L331" s="1"/>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12">
       <c r="A332" s="3">
         <v>329</v>
       </c>
@@ -16720,7 +16716,7 @@
       </c>
       <c r="L332" s="1"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12">
       <c r="A333" s="3">
         <v>330</v>
       </c>
@@ -16756,7 +16752,7 @@
       </c>
       <c r="L333" s="1"/>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12">
       <c r="A334" s="3">
         <v>331</v>
       </c>
@@ -16770,7 +16766,7 @@
         <v>1099</v>
       </c>
       <c r="E334" s="1">
-        <v>762330900</v>
+        <v>204133200</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>1138</v>
@@ -16779,7 +16775,7 @@
         <v>1128</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>1129</v>
+        <v>1018</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>59</v>
@@ -16792,7 +16788,7 @@
       </c>
       <c r="L334" s="1"/>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12">
       <c r="A335" s="3">
         <v>332</v>
       </c>
@@ -16806,7 +16802,7 @@
         <v>1099</v>
       </c>
       <c r="E335" s="1">
-        <v>4313300</v>
+        <v>193894600</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>1141</v>
@@ -16828,7 +16824,7 @@
       </c>
       <c r="L335" s="1"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12">
       <c r="A336" s="3">
         <v>333</v>
       </c>
@@ -16842,7 +16838,7 @@
         <v>1099</v>
       </c>
       <c r="E336" s="1">
-        <v>63500000</v>
+        <v>4313300</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>1144</v>
@@ -16851,7 +16847,7 @@
         <v>1128</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>1080</v>
+        <v>1129</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>59</v>
@@ -16864,7 +16860,7 @@
       </c>
       <c r="L336" s="1"/>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12">
       <c r="A337" s="3">
         <v>334</v>
       </c>
@@ -16878,7 +16874,7 @@
         <v>1099</v>
       </c>
       <c r="E337" s="1">
-        <v>151924700</v>
+        <v>762330900</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>1147</v>
@@ -16887,7 +16883,7 @@
         <v>1128</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>1018</v>
+        <v>1129</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>59</v>
@@ -16900,7 +16896,7 @@
       </c>
       <c r="L337" s="1"/>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12">
       <c r="A338" s="3">
         <v>335</v>
       </c>
@@ -16914,7 +16910,7 @@
         <v>1099</v>
       </c>
       <c r="E338" s="1">
-        <v>193894600</v>
+        <v>151924700</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>1150</v>
@@ -16923,7 +16919,7 @@
         <v>1128</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1129</v>
+        <v>1018</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>59</v>
@@ -16936,7 +16932,7 @@
       </c>
       <c r="L338" s="1"/>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12">
       <c r="A339" s="3">
         <v>336</v>
       </c>
@@ -16950,7 +16946,7 @@
         <v>1099</v>
       </c>
       <c r="E339" s="1">
-        <v>204133200</v>
+        <v>63500000</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>1153</v>
@@ -16959,7 +16955,7 @@
         <v>1128</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1018</v>
+        <v>1080</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>59</v>
@@ -16972,7 +16968,7 @@
       </c>
       <c r="L339" s="1"/>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12">
       <c r="A340" s="3">
         <v>337</v>
       </c>
@@ -16983,7 +16979,7 @@
         <v>1156</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E340" s="1">
         <v>5890000</v>
@@ -17008,7 +17004,7 @@
       </c>
       <c r="L340" s="1"/>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12">
       <c r="A341" s="3">
         <v>338</v>
       </c>
@@ -17044,7 +17040,7 @@
       </c>
       <c r="L341" s="1"/>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12">
       <c r="A342" s="3">
         <v>339</v>
       </c>
@@ -17058,7 +17054,7 @@
         <v>1156</v>
       </c>
       <c r="E342" s="1">
-        <v>33963050</v>
+        <v>852003538</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>1163</v>
@@ -17067,7 +17063,7 @@
         <v>1042</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>17</v>
@@ -17080,7 +17076,7 @@
       </c>
       <c r="L342" s="1"/>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12">
       <c r="A343" s="3">
         <v>340</v>
       </c>
@@ -17094,7 +17090,7 @@
         <v>1156</v>
       </c>
       <c r="E343" s="1">
-        <v>852003538</v>
+        <v>33963050</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>1166</v>
@@ -17103,7 +17099,7 @@
         <v>1042</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>17</v>
@@ -17116,7 +17112,7 @@
       </c>
       <c r="L343" s="1"/>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12">
       <c r="A344" s="3">
         <v>341</v>
       </c>
@@ -17130,7 +17126,7 @@
         <v>1156</v>
       </c>
       <c r="E344" s="1">
-        <v>5979200</v>
+        <v>5246000</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>1169</v>
@@ -17139,25 +17135,25 @@
         <v>1042</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>73</v>
+        <v>1170</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K344" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L344" s="1"/>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12">
       <c r="A345" s="3">
         <v>342</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>1156</v>
@@ -17166,16 +17162,16 @@
         <v>1156</v>
       </c>
       <c r="E345" s="1">
-        <v>5246000</v>
+        <v>1067934069</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>1042</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>1173</v>
+        <v>73</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>17</v>
@@ -17188,7 +17184,7 @@
       </c>
       <c r="L345" s="1"/>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12">
       <c r="A346" s="3">
         <v>343</v>
       </c>
@@ -17202,7 +17198,7 @@
         <v>1156</v>
       </c>
       <c r="E346" s="1">
-        <v>1067934069</v>
+        <v>5979200</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>1176</v>
@@ -17224,7 +17220,7 @@
       </c>
       <c r="L346" s="1"/>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12">
       <c r="A347" s="3">
         <v>344</v>
       </c>
@@ -17260,7 +17256,7 @@
       </c>
       <c r="L347" s="1"/>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12">
       <c r="A348" s="3">
         <v>345</v>
       </c>
@@ -17296,7 +17292,7 @@
       </c>
       <c r="L348" s="1"/>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12">
       <c r="A349" s="3">
         <v>346</v>
       </c>
@@ -17310,7 +17306,7 @@
         <v>1156</v>
       </c>
       <c r="E349" s="1">
-        <v>25170300</v>
+        <v>213083067</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>1185</v>
@@ -17319,7 +17315,7 @@
         <v>1042</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>17</v>
@@ -17332,7 +17328,7 @@
       </c>
       <c r="L349" s="1"/>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12">
       <c r="A350" s="3">
         <v>347</v>
       </c>
@@ -17346,7 +17342,7 @@
         <v>1156</v>
       </c>
       <c r="E350" s="1">
-        <v>213083067</v>
+        <v>25170300</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>1188</v>
@@ -17355,7 +17351,7 @@
         <v>1042</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>17</v>
@@ -17368,7 +17364,7 @@
       </c>
       <c r="L350" s="1"/>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12">
       <c r="A351" s="3">
         <v>348</v>
       </c>
@@ -17404,7 +17400,7 @@
       </c>
       <c r="L351" s="1"/>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12">
       <c r="A352" s="3">
         <v>349</v>
       </c>
@@ -17418,7 +17414,7 @@
         <v>1156</v>
       </c>
       <c r="E352" s="1">
-        <v>44072100</v>
+        <v>121463700</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>1194</v>
@@ -17427,7 +17423,7 @@
         <v>1042</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>17</v>
@@ -17440,7 +17436,7 @@
       </c>
       <c r="L352" s="1"/>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12">
       <c r="A353" s="3">
         <v>350</v>
       </c>
@@ -17476,7 +17472,7 @@
       </c>
       <c r="L353" s="1"/>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12">
       <c r="A354" s="3">
         <v>351</v>
       </c>
@@ -17490,7 +17486,7 @@
         <v>1156</v>
       </c>
       <c r="E354" s="1">
-        <v>121463700</v>
+        <v>44072100</v>
       </c>
       <c r="F354" s="1" t="s">
         <v>1200</v>
@@ -17499,7 +17495,7 @@
         <v>1042</v>
       </c>
       <c r="H354" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>17</v>
@@ -17512,7 +17508,7 @@
       </c>
       <c r="L354" s="1"/>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12">
       <c r="A355" s="3">
         <v>352</v>
       </c>
@@ -17548,7 +17544,7 @@
       </c>
       <c r="L355" s="1"/>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12">
       <c r="A356" s="3">
         <v>353</v>
       </c>
@@ -17584,7 +17580,7 @@
       </c>
       <c r="L356" s="1"/>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12">
       <c r="A357" s="3">
         <v>354</v>
       </c>
@@ -17620,7 +17616,7 @@
       </c>
       <c r="L357" s="1"/>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12">
       <c r="A358" s="3">
         <v>355</v>
       </c>
@@ -17643,7 +17639,7 @@
         <v>1205</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>17</v>
@@ -17656,7 +17652,7 @@
       </c>
       <c r="L358" s="1"/>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12">
       <c r="A359" s="3">
         <v>356</v>
       </c>
@@ -17692,7 +17688,7 @@
       </c>
       <c r="L359" s="1"/>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12">
       <c r="A360" s="3">
         <v>357</v>
       </c>
@@ -17728,7 +17724,7 @@
       </c>
       <c r="L360" s="1"/>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12">
       <c r="A361" s="3">
         <v>358</v>
       </c>
@@ -17764,7 +17760,7 @@
       </c>
       <c r="L361" s="1"/>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12">
       <c r="A362" s="3">
         <v>359</v>
       </c>
@@ -17800,7 +17796,7 @@
       </c>
       <c r="L362" s="1"/>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12">
       <c r="A363" s="3">
         <v>360</v>
       </c>
@@ -17836,7 +17832,7 @@
       </c>
       <c r="L363" s="1"/>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12">
       <c r="A364" s="3">
         <v>361</v>
       </c>
@@ -17872,7 +17868,7 @@
       </c>
       <c r="L364" s="1"/>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12">
       <c r="A365" s="3">
         <v>362</v>
       </c>
@@ -17886,7 +17882,7 @@
         <v>1238</v>
       </c>
       <c r="E365" s="1">
-        <v>116066650</v>
+        <v>279584469</v>
       </c>
       <c r="F365" s="1" t="s">
         <v>1239</v>
@@ -17895,7 +17891,7 @@
         <v>1237</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>17</v>
@@ -17908,7 +17904,7 @@
       </c>
       <c r="L365" s="1"/>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12">
       <c r="A366" s="3">
         <v>363</v>
       </c>
@@ -17922,7 +17918,7 @@
         <v>1238</v>
       </c>
       <c r="E366" s="1">
-        <v>1071525202</v>
+        <v>41365850</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>1242</v>
@@ -17931,7 +17927,7 @@
         <v>1237</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>17</v>
@@ -17944,7 +17940,7 @@
       </c>
       <c r="L366" s="1"/>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12">
       <c r="A367" s="3">
         <v>364</v>
       </c>
@@ -17958,7 +17954,7 @@
         <v>1238</v>
       </c>
       <c r="E367" s="1">
-        <v>279584469</v>
+        <v>116066650</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>1245</v>
@@ -17967,7 +17963,7 @@
         <v>1237</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>17</v>
@@ -17980,7 +17976,7 @@
       </c>
       <c r="L367" s="1"/>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12">
       <c r="A368" s="3">
         <v>365</v>
       </c>
@@ -17994,7 +17990,7 @@
         <v>1238</v>
       </c>
       <c r="E368" s="1">
-        <v>41365850</v>
+        <v>1071525202</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>1248</v>
@@ -18003,7 +17999,7 @@
         <v>1237</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>17</v>
@@ -18016,7 +18012,7 @@
       </c>
       <c r="L368" s="1"/>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12">
       <c r="A369" s="3">
         <v>366</v>
       </c>
@@ -18052,7 +18048,7 @@
       </c>
       <c r="L369" s="1"/>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12">
       <c r="A370" s="3">
         <v>367</v>
       </c>
@@ -18088,7 +18084,7 @@
       </c>
       <c r="L370" s="1"/>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12">
       <c r="A371" s="3">
         <v>368</v>
       </c>
@@ -18124,7 +18120,7 @@
       </c>
       <c r="L371" s="1"/>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12">
       <c r="A372" s="3">
         <v>369</v>
       </c>
@@ -18160,7 +18156,7 @@
       </c>
       <c r="L372" s="1"/>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12">
       <c r="A373" s="3">
         <v>370</v>
       </c>
@@ -18174,34 +18170,34 @@
         <v>1252</v>
       </c>
       <c r="E373" s="1">
-        <v>177151200</v>
+        <v>149250700</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>1267</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J373" s="1" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="K373" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L373" s="1"/>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12">
       <c r="A374" s="3">
         <v>371</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>1254</v>
@@ -18210,16 +18206,16 @@
         <v>1252</v>
       </c>
       <c r="E374" s="1">
-        <v>149250700</v>
+        <v>177151200</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>59</v>
@@ -18232,7 +18228,7 @@
       </c>
       <c r="L374" s="1"/>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12">
       <c r="A375" s="3">
         <v>372</v>
       </c>
@@ -18246,34 +18242,34 @@
         <v>1252</v>
       </c>
       <c r="E375" s="1">
-        <v>199981800</v>
+        <v>62679696</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>1274</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>1264</v>
+        <v>1275</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J375" s="1" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K375" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L375" s="1"/>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12">
       <c r="A376" s="3">
         <v>373</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>1254</v>
@@ -18282,16 +18278,16 @@
         <v>1252</v>
       </c>
       <c r="E376" s="1">
-        <v>62679696</v>
+        <v>199981800</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>1278</v>
+        <v>1264</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>59</v>
@@ -18304,7 +18300,7 @@
       </c>
       <c r="L376" s="1"/>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12">
       <c r="A377" s="3">
         <v>374</v>
       </c>
@@ -18340,7 +18336,7 @@
       </c>
       <c r="L377" s="1"/>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12">
       <c r="A378" s="3">
         <v>375</v>
       </c>
@@ -18360,7 +18356,7 @@
         <v>1284</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="H378" s="1" t="s">
         <v>58</v>
@@ -18376,7 +18372,7 @@
       </c>
       <c r="L378" s="1"/>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12">
       <c r="A379" s="3">
         <v>376</v>
       </c>
@@ -18387,7 +18383,7 @@
         <v>1287</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="E379" s="1">
         <v>258570562</v>
@@ -18412,7 +18408,7 @@
       </c>
       <c r="L379" s="1"/>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12">
       <c r="A380" s="3">
         <v>377</v>
       </c>
@@ -18423,7 +18419,7 @@
         <v>1264</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E380" s="1">
         <v>837896759</v>
@@ -18448,7 +18444,7 @@
       </c>
       <c r="L380" s="1"/>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12">
       <c r="A381" s="3">
         <v>378</v>
       </c>
@@ -18459,10 +18455,10 @@
         <v>1264</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E381" s="1">
-        <v>213243288</v>
+        <v>158575478</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>1294</v>
@@ -18484,7 +18480,7 @@
       </c>
       <c r="L381" s="1"/>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12">
       <c r="A382" s="3">
         <v>379</v>
       </c>
@@ -18495,10 +18491,10 @@
         <v>1264</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E382" s="1">
-        <v>158575478</v>
+        <v>213243288</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>1297</v>
@@ -18520,7 +18516,7 @@
       </c>
       <c r="L382" s="1"/>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12">
       <c r="A383" s="3">
         <v>380</v>
       </c>
@@ -18534,7 +18530,7 @@
         <v>1264</v>
       </c>
       <c r="E383" s="1">
-        <v>22608400</v>
+        <v>24034050</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>1301</v>
@@ -18543,7 +18539,7 @@
         <v>1302</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>17</v>
@@ -18556,7 +18552,7 @@
       </c>
       <c r="L383" s="1"/>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12">
       <c r="A384" s="3">
         <v>381</v>
       </c>
@@ -18570,7 +18566,7 @@
         <v>1264</v>
       </c>
       <c r="E384" s="1">
-        <v>24034050</v>
+        <v>22608400</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>1305</v>
@@ -18579,7 +18575,7 @@
         <v>1302</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>17</v>
@@ -18592,7 +18588,7 @@
       </c>
       <c r="L384" s="1"/>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12">
       <c r="A385" s="3">
         <v>382</v>
       </c>
@@ -18628,7 +18624,7 @@
       </c>
       <c r="L385" s="1"/>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12">
       <c r="A386" s="3">
         <v>383</v>
       </c>
@@ -18664,7 +18660,7 @@
       </c>
       <c r="L386" s="1"/>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12">
       <c r="A387" s="3">
         <v>384</v>
       </c>
@@ -18700,7 +18696,7 @@
       </c>
       <c r="L387" s="1"/>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12">
       <c r="A388" s="3">
         <v>385</v>
       </c>
@@ -18736,7 +18732,7 @@
       </c>
       <c r="L388" s="1"/>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12">
       <c r="A389" s="3">
         <v>386</v>
       </c>
@@ -18772,7 +18768,7 @@
       </c>
       <c r="L389" s="1"/>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12">
       <c r="A390" s="3">
         <v>387</v>
       </c>
@@ -18808,7 +18804,7 @@
       </c>
       <c r="L390" s="1"/>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12">
       <c r="A391" s="3">
         <v>388</v>
       </c>
@@ -18819,7 +18815,7 @@
         <v>1326</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E391" s="1">
         <v>60825925</v>
@@ -18844,7 +18840,7 @@
       </c>
       <c r="L391" s="1"/>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12">
       <c r="A392" s="3">
         <v>389</v>
       </c>
@@ -18855,7 +18851,7 @@
         <v>1326</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E392" s="1">
         <v>2844264</v>
@@ -18880,7 +18876,7 @@
       </c>
       <c r="L392" s="1"/>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12">
       <c r="A393" s="3">
         <v>390</v>
       </c>
@@ -18916,7 +18912,7 @@
       </c>
       <c r="L393" s="1"/>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12">
       <c r="A394" s="3">
         <v>391</v>
       </c>
@@ -18952,7 +18948,7 @@
       </c>
       <c r="L394" s="1"/>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12">
       <c r="A395" s="3">
         <v>392</v>
       </c>
@@ -18988,7 +18984,7 @@
       </c>
       <c r="L395" s="1"/>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12">
       <c r="A396" s="3">
         <v>393</v>
       </c>
@@ -19024,7 +19020,7 @@
       </c>
       <c r="L396" s="1"/>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12">
       <c r="A397" s="3">
         <v>394</v>
       </c>
@@ -19060,7 +19056,7 @@
       </c>
       <c r="L397" s="1"/>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12">
       <c r="A398" s="3">
         <v>395</v>
       </c>
@@ -19096,7 +19092,7 @@
       </c>
       <c r="L398" s="1"/>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12">
       <c r="A399" s="3">
         <v>396</v>
       </c>
@@ -19132,7 +19128,7 @@
       </c>
       <c r="L399" s="1"/>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12">
       <c r="A400" s="3">
         <v>397</v>
       </c>
@@ -19168,7 +19164,7 @@
       </c>
       <c r="L400" s="1"/>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12">
       <c r="A401" s="3">
         <v>398</v>
       </c>
@@ -19204,7 +19200,7 @@
       </c>
       <c r="L401" s="1"/>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12">
       <c r="A402" s="3">
         <v>399</v>
       </c>
@@ -19240,7 +19236,7 @@
       </c>
       <c r="L402" s="1"/>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12">
       <c r="A403" s="3">
         <v>400</v>
       </c>
@@ -19276,7 +19272,7 @@
       </c>
       <c r="L403" s="1"/>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12">
       <c r="A404" s="3">
         <v>401</v>
       </c>
@@ -19312,7 +19308,7 @@
       </c>
       <c r="L404" s="1"/>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12">
       <c r="A405" s="3">
         <v>402</v>
       </c>
@@ -19326,7 +19322,7 @@
         <v>1373</v>
       </c>
       <c r="E405" s="1">
-        <v>3915950</v>
+        <v>161741108</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>1377</v>
@@ -19348,7 +19344,7 @@
       </c>
       <c r="L405" s="1"/>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12">
       <c r="A406" s="3">
         <v>403</v>
       </c>
@@ -19362,7 +19358,7 @@
         <v>1373</v>
       </c>
       <c r="E406" s="1">
-        <v>161741108</v>
+        <v>3915950</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>1380</v>
@@ -19384,7 +19380,7 @@
       </c>
       <c r="L406" s="1"/>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12">
       <c r="A407" s="3">
         <v>404</v>
       </c>
@@ -19420,7 +19416,7 @@
       </c>
       <c r="L407" s="1"/>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12">
       <c r="A408" s="3">
         <v>405</v>
       </c>
@@ -19456,7 +19452,7 @@
       </c>
       <c r="L408" s="1"/>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12">
       <c r="A409" s="3">
         <v>406</v>
       </c>
@@ -19492,7 +19488,7 @@
       </c>
       <c r="L409" s="1"/>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12">
       <c r="A410" s="3">
         <v>407</v>
       </c>
@@ -19528,7 +19524,7 @@
       </c>
       <c r="L410" s="1"/>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12">
       <c r="A411" s="3">
         <v>408</v>
       </c>
@@ -19542,7 +19538,7 @@
         <v>1396</v>
       </c>
       <c r="E411" s="1">
-        <v>346500</v>
+        <v>4759600</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>1397</v>
@@ -19551,7 +19547,7 @@
         <v>1392</v>
       </c>
       <c r="H411" s="1" t="s">
-        <v>137</v>
+        <v>1170</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>17</v>
@@ -19564,7 +19560,7 @@
       </c>
       <c r="L411" s="1"/>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12">
       <c r="A412" s="3">
         <v>409</v>
       </c>
@@ -19578,7 +19574,7 @@
         <v>1396</v>
       </c>
       <c r="E412" s="1">
-        <v>4759600</v>
+        <v>346500</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>1400</v>
@@ -19587,7 +19583,7 @@
         <v>1392</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>1173</v>
+        <v>137</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>17</v>
@@ -19600,7 +19596,7 @@
       </c>
       <c r="L412" s="1"/>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12">
       <c r="A413" s="3">
         <v>410</v>
       </c>
@@ -19636,7 +19632,7 @@
       </c>
       <c r="L413" s="1"/>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12">
       <c r="A414" s="3">
         <v>411</v>
       </c>
@@ -19672,7 +19668,7 @@
       </c>
       <c r="L414" s="1"/>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12">
       <c r="A415" s="3">
         <v>412</v>
       </c>
@@ -19686,34 +19682,34 @@
         <v>1373</v>
       </c>
       <c r="E415" s="1">
-        <v>199981800</v>
+        <v>694524200</v>
       </c>
       <c r="F415" s="1" t="s">
         <v>1411</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>59</v>
       </c>
       <c r="J415" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="K415" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L415" s="1"/>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12">
       <c r="A416" s="3">
         <v>413</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>1406</v>
@@ -19722,16 +19718,16 @@
         <v>1373</v>
       </c>
       <c r="E416" s="1">
-        <v>176866300</v>
+        <v>199981800</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="H416" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>59</v>
@@ -19744,7 +19740,7 @@
       </c>
       <c r="L416" s="1"/>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12">
       <c r="A417" s="3">
         <v>414</v>
       </c>
@@ -19758,13 +19754,13 @@
         <v>1373</v>
       </c>
       <c r="E417" s="1">
-        <v>694524200</v>
+        <v>176866300</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>1418</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H417" s="1" t="s">
         <v>63</v>
@@ -19780,7 +19776,7 @@
       </c>
       <c r="L417" s="1"/>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12">
       <c r="A418" s="3">
         <v>415</v>
       </c>
@@ -19800,7 +19796,7 @@
         <v>1421</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H418" s="1" t="s">
         <v>63</v>
@@ -19816,7 +19812,7 @@
       </c>
       <c r="L418" s="1"/>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12">
       <c r="A419" s="3">
         <v>416</v>
       </c>
@@ -19852,7 +19848,7 @@
       </c>
       <c r="L419" s="1"/>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12">
       <c r="A420" s="3">
         <v>417</v>
       </c>
@@ -19872,7 +19868,7 @@
         <v>1427</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H420" s="1" t="s">
         <v>63</v>
@@ -19888,7 +19884,7 @@
       </c>
       <c r="L420" s="1"/>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12">
       <c r="A421" s="3">
         <v>418</v>
       </c>
@@ -19908,7 +19904,7 @@
         <v>1432</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H421" s="1" t="s">
         <v>17</v>
@@ -19924,7 +19920,7 @@
       </c>
       <c r="L421" s="1"/>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12">
       <c r="A422" s="3">
         <v>419</v>
       </c>
@@ -19938,7 +19934,7 @@
         <v>1436</v>
       </c>
       <c r="E422" s="1">
-        <v>120000000</v>
+        <v>4759600</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>1437</v>
@@ -19947,25 +19943,25 @@
         <v>1435</v>
       </c>
       <c r="H422" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I422" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J422" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="I422" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J422" s="1" t="s">
-        <v>1439</v>
-      </c>
       <c r="K422" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="1"/>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12">
       <c r="A423" s="3">
         <v>420</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>1435</v>
@@ -19974,16 +19970,16 @@
         <v>1436</v>
       </c>
       <c r="E423" s="1">
-        <v>4759600</v>
+        <v>120000000</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>1435</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>1173</v>
+        <v>1441</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>17</v>
@@ -19996,7 +19992,7 @@
       </c>
       <c r="L423" s="1"/>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12">
       <c r="A424" s="3">
         <v>421</v>
       </c>
@@ -20032,7 +20028,7 @@
       </c>
       <c r="L424" s="1"/>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12">
       <c r="A425" s="3">
         <v>422</v>
       </c>
@@ -20068,7 +20064,7 @@
       </c>
       <c r="L425" s="1"/>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12">
       <c r="A426" s="3">
         <v>423</v>
       </c>
@@ -20104,7 +20100,7 @@
       </c>
       <c r="L426" s="1"/>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12">
       <c r="A427" s="3">
         <v>424</v>
       </c>
@@ -20140,7 +20136,7 @@
       </c>
       <c r="L427" s="1"/>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12">
       <c r="A428" s="3">
         <v>425</v>
       </c>
@@ -20176,7 +20172,7 @@
       </c>
       <c r="L428" s="1"/>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12">
       <c r="A429" s="3">
         <v>426</v>
       </c>
@@ -20212,7 +20208,7 @@
       </c>
       <c r="L429" s="1"/>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12">
       <c r="A430" s="3">
         <v>427</v>
       </c>
@@ -20248,7 +20244,7 @@
       </c>
       <c r="L430" s="1"/>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12">
       <c r="A431" s="3">
         <v>428</v>
       </c>
@@ -20284,7 +20280,7 @@
       </c>
       <c r="L431" s="1"/>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12">
       <c r="A432" s="3">
         <v>429</v>
       </c>
@@ -20320,7 +20316,7 @@
       </c>
       <c r="L432" s="1"/>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12">
       <c r="A433" s="3">
         <v>430</v>
       </c>
@@ -20356,7 +20352,7 @@
       </c>
       <c r="L433" s="1"/>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12">
       <c r="A434" s="3">
         <v>431</v>
       </c>
@@ -20392,7 +20388,7 @@
       </c>
       <c r="L434" s="1"/>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12">
       <c r="A435" s="3">
         <v>432</v>
       </c>
@@ -20428,12 +20424,21 @@
       </c>
       <c r="L435" s="1"/>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12">
       <c r="A436" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" orientation="landscape"/>
+  <pageSetup paperSize="5" orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>